--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69C39F2-55C1-4CE6-8DF6-1EE85B719096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED30AF78-6B06-410A-9F13-2FAE528138F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="285" windowWidth="30375" windowHeight="15345" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="139">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -303,18 +303,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>bg_hall</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>SE</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>se_jihanki</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>TEXT</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -417,159 +409,187 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>계주라던가, 어때?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001008</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001009</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아… 최악이야. 계주같은 건, 죽어도 사양이야</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_jito lip_cry</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>에, 정말? 계주는 운동회의 꽃이잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001010</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러니까 싫은 거야. 그렇게 보는 눈이 많은 곳에서 넘어지기라도 해 봐.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001011</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001012</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001013</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>애초에 후유, 달리기 그렇게 잘 하는 편이 아니니까…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬들에게 완벽하지 않은 모습은 보여주고 싶지 않아.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001014</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇구나… 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001015</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 근데 아사히쨩은 분명 이어달리기 나가고 싶어할 텐데…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 녀석 성격 상, 무조건 그렇겠지…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐만, 메이.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001016</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001017</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001018</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_surp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>왠지 불길한 기분이 들어… 빨리 돌아가자.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001019</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 잠깐만 후유코쨩!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001020</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>iris</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
     <t>zoom</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_can</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>계주라던가, 어때?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001008</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001009</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아… 최악이야. 계주같은 건, 죽어도 사양이야</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_jito lip_cry</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>에, 정말? 계주는 운동회의 꽃이잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001010</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러니까 싫은 거야. 그렇게 보는 눈이 많은 곳에서 넘어지기라도 해 봐.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001011</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001012</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001013</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>애초에 후유, 달리기 그렇게 잘 하는 편이 아니니까…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>팬들에게 완벽하지 않은 모습은 보여주고 싶지 않아.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001014</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇구나… 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001015</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아, 근데 아사히쨩은 분명 이어달리기 나가고 싶어할 텐데…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 녀석 성격 상, 무조건 그렇겠지…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠깐만, 메이.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001016</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001017</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001018</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_surp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>왠지 불길한 기분이 들어… 빨리 돌아가자.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001019</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_anger</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 잠깐만 후유코쨩!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001020</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>iris</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_iris_out|se_iris_in</t>
+  </si>
+  <si>
+    <t>skill2 face_sad</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 face_jito lip_anger</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_trans_out|se_trans_in</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_rouka</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_jihannki</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_tansan</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>달려나가는 SE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 face_serious lip_sad</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이거 추가합시다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +648,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,6 +664,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +694,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -691,6 +717,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,8 +784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}" name="표1" displayName="표1" ref="B2:P30" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P30" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}" name="표1" displayName="표1" ref="B2:P32" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P32" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F024CDFB-5FBA-43BE-BDFD-3D0EC697E324}" uniqueName="Type" name="Type">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
@@ -1442,7 +1471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4195EE-9A61-4194-93C9-2C566DA7C2D7}">
-  <dimension ref="B2:P30"/>
+  <dimension ref="A2:P32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.9140625" bestFit="1" customWidth="1"/>
@@ -1510,81 +1539,63 @@
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>67</v>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="M5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1592,25 +1603,25 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
         <v>73</v>
-      </c>
-      <c r="G7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" t="s">
-        <v>75</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -1618,25 +1629,25 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1644,25 +1655,25 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1670,16 +1681,25 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1687,25 +1707,16 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
         <v>68</v>
       </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
       <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
         <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
-        <v>83</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1713,400 +1724,444 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7" t="s">
-        <v>65</v>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+      <c r="P13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>66</v>
       </c>
-      <c r="M14" t="s">
-        <v>96</v>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" t="s">
-        <v>83</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="M15" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
         <v>68</v>
       </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
       <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
         <v>100</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>129</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" t="s">
+        <v>137</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
+        <v>115</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" t="s">
+        <v>118</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" t="s">
+        <v>130</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" t="s">
         <v>99</v>
       </c>
-      <c r="F16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" t="s">
-        <v>101</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" t="s">
-        <v>107</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>114</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" t="s">
-        <v>117</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="L31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" t="s">
         <v>124</v>
       </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" t="s">
-        <v>127</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" t="s">
-        <v>73</v>
-      </c>
-      <c r="G29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H29" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="O32" t="s">
         <v>131</v>
-      </c>
-      <c r="O30" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED30AF78-6B06-410A-9F13-2FAE528138F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2656F494-ECA0-47C3-81D1-F4F08C31DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
@@ -581,15 +581,14 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>달려나가는 SE</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>wait2 face_serious lip_sad</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>이거 추가합시다</t>
+    <t>se_rouka_run</t>
+  </si>
+  <si>
+    <t>2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -648,7 +647,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,12 +663,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,7 +687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -717,9 +710,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1471,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4195EE-9A61-4194-93C9-2C566DA7C2D7}">
-  <dimension ref="A2:P32"/>
+  <dimension ref="B2:P32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.9140625" bestFit="1" customWidth="1"/>
@@ -1804,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>66</v>
       </c>
@@ -1830,7 +1820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>66</v>
       </c>
@@ -1856,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>66</v>
       </c>
@@ -1882,7 +1872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>66</v>
       </c>
@@ -1899,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>66</v>
       </c>
@@ -1916,7 +1906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>66</v>
       </c>
@@ -1942,7 +1932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>66</v>
       </c>
@@ -1968,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>66</v>
       </c>
@@ -1988,13 +1978,13 @@
         <v>77</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>66</v>
       </c>
@@ -2020,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>66</v>
       </c>
@@ -2046,7 +2036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>66</v>
       </c>
@@ -2072,7 +2062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>90</v>
       </c>
@@ -2080,7 +2070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>64</v>
       </c>
@@ -2103,8 +2093,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>65</v>
       </c>
@@ -2121,13 +2110,13 @@
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>66</v>
       </c>
@@ -2153,7 +2142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>90</v>
       </c>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2656F494-ECA0-47C3-81D1-F4F08C31DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB345C6F-CB68-49DB-A73B-2632EB930D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
     <sheet name="Script" sheetId="2" r:id="rId2"/>
+    <sheet name="Template" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="239">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -582,13 +583,376 @@
   </si>
   <si>
     <t>wait2 face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>wait2 face_serious lip_sad</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>se_rouka_run</t>
   </si>
   <si>
-    <t>2</t>
+    <t>wait1 face_jito lip_cry</t>
+  </si>
+  <si>
+    <t>* 마유즈미 후유코</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진심으로 싫음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진지한 무표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 이즈미 메이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 놀람</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>걱정? 진지? 조금 애매한 표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_idol_3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>방송 PD</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>와하핫! 좋네, 그거!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히쨩이 멋있게 달리는 거, 분명 그림이 될 테니까!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 세리자와 아사히</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>두근두근</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그거, 본 적 있슴다!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 감독님이 카메라를 들고 선수보다 빨리 뛰는 거!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 아무리 그래도 직접 들고 뛰진 않지~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐야, 직접 뛰는 건 줄 알았슴다…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>실망</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐, 옛날에는 직접 들고 뛰었을지도 모르겠지만</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금은 보통 트랙 러너 카메라라는 녀석으로 찍거든</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 트랙 러너 카메라라는 거, 빠른 검까?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>고민/궁금</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그야 달리는 선수들을 찍어야 하니까 당연히…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼, 그 녀석을 이기면 제가 1등인 거네요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>밝게 웃음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하하! 그렇네, 아사히쨩이 이길 수 있다면 말이지!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 트랙… 무슨 카메라는 지금 어디있슴까?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨리 승부하고 싶슴다!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쉽게도 다음 달 대여 예정이라서~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하십니다~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하십니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 달까지는 못 기다림다~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀엽게 토라짐</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기, 프로듀서 님… 이건…?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_bitter_smile</t>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_bitter_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>곤란한 웃음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로듀서</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 후유코, 메이. 어서 와.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>PD님이랑 아사히가 다음 달에 나갈 운동회 이야기를 하고 있던 중이었는데…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>어, 마침 잘 왔네!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트한테는 꼭 이어달리기에 나가줬으면 해서!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 사람도 괜찮지? 운동 잘 하잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>P, PD님, 잠시…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 그건…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_surp lip_surp</t>
+  </si>
+  <si>
+    <t>wait1 face_surp lip_surp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작 없이 놀람</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>네. 저희한테 맡겨주세요.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후, 후유코쨩…?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코…?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하, 좋네! 그럼 다음 달에 잘 부탁해!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>네, 잘 부탁드립니다~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_sime</t>
+  </si>
+  <si>
+    <t>door_knock</t>
+  </si>
+  <si>
+    <t>작년 방송이 꽤 화제가 돼서 말이야.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 이어달리기용 원샷 카메라도 준비해뒀다고!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001021</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001022</t>
+  </si>
+  <si>
+    <t>s001023</t>
+  </si>
+  <si>
+    <t>s001024</t>
+  </si>
+  <si>
+    <t>s001025</t>
+  </si>
+  <si>
+    <t>s001026</t>
+  </si>
+  <si>
+    <t>s001027</t>
+  </si>
+  <si>
+    <t>s001028</t>
+  </si>
+  <si>
+    <t>s001029</t>
+  </si>
+  <si>
+    <t>s001030</t>
+  </si>
+  <si>
+    <t>s001031</t>
+  </si>
+  <si>
+    <t>s001032</t>
+  </si>
+  <si>
+    <t>s001033</t>
+  </si>
+  <si>
+    <t>s001034</t>
+  </si>
+  <si>
+    <t>s001035</t>
+  </si>
+  <si>
+    <t>s001036</t>
+  </si>
+  <si>
+    <t>s001037</t>
+  </si>
+  <si>
+    <t>s001039</t>
+  </si>
+  <si>
+    <t>s001040</t>
+  </si>
+  <si>
+    <t>s001041</t>
+  </si>
+  <si>
+    <t>s001042</t>
+  </si>
+  <si>
+    <t>s001043</t>
+  </si>
+  <si>
+    <t>s001044</t>
+  </si>
+  <si>
+    <t>s001045</t>
+  </si>
+  <si>
+    <t>s001046</t>
+  </si>
+  <si>
+    <t>s001047</t>
+  </si>
+  <si>
+    <t>s001048</t>
+  </si>
+  <si>
+    <t>s001049</t>
+  </si>
+  <si>
+    <t>s001050</t>
+  </si>
+  <si>
+    <t>s001051</t>
+  </si>
+  <si>
+    <t>s001052</t>
+  </si>
+  <si>
+    <t>s001053</t>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001038</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +1011,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +1027,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +1057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -710,6 +1080,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,8 +1147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}" name="표1" displayName="표1" ref="B2:P32" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P32" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}" name="표1" displayName="표1" ref="B2:P73" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P73" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F024CDFB-5FBA-43BE-BDFD-3D0EC697E324}" uniqueName="Type" name="Type">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
@@ -1461,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4195EE-9A61-4194-93C9-2C566DA7C2D7}">
-  <dimension ref="B2:P32"/>
+  <dimension ref="A2:P73"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.9140625" bestFit="1" customWidth="1"/>
@@ -1535,6 +1908,9 @@
       <c r="M3" t="s">
         <v>39</v>
       </c>
+      <c r="N3">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
@@ -1736,36 +2112,39 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="M14" t="s">
+        <v>135</v>
+      </c>
+      <c r="N14">
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" t="s">
-        <v>135</v>
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
@@ -1794,7 +2173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>66</v>
       </c>
@@ -1820,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>66</v>
       </c>
@@ -1846,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>66</v>
       </c>
@@ -1872,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>66</v>
       </c>
@@ -1889,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>66</v>
       </c>
@@ -1906,7 +2285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>66</v>
       </c>
@@ -1932,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>66</v>
       </c>
@@ -1958,7 +2337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>66</v>
       </c>
@@ -1978,13 +2357,13 @@
         <v>77</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>66</v>
       </c>
@@ -2010,7 +2389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>66</v>
       </c>
@@ -2036,7 +2415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>66</v>
       </c>
@@ -2062,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>90</v>
       </c>
@@ -2070,7 +2449,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>64</v>
       </c>
@@ -2093,7 +2472,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>65</v>
       </c>
@@ -2106,17 +2485,17 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>66</v>
       </c>
@@ -2142,7 +2521,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
       <c r="B32" t="s">
         <v>90</v>
       </c>
@@ -2150,6 +2530,784 @@
         <v>124</v>
       </c>
       <c r="O32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>133</v>
+      </c>
+      <c r="M33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="P34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" t="s">
+        <v>149</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" t="s">
+        <v>205</v>
+      </c>
+      <c r="L36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" t="s">
+        <v>206</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" t="s">
+        <v>207</v>
+      </c>
+      <c r="L38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" t="s">
+        <v>208</v>
+      </c>
+      <c r="L39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" t="s">
+        <v>154</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" t="s">
+        <v>211</v>
+      </c>
+      <c r="L42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" t="s">
+        <v>160</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" t="s">
+        <v>213</v>
+      </c>
+      <c r="L44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" t="s">
+        <v>214</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" t="s">
+        <v>215</v>
+      </c>
+      <c r="F46" t="s">
+        <v>147</v>
+      </c>
+      <c r="G46" t="s">
+        <v>148</v>
+      </c>
+      <c r="H46" t="s">
+        <v>165</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" t="s">
+        <v>167</v>
+      </c>
+      <c r="E47" t="s">
+        <v>216</v>
+      </c>
+      <c r="L47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" t="s">
+        <v>168</v>
+      </c>
+      <c r="E48" t="s">
+        <v>217</v>
+      </c>
+      <c r="F48" t="s">
+        <v>147</v>
+      </c>
+      <c r="G48" t="s">
+        <v>148</v>
+      </c>
+      <c r="H48" t="s">
+        <v>169</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" t="s">
+        <v>171</v>
+      </c>
+      <c r="E49" t="s">
+        <v>218</v>
+      </c>
+      <c r="L49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" t="s">
+        <v>148</v>
+      </c>
+      <c r="H50" t="s">
+        <v>154</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>220</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" t="s">
+        <v>221</v>
+      </c>
+      <c r="L52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="P54" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B55" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" t="s">
+        <v>175</v>
+      </c>
+      <c r="E56" t="s">
+        <v>238</v>
+      </c>
+      <c r="F56" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" t="s">
+        <v>196</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>176</v>
+      </c>
+      <c r="E57" t="s">
+        <v>222</v>
+      </c>
+      <c r="F57" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s">
+        <v>111</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" t="s">
+        <v>147</v>
+      </c>
+      <c r="G58" t="s">
+        <v>148</v>
+      </c>
+      <c r="H58" t="s">
+        <v>178</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" t="s">
+        <v>224</v>
+      </c>
+      <c r="F59" t="s">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s">
+        <v>72</v>
+      </c>
+      <c r="H59" t="s">
+        <v>182</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" t="s">
+        <v>225</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
+        <v>186</v>
+      </c>
+      <c r="E61" t="s">
+        <v>226</v>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" t="s">
+        <v>187</v>
+      </c>
+      <c r="E62" t="s">
+        <v>227</v>
+      </c>
+      <c r="L62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63" t="s">
+        <v>228</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" t="s">
+        <v>189</v>
+      </c>
+      <c r="E64" t="s">
+        <v>229</v>
+      </c>
+      <c r="L64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" t="s">
+        <v>230</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>191</v>
+      </c>
+      <c r="E66" t="s">
+        <v>231</v>
+      </c>
+      <c r="F66" t="s">
+        <v>71</v>
+      </c>
+      <c r="G66" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s">
+        <v>193</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" t="s">
+        <v>195</v>
+      </c>
+      <c r="E67" t="s">
+        <v>232</v>
+      </c>
+      <c r="F67" t="s">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s">
+        <v>72</v>
+      </c>
+      <c r="H67" t="s">
+        <v>196</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>197</v>
+      </c>
+      <c r="E68" t="s">
+        <v>233</v>
+      </c>
+      <c r="F68" t="s">
+        <v>71</v>
+      </c>
+      <c r="G68" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" t="s">
+        <v>99</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>66</v>
+      </c>
+      <c r="C69" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" t="s">
+        <v>198</v>
+      </c>
+      <c r="E69" t="s">
+        <v>234</v>
+      </c>
+      <c r="L69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" t="s">
+        <v>235</v>
+      </c>
+      <c r="L70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D71" t="s">
+        <v>200</v>
+      </c>
+      <c r="E71" t="s">
+        <v>236</v>
+      </c>
+      <c r="F71" t="s">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s">
+        <v>72</v>
+      </c>
+      <c r="H71" t="s">
+        <v>196</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B72" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="8"/>
+      <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="I73" t="s">
+        <v>124</v>
+      </c>
+      <c r="O73" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2160,4 +3318,102 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0AC287-6B30-491F-A320-ECD650B57881}">
+  <dimension ref="B2:P7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M3" t="s">
+        <v>154</v>
+      </c>
+      <c r="P3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" t="s">
+        <v>145</v>
+      </c>
+      <c r="M4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J5" t="s">
+        <v>194</v>
+      </c>
+      <c r="M5" t="s">
+        <v>165</v>
+      </c>
+      <c r="P5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>169</v>
+      </c>
+      <c r="P6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>178</v>
+      </c>
+      <c r="P7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2385AC71-56F3-493B-89DA-886A8DDAADBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E731F8F-826B-4BDA-A4FF-B3EA5F72EC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="855" windowWidth="30375" windowHeight="15345" activeTab="3" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="30375" windowHeight="15345" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
-    <sheet name="Script_Demo" sheetId="2" r:id="rId2"/>
+    <sheet name="Script_Demo" sheetId="7" r:id="rId2"/>
     <sheet name="Template" sheetId="3" r:id="rId3"/>
     <sheet name="VoiceMatch" sheetId="5" r:id="rId4"/>
+    <sheet name="BGMMatcth" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="476">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -313,405 +314,1508 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>wait1 face_surp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill2 face_sad</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>wait1 face_jito lip_cry</t>
+  </si>
+  <si>
+    <t>* 마유즈미 후유코</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진심으로 싫음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진지한 무표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 이즈미 메이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 놀람</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>걱정? 진지? 조금 애매한 표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 세리자와 아사히</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>실망</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>고민/궁금</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>밝게 웃음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀엽게 토라짐</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_bitter_smile</t>
+  </si>
+  <si>
+    <t>곤란한 웃음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로듀서</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_surp lip_surp</t>
+  </si>
+  <si>
+    <t>동작 없이 놀람</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>후유코</t>
+  </si>
+  <si>
+    <t>fuyuko_idol_3</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>smile3 lip_wait</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>두근두근 (Lip Wait으로 해야 이빨 안보임)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>28명을 매칭해야 되는데… 개수가 부족하다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>일루미네</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>안티카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>마노</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>히오리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메구루</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>코가네</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>마미미</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>키리코</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사쿠야</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유이카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>알스메</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>치유키</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아마나</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>텐카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>방클걸</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>카호</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>쥬리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>린제</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>치요코</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나츠하</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹칠</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>토오루</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>마도카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>코이토</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>히나나</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>시즈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>미코토</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>니치카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>코메틱</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하루키</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>루카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메탄</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>즌다몬</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아오야마 류세이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유카</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>미타마</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>토바리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>앙코몬?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>츠루기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>비 &gt; 츠요츠요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>비슷한거같기도하고?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>키티탄</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>No7</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>shrug face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>iris</t>
+  </si>
+  <si>
+    <t>door_sime</t>
+  </si>
+  <si>
+    <t>se_trans_out|se_trans_in</t>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_anger2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진지하게 이야기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>lip_surp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히는 대부분 움직이는 게 없어서 surp가 거의 무표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 lip_anger</t>
+  </si>
+  <si>
+    <t>한숨 쉬며 도리도리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_sad lip_anger2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬픈 표정으로 이야기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_surp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진지한 표정으로 이야기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>웃는 입 대신 정색</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>어깨 으쓱</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001074</t>
+  </si>
+  <si>
+    <t>시리어스</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>こころのいろは</t>
+  </si>
+  <si>
+    <t>센치</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨音に寄り添う</t>
+  </si>
+  <si>
+    <t>굉장히 가라앉은 시리어스</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼吸の温度</t>
+  </si>
+  <si>
+    <t>에모이한 저녁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>街灯りで照らされて</t>
+  </si>
+  <si>
+    <t>슬픔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>88つの手触り</t>
+  </si>
+  <si>
+    <t>긴박함</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>通過していく光の意味を</t>
+  </si>
+  <si>
+    <t>エスプレッソと甘いクッキー</t>
+  </si>
+  <si>
+    <t>インディムライト</t>
+  </si>
+  <si>
+    <t>차분한 밤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>차분함 카페</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ロー・ポジション</t>
+  </si>
+  <si>
+    <t>과거회상같은 차분함</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후일담같은? 다음 날 아침</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나나쿠사 니치카 야쿠모 나미</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>재즈틱한 차분함</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴박한 액션</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>レッツ☆忍び足</t>
+  </si>
+  <si>
+    <t>샤니P 갈등의 곡</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>おかえり、ギター</t>
+  </si>
+  <si>
+    <t>나른한 일상</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>엉뚱한 일상</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wipe_left</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_room_fuyuko</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_phone</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[스트레이라이트는 이어달리기에 나가는 걸로 결정됐어.]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[다들 걱정되는 부분도 있겠지만, 최선을 다하면 좋은 결과가 있을 거라고 생각해.]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[네.]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[OK~]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>최선을 다하면, 말이지…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashback</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러게, 괜히 폼 같은 걸 잡아서…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuyuko_homewear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐 운동 갔다 올게요.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuyuko_sports_2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 face_serious</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코의 엄마</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침에 운동 갔다 왔잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 조금 다른 거.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 전에는 돌아와야 한다?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>7시 전에는 돌아올거야.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>다치지 말고~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>다녀오겠습니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>무표정으로 눈치챔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_phone_vibe</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 후유코. 잠시 괜찮아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_close lip_smile</t>
+  </si>
+  <si>
+    <t>wait1 face_close lip_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈 감고 농담</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>농담이야. 진지하게 받아들이지 마.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>별 내용은 아니니까, 후유코가 불편하다면…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>농담이라고 했잖아. 용건이나 말 해.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>용건이 있는 건 아니고, 달리기 연습은 잘 되고 있나 해서.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>너… 감이 너무 좋아서 기분 나빠.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 후유코는 하기 싫다고 말은 하지만, 분명 보이지 않는 곳에서 노력하고 있을 테니까.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>방금 거, 칭찬한 거 아니거든?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 이런 모습을 팬들이 볼 수 있으면, 더욱 좋아할텐데 말이야.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아? 절대 싫거든.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>너, 후유가 지금까지 쌓아온 이미지를 뭐라고 생각하는 거야…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>물론 그건 알지만, 프로듀서 입장에서는 아쉽다고 할까…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>용건 끝나셨으면 끊을게요, 프로듀서 님?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 미안. 그럼 마지막으로…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 뭔데.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코는 이미 충분히 열심히 하고 있으니까.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가끔은 자신에게 솔직해져도 된다고 생각해.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 물론 후유코의 생각이나 판단에 대해서는 나도 동의하고 있고…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>너도 바보네.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>너, 후유가 그걸 모르고 있을 것 같아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응. 그렇다면 안심이야.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>끊을게. 얼마만에 얻은 주말인데, 업무 전화에 설교까지…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>확 사장님한테 일러버릴까보다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>안 해. 후유, 다시 연습하러 갈 거니까.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응. 무슨 일 생기거나 하면 바로 연락 줘.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 네~</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람들이 보고 싶어하는 건, 항상 완벽한 모습 뿐이 아니란 말이지…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 하지만 그런 걸로는, 후유가 납득 못 한다고.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아… 하아…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬슬 돌아가야…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌써 시간이 이렇게…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[후유코쨩, 잠깐 통화 괜찮아?]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유, 언제부터 이렇게 인기 만점이 됐는지 모르겠네.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 후유코쨩!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 무슨 일이야?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>wait1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>smile2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_surp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>skill2 face_sad</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait2 face_serious lip_sad</t>
-  </si>
-  <si>
-    <t>wait1 face_jito lip_cry</t>
-  </si>
-  <si>
-    <t>* 마유즈미 후유코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>진심으로 싫음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>진지한 무표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 이즈미 메이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>살짝 놀람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>걱정? 진지? 조금 애매한 표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 세리자와 아사히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>sad2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>실망</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>think1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>고민/궁금</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>밝게 웃음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀엽게 토라짐</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_smile lip_bitter_smile</t>
-  </si>
-  <si>
-    <t>곤란한 웃음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로듀서</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_surp lip_surp</t>
-  </si>
-  <si>
-    <t>동작 없이 놀람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-  <si>
-    <t>메이</t>
-  </si>
-  <si>
-    <t>후유코</t>
-  </si>
-  <si>
-    <t>아사히</t>
-  </si>
-  <si>
-    <t>mei_idol_3</t>
-  </si>
-  <si>
-    <t>fuyuko_idol_3</t>
-  </si>
-  <si>
-    <t>asahi_idol_3</t>
-  </si>
-  <si>
-    <t>left</t>
-  </si>
-  <si>
-    <t>right</t>
-  </si>
-  <si>
-    <t>center</t>
-  </si>
-  <si>
-    <t>think1</t>
-  </si>
-  <si>
-    <t>smile1</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>smile3 lip_wait</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>두근두근 (Lip Wait으로 해야 이빨 안보임)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CGGROUP</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s002001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건 뭐 찍고 있는 검까?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히쨩? 아까 대기실에서 이야기했잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에 새롭게 오픈하는 극장 선전이야.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤에. 그렇슴까.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>우, 우선 인사드리자</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕하세요. 저희는,</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트입니다!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s002002</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>s002003</t>
-  </si>
-  <si>
-    <t>s002004</t>
-  </si>
-  <si>
-    <t>s002005</t>
-  </si>
-  <si>
-    <t>s002006</t>
-  </si>
-  <si>
-    <t>s002007 s002008 s002009</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>28명을 매칭해야 되는데… 개수가 부족하다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>일루미네</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>안티카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>마노</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>히오리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>메구루</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>코가네</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>마미미</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>키리코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>사쿠야</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>유이카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>알스메</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>치유키</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아마나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>텐카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>방클걸</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>카호</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>쥬리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>린제</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>치요코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나츠하</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>녹칠</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>토오루</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>마도카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>코이토</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>히나나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>시즈</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>미코토</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>니치카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>코메틱</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>하루키</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>하나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>루카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>메탄</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>즌다몬</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아오야마 류세이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>유카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>미타마</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>토바리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>앙코몬?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>츠루기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>비 &gt; 츠요츠요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>비슷한거같기도하고?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>키티탄</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>No7</t>
+    <t>그… 하고 싶은 말이 있어서!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔데?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저번에 후유코쨩이랑 있을 때, 후유코쨩이 해준 이야기 말이야…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>완벽하지 않은 모습을 보여주기 싫다는 이야기?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응. 근데 결국 이어달리기 나가게 돼서…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나, 열심히 생각해 봤어.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 할 수 있는 게 뭘까 하고.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 후유코쨩의 마음도 이해하고 있고, 아사히쨩이 하고 싶다면 같이 하고 싶다고도 생각하니까.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떻게 하면 해결할 수 있을까, 하고.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(그런 거, 그냥 후유의 고집을 뿐인데.)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(메이, 네가 고민하고 해결해야 할 이유같은 건 조금도…)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>근데, 역시 모르겠더라고!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이, 너 말이야…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하, 마법같이 짜잔~ 하고 해결할 방법같은 거, 나한테는 안 떠오르더라고</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서 말이야,</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그냥 내가 할 수 있는 일을 하기로 했어!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀람</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>할 수 있는 일?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히쨩은 이어달리기에서 1등을 하고 싶은 거고,</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩은 팬들 앞에서 진심으로 달리는 모습을 보이는 게 싫은 거잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐, 완벽히 그렇다는 건 아니지만…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼 엄~청 빠르게 달리면 된다는 거잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이, 너…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_sad lip_bitter_smile</t>
+  </si>
+  <si>
+    <t>wait1 face_sad lip_bitter_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>감동받은 표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서, 사실 지금 달리기 연습하는 중이거든!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>남은 2주동안 매일매일 달리면 빨라지지 않을까?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇네…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>대박인게, 오늘 하루 연습했는데도 왠지 엄청 빨라진 것 같은 기분이…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 너도 바보네.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>엣, 어째서?!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>네가 그렇게 이야기하면 후유가, '알겠어. 내 몫까지 죽을 힘을 다해서 달려줘.' 할 줄 알았어?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하, 그것도 그렇네!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>고마워.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러고 보니, 후유코쨩은 지금 뭐 하고 있었어?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_close3 lip_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈 감고 웃음 (곤란)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 그냥, 잠깐 바람 쐬러 나왔어.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇구나… 아!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 라디오 QNA 쓰는 거 까먹고 있었다!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질렸다는 표정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_jito lip_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>한가롭게 달리기나 할 때가 아니잖아…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진심 큰일날 뻔 했다... 그럼, 이만 끊을게 후유코쨩!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>작가님이 불쌍하니까, 빨리 해서 보내.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>응! 후유코쨩!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>또 뭔데?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 맛있게 먹어!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_smile</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 메이 너도.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 한 팀이니까!</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 팀이니까…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히, 왜 그렇게 1등을 하고 싶어하는 거야?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2 lip_sad</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuyuko_normal_9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_normal_3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩은 1등하고 싶지 않은 검까?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그게 왜 그렇게 되는데…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유도 가능하다면 1등을 하는 게 좋다고 생각해.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 그렇다고 해서, 모든 것에서 1등을 해야 할 필요는 없잖아?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1등을 하는 건 최강이라는 검다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 스트레이라이트는 항상 최강을 목표로 함다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러니까, 저는 항상 1등을 하고 싶슴다. 스트레이라이트니까요.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진짜, 후유의 주위에는 바보들 뿐이네.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이러다가, 바보가 옮아 버리겠어.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>미안. 오랜만에 얻은 휴일인데…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴일에 업무 전화가 왔다는 것만 빼면 괜찮아.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 그것만큼은 봐 줘.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002003</t>
+  </si>
+  <si>
+    <t>S002002</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002004</t>
+  </si>
+  <si>
+    <t>S002005</t>
+  </si>
+  <si>
+    <t>S002006</t>
+  </si>
+  <si>
+    <t>S002007</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002008</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002009</t>
+  </si>
+  <si>
+    <t>S002010</t>
+  </si>
+  <si>
+    <t>S002011</t>
+  </si>
+  <si>
+    <t>S002012</t>
+  </si>
+  <si>
+    <t>S002013</t>
+  </si>
+  <si>
+    <t>S002014</t>
+  </si>
+  <si>
+    <t>S002015</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002025</t>
+  </si>
+  <si>
+    <t>S002016</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002017</t>
+  </si>
+  <si>
+    <t>S002018</t>
+  </si>
+  <si>
+    <t>S002019</t>
+  </si>
+  <si>
+    <t>S002020</t>
+  </si>
+  <si>
+    <t>S002021</t>
+  </si>
+  <si>
+    <t>S002022</t>
+  </si>
+  <si>
+    <t>S002023</t>
+  </si>
+  <si>
+    <t>S002024</t>
+  </si>
+  <si>
+    <t>S002026</t>
+  </si>
+  <si>
+    <t>S002027</t>
+  </si>
+  <si>
+    <t>S002028</t>
+  </si>
+  <si>
+    <t>S002029</t>
+  </si>
+  <si>
+    <t>S002030</t>
+  </si>
+  <si>
+    <t>S002031</t>
+  </si>
+  <si>
+    <t>S002032</t>
+  </si>
+  <si>
+    <t>S002033</t>
+  </si>
+  <si>
+    <t>S002035</t>
+  </si>
+  <si>
+    <t>S002036</t>
+  </si>
+  <si>
+    <t>S002037</t>
+  </si>
+  <si>
+    <t>S002038</t>
+  </si>
+  <si>
+    <t>S002039</t>
+  </si>
+  <si>
+    <t>S002040</t>
+  </si>
+  <si>
+    <t>S002041</t>
+  </si>
+  <si>
+    <t>S002042</t>
+  </si>
+  <si>
+    <t>S002043</t>
+  </si>
+  <si>
+    <t>S002044</t>
+  </si>
+  <si>
+    <t>S002045</t>
+  </si>
+  <si>
+    <t>S002046</t>
+  </si>
+  <si>
+    <t>S002047</t>
+  </si>
+  <si>
+    <t>S002048</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002049</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002050</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002051</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002052</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002053</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코도 이미 알고 있겠지만, 사람들이 보고 싶어하는 건, 항상 완벽한 모습 뿐이 아니라는 것</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것만은 잊지 말아줬으면 해.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002034</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002054</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002055</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002056</t>
+  </si>
+  <si>
+    <t>S002057</t>
+  </si>
+  <si>
+    <t>S002058</t>
+  </si>
+  <si>
+    <t>S002059</t>
+  </si>
+  <si>
+    <t>S002060</t>
+  </si>
+  <si>
+    <t>S002061</t>
+  </si>
+  <si>
+    <t>S002062</t>
+  </si>
+  <si>
+    <t>S002063</t>
+  </si>
+  <si>
+    <t>S002064</t>
+  </si>
+  <si>
+    <t>S002065</t>
+  </si>
+  <si>
+    <t>S002066</t>
+  </si>
+  <si>
+    <t>S002067</t>
+  </si>
+  <si>
+    <t>S002068</t>
+  </si>
+  <si>
+    <t>S002069</t>
+  </si>
+  <si>
+    <t>S002070</t>
+  </si>
+  <si>
+    <t>S002071</t>
+  </si>
+  <si>
+    <t>S002072</t>
+  </si>
+  <si>
+    <t>S002073</t>
+  </si>
+  <si>
+    <t>S002074</t>
+  </si>
+  <si>
+    <t>S002075</t>
+  </si>
+  <si>
+    <t>S002076</t>
+  </si>
+  <si>
+    <t>S002077</t>
+  </si>
+  <si>
+    <t>S002078</t>
+  </si>
+  <si>
+    <t>S002079</t>
+  </si>
+  <si>
+    <t>S002080</t>
+  </si>
+  <si>
+    <t>S002081</t>
+  </si>
+  <si>
+    <t>S002082</t>
+  </si>
+  <si>
+    <t>S002083</t>
+  </si>
+  <si>
+    <t>S002084</t>
+  </si>
+  <si>
+    <t>S002085</t>
+  </si>
+  <si>
+    <t>S002086</t>
+  </si>
+  <si>
+    <t>S002087</t>
+  </si>
+  <si>
+    <t>S002088</t>
+  </si>
+  <si>
+    <t>S002089</t>
+  </si>
+  <si>
+    <t>S002090</t>
+  </si>
+  <si>
+    <t>S002091</t>
+  </si>
+  <si>
+    <t>S002092</t>
+  </si>
+  <si>
+    <t>S002093</t>
+  </si>
+  <si>
+    <t>S002094</t>
+  </si>
+  <si>
+    <t>S002095</t>
+  </si>
+  <si>
+    <t>S002096</t>
+  </si>
+  <si>
+    <t>S002097</t>
+  </si>
+  <si>
+    <t>S002098</t>
+  </si>
+  <si>
+    <t>S002099</t>
+  </si>
+  <si>
+    <t>S002100</t>
+  </si>
+  <si>
+    <t>S002101</t>
+  </si>
+  <si>
+    <t>S002102</t>
+  </si>
+  <si>
+    <t>S002103</t>
+  </si>
+  <si>
+    <t>S002104</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002105</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002106</t>
+  </si>
+  <si>
+    <t>S002107</t>
+  </si>
+  <si>
+    <t>S002108</t>
+  </si>
+  <si>
+    <t>S002109</t>
+  </si>
+  <si>
+    <t>S002110</t>
+  </si>
+  <si>
+    <t>S002111</t>
+  </si>
+  <si>
+    <t>S002112</t>
+  </si>
+  <si>
+    <t>S002113</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S002114</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_living_fuyuko</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hasisita_day</t>
+  </si>
+  <si>
+    <t>bg_hasisita_sunset</t>
+  </si>
+  <si>
+    <t>se_footstep_slip</t>
+  </si>
+  <si>
+    <t>se_phone_long</t>
+  </si>
+  <si>
+    <t>se_phone_vibe</t>
+  </si>
+  <si>
+    <t>se_phone_short</t>
+  </si>
+  <si>
+    <t>bg_car_sunset</t>
+  </si>
+  <si>
+    <t>BGM_77</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -719,7 +1823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -769,6 +1873,26 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -810,7 +1934,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,6 +1957,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -897,52 +2030,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}" name="표1" displayName="표1" ref="B2:P13" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P13" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P152" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P152" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F024CDFB-5FBA-43BE-BDFD-3D0EC697E324}" uniqueName="Type" name="Type">
+    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{73C7A17F-D221-4CF8-B42F-2876AEAC322B}" uniqueName="Name" name="Name">
+    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DD550F31-322F-4817-807E-AAF3E6CF0FFF}" uniqueName="Text" name="Text">
+    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CDF95646-B83D-495D-BD41-06D7D3A95C54}" uniqueName="Voice" name="Voice">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1147BB2-0A7B-4622-BBAA-91570393BF78}" uniqueName="CG" name="CG">
+    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@CG" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4155DD9B-C05C-434F-A609-1CEAC810DDB9}" uniqueName="Position" name="Position">
+    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Position" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8BA44913-D749-4A3E-80D0-3168A1F34D0C}" uniqueName="Animation" name="Animation">
+    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Animation" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{11225872-C73D-45E3-8E99-BB2E74DB7DC5}" uniqueName="Effect" name="Effect">
+    <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Effect" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E39B4478-B8F4-473F-AC5F-B034D6CA7849}" uniqueName="Value" name="Value">
+    <tableColumn id="9" xr3:uid="{2C783B40-3686-4969-B9A9-74472F998668}" uniqueName="Value" name="Value">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2F734473-8501-4E3D-841A-731E04785078}" uniqueName="Duration" name="Duration">
+    <tableColumn id="10" xr3:uid="{7C434785-78DE-4265-81AB-F66F688FF0FE}" uniqueName="Duration" name="Duration">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Duration" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0FE56BB9-365C-4107-9D7D-F50088A6DF87}" uniqueName="SpeakerType" name="SpeakerType">
+    <tableColumn id="11" xr3:uid="{F6E13514-3140-425B-B085-594C866D0BE4}" uniqueName="SpeakerType" name="SpeakerType">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@SpeakerType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{179D82E1-B734-4421-85E0-55BA17590B22}" uniqueName="Track" name="Track">
+    <tableColumn id="12" xr3:uid="{81AD69B1-A848-4447-AE83-9939AF9AADE2}" uniqueName="Track" name="Track">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Track" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{44E25104-104B-4E0B-B46E-D8BC95108BFE}" uniqueName="Volume" name="Volume">
+    <tableColumn id="13" xr3:uid="{22867833-2213-4504-85D6-75D89AEE42DB}" uniqueName="Volume" name="Volume">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Volume" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{905C58BC-925F-41E8-8E03-FF9DF0EC66AE}" uniqueName="SE" name="SE">
+    <tableColumn id="14" xr3:uid="{09054161-AA65-4541-ADB6-9558E5C44DF4}" uniqueName="SE" name="SE">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@SE" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{A7F805DD-14D9-478F-8616-C2F64F1371E4}" uniqueName="Key" name="Key">
+    <tableColumn id="15" xr3:uid="{E0ADDA94-13D5-450F-B917-8EC04E0E722E}" uniqueName="Key" name="Key">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Key" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -1583,25 +2716,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4195EE-9A61-4194-93C9-2C566DA7C2D7}">
-  <dimension ref="B2:P13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
+  <dimension ref="B2:P152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
@@ -1653,7 +2786,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1665,71 +2798,63 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="M3" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>200</v>
+      </c>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>106</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
-      <c r="L4" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>121</v>
+        <v>351</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1738,32 +2863,20 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="7"/>
+        <v>207</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>208</v>
+      </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -1771,64 +2884,46 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>67</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>118</v>
+        <v>210</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>90</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -1837,16 +2932,16 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>119</v>
+        <v>211</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1855,7 +2950,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1864,27 +2959,25 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1893,26 +2986,26 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="7" t="s">
+        <v>225</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -1920,26 +3013,28 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+        <v>65</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="F12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="L12" s="7" t="s">
+        <v>212</v>
+      </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -1947,32 +3042,3923 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>112</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B32" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P33" s="7"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="N35" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B38" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B42" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B44" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B45" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B46" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B47" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B48" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B49" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B50" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B51" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B52" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B53" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B54" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B55" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B56" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B57" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B58" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M58" s="7"/>
+      <c r="N58" s="7"/>
+      <c r="O58" s="7"/>
+      <c r="P58" s="7"/>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B59" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B60" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M61" s="7"/>
+      <c r="N61" s="7"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B62" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B63" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B64" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M64" s="7"/>
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="7"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B65" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M65" s="7"/>
+      <c r="N65" s="7"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="7"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B66" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M66" s="7"/>
+      <c r="N66" s="7"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="7"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B67" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B68" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B69" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M69" s="7"/>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B70" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B71" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B72" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B73" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P73" s="7"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B74" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B75" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B76" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B77" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B78" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
+      <c r="O78" s="7"/>
+      <c r="P78" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B79" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+    </row>
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B80" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+    </row>
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B81" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="N81" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+    </row>
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B82" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+    </row>
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B83" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+      <c r="P83" s="7"/>
+    </row>
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B84" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B85" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
+      <c r="P85" s="7"/>
+    </row>
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B86" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N86" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
+    </row>
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B87" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M87" s="7"/>
+      <c r="N87" s="7"/>
+      <c r="O87" s="7"/>
+      <c r="P87" s="7"/>
+    </row>
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B88" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M88" s="7"/>
+      <c r="N88" s="7"/>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
+    </row>
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B89" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M89" s="7"/>
+      <c r="N89" s="7"/>
+      <c r="O89" s="7"/>
+      <c r="P89" s="7"/>
+    </row>
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B90" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I90" s="7"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M90" s="7"/>
+      <c r="N90" s="7"/>
+      <c r="O90" s="7"/>
+      <c r="P90" s="7"/>
+    </row>
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B91" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M91" s="7"/>
+      <c r="N91" s="7"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
+    </row>
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B92" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M92" s="7"/>
+      <c r="N92" s="7"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7"/>
+    </row>
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B93" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+    </row>
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B94" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M94" s="7"/>
+      <c r="N94" s="7"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+    </row>
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B95" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M95" s="7"/>
+      <c r="N95" s="7"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+    </row>
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B96" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M96" s="7"/>
+      <c r="N96" s="7"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7"/>
+    </row>
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B97" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M97" s="7"/>
+      <c r="N97" s="7"/>
+      <c r="O97" s="7"/>
+      <c r="P97" s="7"/>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B98" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="7"/>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B99" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
+      <c r="O99" s="7"/>
+      <c r="P99" s="7"/>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B100" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M100" s="7"/>
+      <c r="N100" s="7"/>
+      <c r="O100" s="7"/>
+      <c r="P100" s="7"/>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B101" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+      <c r="P101" s="7"/>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B102" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M102" s="7"/>
+      <c r="N102" s="7"/>
+      <c r="O102" s="7"/>
+      <c r="P102" s="7"/>
+    </row>
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B103" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M103" s="7"/>
+      <c r="N103" s="7"/>
+      <c r="O103" s="7"/>
+      <c r="P103" s="7"/>
+    </row>
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B104" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M104" s="7"/>
+      <c r="N104" s="7"/>
+      <c r="O104" s="7"/>
+      <c r="P104" s="7"/>
+    </row>
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B105" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M105" s="7"/>
+      <c r="N105" s="7"/>
+      <c r="O105" s="7"/>
+      <c r="P105" s="7"/>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B106" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M106" s="7"/>
+      <c r="N106" s="7"/>
+      <c r="O106" s="7"/>
+      <c r="P106" s="7"/>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B107" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M107" s="7"/>
+      <c r="N107" s="7"/>
+      <c r="O107" s="7"/>
+      <c r="P107" s="7"/>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B108" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I108" s="7"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M108" s="7"/>
+      <c r="N108" s="7"/>
+      <c r="O108" s="7"/>
+      <c r="P108" s="7"/>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B109" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M109" s="7"/>
+      <c r="N109" s="7"/>
+      <c r="O109" s="7"/>
+      <c r="P109" s="7"/>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B110" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="7"/>
+      <c r="K110" s="7"/>
+      <c r="L110" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M110" s="7"/>
+      <c r="N110" s="7"/>
+      <c r="O110" s="7"/>
+      <c r="P110" s="7"/>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B111" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="7"/>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B112" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M112" s="7"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="7"/>
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B113" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="7"/>
+      <c r="P113" s="7"/>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B114" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M114" s="7"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+    </row>
+    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B115" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="7"/>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M115" s="7"/>
+      <c r="N115" s="7"/>
+      <c r="O115" s="7"/>
+      <c r="P115" s="7"/>
+    </row>
+    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B116" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I116" s="7"/>
+      <c r="J116" s="7"/>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M116" s="7"/>
+      <c r="N116" s="7"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="7"/>
+    </row>
+    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B117" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="7"/>
+      <c r="K117" s="7"/>
+      <c r="L117" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M117" s="7"/>
+      <c r="N117" s="7"/>
+      <c r="O117" s="7"/>
+      <c r="P117" s="7"/>
+    </row>
+    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B118" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K118" s="7"/>
+      <c r="L118" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M118" s="7"/>
+      <c r="N118" s="7"/>
+      <c r="O118" s="7"/>
+      <c r="P118" s="7"/>
+    </row>
+    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B119" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+    </row>
+    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B120" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="K120" s="7"/>
+      <c r="L120" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M120" s="7"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="7"/>
+      <c r="P120" s="7"/>
+    </row>
+    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B121" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M121" s="7"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="7"/>
+      <c r="P121" s="7"/>
+    </row>
+    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B122" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
+      <c r="K122" s="7"/>
+      <c r="L122" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M122" s="7"/>
+      <c r="N122" s="7"/>
+      <c r="O122" s="7"/>
+      <c r="P122" s="7"/>
+    </row>
+    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B123" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="7"/>
+      <c r="K123" s="7"/>
+      <c r="L123" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M123" s="7"/>
+      <c r="N123" s="7"/>
+      <c r="O123" s="7"/>
+      <c r="P123" s="7"/>
+    </row>
+    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B124" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="7"/>
+      <c r="K124" s="7"/>
+      <c r="L124" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M124" s="7"/>
+      <c r="N124" s="7"/>
+      <c r="O124" s="7"/>
+      <c r="P124" s="7"/>
+    </row>
+    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B125" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="I125" s="7"/>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M125" s="7"/>
+      <c r="N125" s="7"/>
+      <c r="O125" s="7"/>
+      <c r="P125" s="7"/>
+    </row>
+    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B126" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="7"/>
+      <c r="K126" s="7"/>
+      <c r="L126" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M126" s="7"/>
+      <c r="N126" s="7"/>
+      <c r="O126" s="7"/>
+      <c r="P126" s="7"/>
+    </row>
+    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B127" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="I127" s="7"/>
+      <c r="J127" s="7"/>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M127" s="7"/>
+      <c r="N127" s="7"/>
+      <c r="O127" s="7"/>
+      <c r="P127" s="7"/>
+    </row>
+    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B128" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="F128" s="7"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="7"/>
+      <c r="J128" s="7"/>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M128" s="7"/>
+      <c r="N128" s="7"/>
+      <c r="O128" s="7"/>
+      <c r="P128" s="7"/>
+    </row>
+    <row r="129" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B129" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I129" s="7"/>
+      <c r="J129" s="7"/>
+      <c r="K129" s="7"/>
+      <c r="L129" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M129" s="7"/>
+      <c r="N129" s="7"/>
+      <c r="O129" s="7"/>
+      <c r="P129" s="7"/>
+    </row>
+    <row r="130" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B130" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="7"/>
+      <c r="K130" s="7"/>
+      <c r="L130" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M130" s="7"/>
+      <c r="N130" s="7"/>
+      <c r="O130" s="7"/>
+      <c r="P130" s="7"/>
+    </row>
+    <row r="131" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B131" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I131" s="7"/>
+      <c r="J131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M131" s="7"/>
+      <c r="N131" s="7"/>
+      <c r="O131" s="7"/>
+      <c r="P131" s="7"/>
+    </row>
+    <row r="132" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B132" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="7"/>
+      <c r="K132" s="7"/>
+      <c r="L132" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M132" s="7"/>
+      <c r="N132" s="7"/>
+      <c r="O132" s="7"/>
+      <c r="P132" s="7"/>
+    </row>
+    <row r="133" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B133" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I133" s="7"/>
+      <c r="J133" s="7"/>
+      <c r="K133" s="7"/>
+      <c r="L133" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M133" s="7"/>
+      <c r="N133" s="7"/>
+      <c r="O133" s="7"/>
+      <c r="P133" s="7"/>
+    </row>
+    <row r="134" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B134" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="7"/>
+      <c r="K134" s="7"/>
+      <c r="L134" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M134" s="7"/>
+      <c r="N134" s="7"/>
+      <c r="O134" s="7"/>
+      <c r="P134" s="7"/>
+    </row>
+    <row r="135" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B135" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="I135" s="7"/>
+      <c r="J135" s="7"/>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M135" s="7"/>
+      <c r="N135" s="7"/>
+      <c r="O135" s="7"/>
+      <c r="P135" s="7"/>
+    </row>
+    <row r="136" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B136" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="7"/>
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N136" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O136" s="7"/>
+      <c r="P136" s="7"/>
+    </row>
+    <row r="137" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B137" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M137" s="7"/>
+      <c r="N137" s="7"/>
+      <c r="O137" s="7"/>
+      <c r="P137" s="7"/>
+    </row>
+    <row r="138" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B138" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7"/>
+      <c r="N138" s="7"/>
+      <c r="O138" s="7"/>
+      <c r="P138" s="7"/>
+    </row>
+    <row r="139" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B139" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J139" s="7"/>
+      <c r="K139" s="7"/>
+      <c r="L139" s="7"/>
+      <c r="M139" s="7"/>
+      <c r="N139" s="7"/>
+      <c r="O139" s="7"/>
+      <c r="P139" s="7" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B140" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="I140" s="7"/>
+      <c r="J140" s="7"/>
+      <c r="K140" s="7"/>
+      <c r="L140" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M140" s="7"/>
+      <c r="N140" s="7"/>
+      <c r="O140" s="7"/>
+      <c r="P140" s="7"/>
+    </row>
+    <row r="141" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B141" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I141" s="7"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="7"/>
+      <c r="L141" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M141" s="7"/>
+      <c r="N141" s="7"/>
+      <c r="O141" s="7"/>
+      <c r="P141" s="7"/>
+    </row>
+    <row r="142" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B142" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
+      <c r="K142" s="7"/>
+      <c r="L142" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M142" s="7"/>
+      <c r="N142" s="7"/>
+      <c r="O142" s="7"/>
+      <c r="P142" s="7"/>
+    </row>
+    <row r="143" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B143" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="7"/>
+      <c r="K143" s="7"/>
+      <c r="L143" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M143" s="7"/>
+      <c r="N143" s="7"/>
+      <c r="O143" s="7"/>
+      <c r="P143" s="7"/>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B144" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="7"/>
+      <c r="K144" s="7"/>
+      <c r="L144" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M144" s="7"/>
+      <c r="N144" s="7"/>
+      <c r="O144" s="7"/>
+      <c r="P144" s="7"/>
+    </row>
+    <row r="145" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B145" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I145" s="7"/>
+      <c r="J145" s="7"/>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M145" s="7"/>
+      <c r="N145" s="7"/>
+      <c r="O145" s="7"/>
+      <c r="P145" s="7"/>
+    </row>
+    <row r="146" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B146" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
+      <c r="K146" s="7"/>
+      <c r="L146" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M146" s="7"/>
+      <c r="N146" s="7"/>
+      <c r="O146" s="7"/>
+      <c r="P146" s="7"/>
+    </row>
+    <row r="147" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B147" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="7"/>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M147" s="7"/>
+      <c r="N147" s="7"/>
+      <c r="O147" s="7"/>
+      <c r="P147" s="7"/>
+    </row>
+    <row r="148" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B148" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
+    </row>
+    <row r="149" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B149" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+      <c r="M149" s="7"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="7"/>
+      <c r="P149" s="7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="150" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B150" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="I150" s="7"/>
+      <c r="J150" s="7"/>
+      <c r="K150" s="7"/>
+      <c r="L150" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M150" s="7"/>
+      <c r="N150" s="7"/>
+      <c r="O150" s="7"/>
+      <c r="P150" s="7"/>
+    </row>
+    <row r="151" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B151" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="7"/>
+      <c r="K151" s="7"/>
+      <c r="L151" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="M151" s="7"/>
+      <c r="N151" s="7"/>
+      <c r="O151" s="7"/>
+      <c r="P151" s="7"/>
+    </row>
+    <row r="152" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B152" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J152" s="7"/>
+      <c r="K152" s="7"/>
+      <c r="L152" s="7"/>
+      <c r="M152" s="7"/>
+      <c r="N152" s="7"/>
+      <c r="O152" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P152" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -1985,94 +6971,186 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0AC287-6B30-491F-A320-ECD650B57881}">
-  <dimension ref="B2:P7"/>
+  <dimension ref="B2:P14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
         <v>74</v>
       </c>
-      <c r="G2" t="s">
-        <v>77</v>
-      </c>
       <c r="M2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
         <v>75</v>
       </c>
-      <c r="G3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" t="s">
-        <v>78</v>
-      </c>
       <c r="M3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" t="s">
         <v>76</v>
       </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>79</v>
       </c>
-      <c r="M4" t="s">
-        <v>82</v>
-      </c>
       <c r="P4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" t="s">
         <v>90</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>91</v>
       </c>
-      <c r="G5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" t="s">
-        <v>94</v>
-      </c>
       <c r="M5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" t="s">
         <v>84</v>
       </c>
-      <c r="P5" t="s">
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="M6" t="s">
+      <c r="P7" t="s">
         <v>86</v>
       </c>
-      <c r="P6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="M7" t="s">
-        <v>88</v>
-      </c>
-      <c r="P7" t="s">
-        <v>89</v>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" t="s">
+        <v>171</v>
+      </c>
+      <c r="M8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
+        <v>233</v>
+      </c>
+      <c r="M9" t="s">
+        <v>161</v>
+      </c>
+      <c r="P9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>317</v>
+      </c>
+      <c r="E13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>324</v>
+      </c>
+      <c r="E14" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2088,122 +7166,122 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
@@ -2211,7 +7289,7 @@
         <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
@@ -2219,81 +7297,232 @@
         <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>163</v>
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAFF6E4-78A0-4059-AA76-1F2F07C1CB1A}">
+  <dimension ref="B2:F17"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E731F8F-826B-4BDA-A4FF-B3EA5F72EC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B958C6D-F516-4225-9C51-1D508DA9120C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="30375" windowHeight="15345" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="30375" windowHeight="15345" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,280 +46,280 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="497">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>** 스크립트에서 사용하는 엘리먼트와 용도를 설명하기 위해서 제작되었습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>** 되도록이면 TYPE 별로 사용하는 엘리먼트를 선형으로 묶어놨지만, 각 TYPE 은 복수의 엘리먼트를 공유하는 경우가 있으니, 완전 선형 구조가 아닐 경우도 있습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Script Element Line</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Text</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>CG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Position</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Animation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Voice</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Effect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Duration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SpeakerType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Track</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Key</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>대사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>보이스 키</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>스파인 키</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>위치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>애니메이션</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이펙트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이펙트 수치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이펙트 시간</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>화자 타입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>후유코</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>~~~</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>s001001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fuyuko_normal_9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>wide_left</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>wait3 face_anger</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>zoom</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>파일 키</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>볼륨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BGM_nanndesyou</t>
   </si>
   <si>
     <t>BGM/SE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이미지 키</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>줌인 기준점</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>줌인 배율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>bg_hikaesitu</t>
   </si>
   <si>
     <t>TRANSITION</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>트랜지션 종류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>wipe_left</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>se_wipe_out|se_wipe_in</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 스파인 키는 Unity/CGManager/Spine Entries 딕셔너리 내부의 Key값을 의미합니다. SpineObject 명과 다르게 등록해도 되지만, 되도록이면 맞추는 것을 추천드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>(SpineObject의 명명법은 아이돌명_의상타입_차수이며, SSR 이외의 Spine은 등급_차수, 특수 의상은 임의 명명을 기본 규칙으로 합니다.)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 위치는 3분할과 5분할로 구분되며, 각각 left/center/right, wide_far_left/wide_left/wide_center/wide_right/wide_far_right로 구분합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>(CGManager의 Awake()에서 Dict를 구성하므로, 변경 시 이 부분을 참고 부탁드립니다.)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 이펙트는 현재 Zoom 기능만 지원하며, Value와 Duration의 서브 값을 가집니다. 미입력 시 둘 다 기본값인 1이 적용됩니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 애니메이션은 기본적으로 멀티 트랙 기능을 지원하며, 총 4개의 트랙으로 구성되어 있습니다. Base/Face/Lip/Arm으로 구성되어 있으며, 구분자는 공백 쉼표 모두 사용 가능합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* BGM과SE는 타입만 다르고 엘리멘트는 동일합니다. 파일 명의 시작만 BGM_/SE_ 규칙에 맞게 작성해주시면 됩니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 현재까지 BGM을 멈추는 기능은 따로 없는데, 필요 시 추후 구현합니다. 새로운 BGM을 세팅하면 기존 BGM이 자동으로 종료됩니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* BG 이펙트의 종류는 Zoom/Flashback을 지원합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* Zoom 이펙트의 기준점은 키패드를 기준으로 1~9까지의 숫자가 방향을 의미합니다. 디폴트는 5입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* Flashback 이펙트는 회상용 이펙트입니다. BG 교체 시 자동으로 해제됩니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* Transition의 종류는 Fade/Iris/Wipe_left/normal을 지원합니다. Fade/Iris는 기본적으로 out후 in까지 자동으로 진행됩니다. normal은 별도의 트랜지션 없이 바로 전환하는 기능입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* SE는 1개 혹은 2개 사용이 가능하며, 2개 입력 시에는 | 구분자를 사용합니다. out/in 시에 각각 출력되며, 없으면 출력되지 않습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_surp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>skill2 face_sad</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait2 face_serious lip_sad</t>
@@ -329,85 +329,85 @@
   </si>
   <si>
     <t>* 마유즈미 후유코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진심으로 싫음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진지한 무표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>* 이즈미 메이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>살짝 놀람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>걱정? 진지? 조금 애매한 표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아사히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>* 세리자와 아사히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>sad2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>실망</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>think1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>고민/궁금</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>skill1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>밝게 웃음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>anger1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>귀엽게 토라짐</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_smile lip_bitter_smile</t>
   </si>
   <si>
     <t>곤란한 웃음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>프로듀서</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_surp lip_surp</t>
   </si>
   <si>
     <t>동작 없이 놀람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
@@ -423,195 +423,195 @@
   </si>
   <si>
     <t>smile3 lip_wait</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>두근두근 (Lip Wait으로 해야 이빨 안보임)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>28명을 매칭해야 되는데… 개수가 부족하다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>일루미네</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>안티카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>마노</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>히오리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메구루</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>코가네</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>마미미</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>키리코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>사쿠야</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>유이카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>알스메</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>치유키</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아마나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>텐카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>방클걸</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>카호</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>쥬리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>린제</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>치요코</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나츠하</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스트레이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>녹칠</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>토오루</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>마도카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>코이토</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>히나나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>시즈</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>미코토</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>니치카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>코메틱</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하루키</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>루카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메탄</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>즌다몬</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아오야마 류세이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>유카</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>미타마</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>토바리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>앙코몬?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>츠루기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>비 &gt; 츠요츠요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>비슷한거같기도하고?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>키티탄</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>No7</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SE</t>
@@ -633,132 +633,132 @@
   </si>
   <si>
     <t>wait1 face_serious lip_anger2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진지하게 이야기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>left</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>right</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>lip_surp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아사히는 대부분 움직이는 게 없어서 surp가 거의 무표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>center</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait4 lip_anger</t>
   </si>
   <si>
     <t>한숨 쉬며 도리도리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait3 face_sad lip_anger2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>슬픈 표정으로 이야기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_serious lip_surp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진지한 표정으로 이야기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>none</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>zoom</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>1.5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait4</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>웃는 입 대신 정색</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>shrug</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>어깨 으쓱</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>s001074</t>
   </si>
   <si>
     <t>시리어스</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>こころのいろは</t>
   </si>
   <si>
     <t>센치</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>雨音に寄り添う</t>
   </si>
   <si>
     <t>굉장히 가라앉은 시리어스</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>呼吸の温度</t>
   </si>
   <si>
     <t>에모이한 저녁</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>街灯りで照らされて</t>
   </si>
   <si>
     <t>슬픔</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>88つの手触り</t>
   </si>
   <si>
     <t>긴박함</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>通過していく光の意味を</t>
@@ -771,665 +771,665 @@
   </si>
   <si>
     <t>차분한 밤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>차분함 카페</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ロー・ポジション</t>
   </si>
   <si>
     <t>과거회상같은 차분함</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후일담같은? 다음 날 아침</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나나쿠사 니치카 야쿠모 나미</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>재즈틱한 차분함</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>긴박한 액션</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>レッツ☆忍び足</t>
   </si>
   <si>
     <t>샤니P 갈등의 곡</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>おかえり、ギター</t>
   </si>
   <si>
     <t>나른한 일상</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>엉뚱한 일상</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0.2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0.3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wipe_left</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BG</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bg_room_fuyuko</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하아…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>TRANSITION</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>normal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bg_phone</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[스트레이라이트는 이어달리기에 나가는 걸로 결정됐어.]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[다들 걱정되는 부분도 있겠지만, 최선을 다하면 좋은 결과가 있을 거라고 생각해.]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[네.]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[OK~]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>최선을 다하면, 말이지…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SE</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bg_hikaesitu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>flashback</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그러게, 괜히 폼 같은 걸 잡아서…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>fuyuko_homewear</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>잠깐 운동 갔다 올게요.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>fuyuko_sports_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait2 face_serious</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코의 엄마</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아침에 운동 갔다 왔잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이건 조금 다른 거.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>저녁 전에는 돌아와야 한다?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>7시 전에는 돌아올거야.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>다치지 말고~</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>다녀오겠습니다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_serious</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>무표정으로 눈치챔</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>se_phone_vibe</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아, 후유코. 잠시 괜찮아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_close lip_smile</t>
   </si>
   <si>
     <t>wait1 face_close lip_smile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>눈 감고 농담</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>농담이야. 진지하게 받아들이지 마.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>별 내용은 아니니까, 후유코가 불편하다면…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>농담이라고 했잖아. 용건이나 말 해.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>용건이 있는 건 아니고, 달리기 연습은 잘 되고 있나 해서.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>너… 감이 너무 좋아서 기분 나빠.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하하, 후유코는 하기 싫다고 말은 하지만, 분명 보이지 않는 곳에서 노력하고 있을 테니까.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>방금 거, 칭찬한 거 아니거든?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>지금 이런 모습을 팬들이 볼 수 있으면, 더욱 좋아할텐데 말이야.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하아? 절대 싫거든.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>너, 후유가 지금까지 쌓아온 이미지를 뭐라고 생각하는 거야…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>물론 그건 알지만, 프로듀서 입장에서는 아쉽다고 할까…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>용건 끝나셨으면 끊을게요, 프로듀서 님?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>smile1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아, 미안. 그럼 마지막으로…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응, 뭔데.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코는 이미 충분히 열심히 하고 있으니까.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가끔은 자신에게 솔직해져도 된다고 생각해.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아, 물론 후유코의 생각이나 판단에 대해서는 나도 동의하고 있고…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>너도 바보네.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>너, 후유가 그걸 모르고 있을 것 같아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응. 그렇다면 안심이야.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>끊을게. 얼마만에 얻은 주말인데, 업무 전화에 설교까지…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>확 사장님한테 일러버릴까보다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>안 해. 후유, 다시 연습하러 갈 거니까.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응. 무슨 일 생기거나 하면 바로 연락 줘.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>네 네~</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>사람들이 보고 싶어하는 건, 항상 완벽한 모습 뿐이 아니란 말이지…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>… 하지만 그런 걸로는, 후유가 납득 못 한다고.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하아… 하아…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>슬슬 돌아가야…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>벌써 시간이 이렇게…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[후유코쨩, 잠깐 통화 괜찮아?]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유, 언제부터 이렇게 인기 만점이 됐는지 모르겠네.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아, 후유코쨩!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응, 무슨 일이야?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그… 하고 싶은 말이 있어서!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>뭔데?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>저번에 후유코쨩이랑 있을 때, 후유코쨩이 해준 이야기 말이야…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>완벽하지 않은 모습을 보여주기 싫다는 이야기?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응. 근데 결국 이어달리기 나가게 돼서…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나, 열심히 생각해 봤어.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>내가 할 수 있는 게 뭘까 하고.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나는 후유코쨩의 마음도 이해하고 있고, 아사히쨩이 하고 싶다면 같이 하고 싶다고도 생각하니까.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>어떻게 하면 해결할 수 있을까, 하고.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(그런 거, 그냥 후유의 고집을 뿐인데.)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(메이, 네가 고민하고 해결해야 할 이유같은 건 조금도…)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>근데, 역시 모르겠더라고!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메이, 너 말이야…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아하하, 마법같이 짜잔~ 하고 해결할 방법같은 거, 나한테는 안 떠오르더라고</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그래서 말이야,</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그냥 내가 할 수 있는 일을 하기로 했어!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>놀람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>할 수 있는 일?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아사히쨩은 이어달리기에서 1등을 하고 싶은 거고,</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코쨩은 팬들 앞에서 진심으로 달리는 모습을 보이는 게 싫은 거잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>뭐, 완벽히 그렇다는 건 아니지만…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼 엄~청 빠르게 달리면 된다는 거잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메이, 너…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_sad lip_bitter_smile</t>
   </si>
   <si>
     <t>wait1 face_sad lip_bitter_smile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>감동받은 표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그래서, 사실 지금 달리기 연습하는 중이거든!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>남은 2주동안 매일매일 달리면 빨라지지 않을까?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그렇네…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대박인게, 오늘 하루 연습했는데도 왠지 엄청 빨라진 것 같은 기분이…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메이.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코쨩?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>역시 너도 바보네.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>엣, 어째서?!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>네가 그렇게 이야기하면 후유가, '알겠어. 내 몫까지 죽을 힘을 다해서 달려줘.' 할 줄 알았어?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아하하, 그것도 그렇네!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그래도…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>고마워.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그러고 보니, 후유코쨩은 지금 뭐 하고 있었어?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_close3 lip_smile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>눈 감고 웃음 (곤란)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>… 그냥, 잠깐 바람 쐬러 나왔어.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그렇구나… 아!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>메이?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>내일 라디오 QNA 쓰는 거 까먹고 있었다!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>질렸다는 표정</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_jito lip_smile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>한가롭게 달리기나 할 때가 아니잖아…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진심 큰일날 뻔 했다... 그럼, 이만 끊을게 후유코쨩!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>작가님이 불쌍하니까, 빨리 해서 보내.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>응! 후유코쨩!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>또 뭔데?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>저녁 맛있게 먹어!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait1 face_smile lip_smile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>… 메이 너도.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>우리는 한 팀이니까!</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>한 팀이니까…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>아사히, 왜 그렇게 1등을 하고 싶어하는 거야?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>wait2 lip_sad</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>fuyuko_normal_9</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>asahi_normal_3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코쨩은 1등하고 싶지 않은 검까?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그게 왜 그렇게 되는데…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유도 가능하다면 1등을 하는 게 좋다고 생각해.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하지만 그렇다고 해서, 모든 것에서 1등을 해야 할 필요는 없잖아?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>1등을 하는 건 최강이라는 검다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그리고 스트레이라이트는 항상 최강을 목표로 함다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그러니까, 저는 항상 1등을 하고 싶슴다. 스트레이라이트니까요.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>진짜, 후유의 주위에는 바보들 뿐이네.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이러다가, 바보가 옮아 버리겠어.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>미안. 오랜만에 얻은 휴일인데…</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴일에 업무 전화가 왔다는 것만 빼면 괜찮아.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하하, 그것만큼은 봐 줘.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002003</t>
   </si>
   <si>
     <t>S002002</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002004</t>
@@ -1442,11 +1442,11 @@
   </si>
   <si>
     <t>S002007</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002008</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002009</t>
@@ -1468,14 +1468,14 @@
   </si>
   <si>
     <t>S002015</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002025</t>
   </si>
   <si>
     <t>S002016</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002017</t>
@@ -1566,47 +1566,47 @@
   </si>
   <si>
     <t>S002048</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002049</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002050</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002051</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002052</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002053</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>후유코도 이미 알고 있겠지만, 사람들이 보고 싶어하는 건, 항상 완벽한 모습 뿐이 아니라는 것</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>그것만은 잊지 말아줬으면 해.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002034</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002054</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002055</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002056</t>
@@ -1754,11 +1754,11 @@
   </si>
   <si>
     <t>S002104</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002105</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002106</t>
@@ -1783,15 +1783,15 @@
   </si>
   <si>
     <t>S002113</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>S002114</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bg_living_fuyuko</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bg_hasisita_day</t>
@@ -1816,19 +1816,107 @@
   </si>
   <si>
     <t>BGM_77</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debug Key</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PageUp/PageDown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음/이전 씬을 로드할 수 있는 기능입니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 보이스 키 값도 동시 출력이 가능하며, 구분자는 공백 쉼표 모두 사용 가능합니다. CGGroup 기능과 함께 사용되는 기능입니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGGROUP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Straylight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_normal_3</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_surp</t>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_normal_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001001 s001002 s001003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* CG를 묶어서 CGGroup으로 만들어서 출력하는 기능을 지원합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 그룹에 포함될 CG를 CGGroup 타입으로 하나씩 추가하고, 스파인과 위치, 애니메이션을 지정하여 추가합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 그룹명이 같으면 해당 CGGroup에 추가되며, 다를 경우에도 Dict에 저장되는 방식으로 추가가 가능합니다. (최대 5명)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* TEXT 타입의 CG 엘리먼트에 스파인 키 대신 CGGroup의 그룹명을 지정하여 출력이 가능합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 이 때, VoiceKey에 복수의 대사를 지정하여 동시에 출력하는 것도 가능합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="넥슨Lv2고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -1893,6 +1981,14 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1927,45 +2023,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2380,7 +2485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16B93A-EFFA-4920-BD1E-220B301284F6}">
-  <dimension ref="B2:P38"/>
+  <dimension ref="B2:P60"/>
   <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="8.6640625" style="1"/>
@@ -2564,153 +2669,281 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B21" s="6" t="s">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N22" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N23" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="6" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6" t="s">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6" t="s">
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6" t="s">
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G29" s="1">
         <v>7</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J29" s="1">
         <v>1.5</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B34" s="6" t="s">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6" t="s">
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P38" s="6"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B42" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B44" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>478</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6961,7 +7194,7 @@
       <c r="P152" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -7154,7 +7387,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7375,7 +7608,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7526,7 +7759,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F5F161-7977-4D41-BAA5-DFEE1F459FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323DF7D-A18B-44A0-BFFE-C4CD47A3F4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51495" yWindow="7080" windowWidth="16410" windowHeight="14520" activeTab="2" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="579">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -318,9 +318,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait2 face_serious lip_sad</t>
-  </si>
-  <si>
     <t>wait1 face_jito lip_cry</t>
   </si>
   <si>
@@ -388,9 +385,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait1 face_smile lip_bitter_smile</t>
-  </si>
-  <si>
     <t>곤란한 웃음</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -412,9 +406,6 @@
     <t>후유코</t>
   </si>
   <si>
-    <t>fuyuko_idol_3</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -659,10 +650,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait1 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>진지한 표정으로 이야기</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -683,9 +670,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>s001074</t>
-  </si>
-  <si>
     <t>시리어스</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -822,279 +806,18 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>S002003</t>
-  </si>
-  <si>
-    <t>S002004</t>
-  </si>
-  <si>
-    <t>S002005</t>
-  </si>
-  <si>
-    <t>S002006</t>
-  </si>
-  <si>
-    <t>S002009</t>
-  </si>
-  <si>
-    <t>S002010</t>
-  </si>
-  <si>
-    <t>S002011</t>
-  </si>
-  <si>
-    <t>S002012</t>
-  </si>
-  <si>
-    <t>S002013</t>
-  </si>
-  <si>
-    <t>S002014</t>
-  </si>
-  <si>
-    <t>S002025</t>
-  </si>
-  <si>
-    <t>S002017</t>
-  </si>
-  <si>
-    <t>S002018</t>
-  </si>
-  <si>
-    <t>S002019</t>
-  </si>
-  <si>
-    <t>S002020</t>
-  </si>
-  <si>
-    <t>S002021</t>
-  </si>
-  <si>
-    <t>S002022</t>
-  </si>
-  <si>
-    <t>S002023</t>
-  </si>
-  <si>
-    <t>S002024</t>
-  </si>
-  <si>
-    <t>S002026</t>
-  </si>
-  <si>
-    <t>S002027</t>
-  </si>
-  <si>
-    <t>S002028</t>
-  </si>
-  <si>
-    <t>S002029</t>
-  </si>
-  <si>
-    <t>S002030</t>
-  </si>
-  <si>
-    <t>S002031</t>
-  </si>
-  <si>
-    <t>S002032</t>
-  </si>
-  <si>
-    <t>S002033</t>
-  </si>
-  <si>
-    <t>S002035</t>
-  </si>
-  <si>
     <t>S002036</t>
   </si>
   <si>
     <t>S002037</t>
   </si>
   <si>
-    <t>S002038</t>
-  </si>
-  <si>
-    <t>S002039</t>
-  </si>
-  <si>
-    <t>S002040</t>
-  </si>
-  <si>
-    <t>S002041</t>
-  </si>
-  <si>
-    <t>S002042</t>
-  </si>
-  <si>
-    <t>S002043</t>
-  </si>
-  <si>
-    <t>S002044</t>
-  </si>
-  <si>
-    <t>S002045</t>
-  </si>
-  <si>
-    <t>S002046</t>
-  </si>
-  <si>
-    <t>S002047</t>
-  </si>
-  <si>
-    <t>S002056</t>
-  </si>
-  <si>
-    <t>S002057</t>
-  </si>
-  <si>
-    <t>S002058</t>
-  </si>
-  <si>
-    <t>S002059</t>
-  </si>
-  <si>
-    <t>S002060</t>
-  </si>
-  <si>
-    <t>S002061</t>
-  </si>
-  <si>
-    <t>S002062</t>
-  </si>
-  <si>
-    <t>S002063</t>
-  </si>
-  <si>
-    <t>S002064</t>
-  </si>
-  <si>
-    <t>S002065</t>
-  </si>
-  <si>
-    <t>S002066</t>
-  </si>
-  <si>
-    <t>S002067</t>
-  </si>
-  <si>
-    <t>S002068</t>
-  </si>
-  <si>
-    <t>S002069</t>
-  </si>
-  <si>
-    <t>S002070</t>
-  </si>
-  <si>
-    <t>S002071</t>
-  </si>
-  <si>
-    <t>S002072</t>
-  </si>
-  <si>
-    <t>S002073</t>
-  </si>
-  <si>
-    <t>S002074</t>
-  </si>
-  <si>
-    <t>S002075</t>
-  </si>
-  <si>
-    <t>S002076</t>
-  </si>
-  <si>
     <t>S002077</t>
   </si>
   <si>
     <t>S002078</t>
   </si>
   <si>
-    <t>S002080</t>
-  </si>
-  <si>
-    <t>S002081</t>
-  </si>
-  <si>
-    <t>S002082</t>
-  </si>
-  <si>
-    <t>S002083</t>
-  </si>
-  <si>
-    <t>S002084</t>
-  </si>
-  <si>
-    <t>S002085</t>
-  </si>
-  <si>
-    <t>S002086</t>
-  </si>
-  <si>
-    <t>S002087</t>
-  </si>
-  <si>
-    <t>S002088</t>
-  </si>
-  <si>
-    <t>S002089</t>
-  </si>
-  <si>
-    <t>S002090</t>
-  </si>
-  <si>
-    <t>S002091</t>
-  </si>
-  <si>
-    <t>S002092</t>
-  </si>
-  <si>
-    <t>S002093</t>
-  </si>
-  <si>
-    <t>S002094</t>
-  </si>
-  <si>
-    <t>S002095</t>
-  </si>
-  <si>
-    <t>S002096</t>
-  </si>
-  <si>
-    <t>S002097</t>
-  </si>
-  <si>
-    <t>S002098</t>
-  </si>
-  <si>
-    <t>S002099</t>
-  </si>
-  <si>
-    <t>S002100</t>
-  </si>
-  <si>
-    <t>S002101</t>
-  </si>
-  <si>
-    <t>S002102</t>
-  </si>
-  <si>
-    <t>S002103</t>
-  </si>
-  <si>
-    <t>S002106</t>
-  </si>
-  <si>
-    <t>S002107</t>
-  </si>
-  <si>
-    <t>S002108</t>
-  </si>
-  <si>
-    <t>S002109</t>
-  </si>
-  <si>
     <t>S002110</t>
   </si>
   <si>
@@ -1108,18 +831,6 @@
   </si>
   <si>
     <t>bg_hasisita_sunset</t>
-  </si>
-  <si>
-    <t>se_footstep_slip</t>
-  </si>
-  <si>
-    <t>se_phone_long</t>
-  </si>
-  <si>
-    <t>se_phone_vibe</t>
-  </si>
-  <si>
-    <t>se_phone_short</t>
   </si>
   <si>
     <t>bg_car_sunset</t>
@@ -1298,12 +1009,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait3</t>
-  </si>
-  <si>
-    <t>wait4</t>
-  </si>
-  <si>
     <t>wait5</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1334,828 +1039,1191 @@
     <t>BG</t>
   </si>
   <si>
+    <t>프로듀서</t>
+  </si>
+  <si>
+    <t>아사히</t>
+  </si>
+  <si>
+    <t>메이</t>
+  </si>
+  <si>
+    <t>후유코는 이미 충분히 열심히 하고 있으니까.</t>
+  </si>
+  <si>
+    <t>가끔은 자신에게 솔직해져도 된다고 생각해.</t>
+  </si>
+  <si>
+    <t>하아… 하아…</t>
+  </si>
+  <si>
+    <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼\n엄~청 빠르게 달리면 된다는 거잖아?</t>
+  </si>
+  <si>
+    <t>우리는 한 팀이니까!</t>
+  </si>
+  <si>
+    <t>1등을 하는 건 최강이라는 검다.</t>
+  </si>
+  <si>
+    <t>그리고 스트레이라이트는 항상 최강을 목표로 함다.</t>
+  </si>
+  <si>
+    <t>그러니까, 저는 항상 1등을 하고 싶슴다. 스트레이라이트니까요.</t>
+  </si>
+  <si>
+    <t>fuyuko_sports_2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>flashback</t>
+  </si>
+  <si>
+    <t>wipe_left</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_cry</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫은 표정으로 한숨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱끼고 웃으며 농담</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_jito</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한쪽 팔 올리고 정색</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_smile lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_sad lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 올려서 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 벌리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 손 모아서 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱 끼고 아래 보기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 넓게 들고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 오른손 허리에 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 허리에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleep</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼팔 들고 들썩 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 좁게 들고 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 들고 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 들썩 후 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp2/3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀라서 들썩 (소/대)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 손가락 입에 가져다 대기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 가슴에 짚고 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>touch</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만지지마</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 앞으로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>why</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 갸우뚱 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_serious lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마따끄</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 머리 갸우뚱 후 절레절레</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 목 뒤 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1과 동일</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞에서 피스</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손만 허리 짚고 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 허리 위로 살짝 올리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 앞에 들썩 후 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 엉덩이 뒤로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>BREAK</t>
-  </si>
-  <si>
-    <t>프로듀서</t>
-  </si>
-  <si>
-    <t>아사히</t>
-  </si>
-  <si>
-    <t>메이</t>
-  </si>
-  <si>
-    <t>후유코의 엄마</t>
-  </si>
-  <si>
-    <t>하아…</t>
-  </si>
-  <si>
-    <t>[스트레이라이트는 이어달리기에 나가는 걸로 결정됐어.]</t>
-  </si>
-  <si>
-    <t>[다들 걱정되는 부분도 있겠지만,\n최선을 다하면 좋은 결과가 있을 거라고 생각해.]</t>
-  </si>
-  <si>
-    <t>[네.]</t>
-  </si>
-  <si>
-    <t>[OK~]</t>
-  </si>
-  <si>
-    <t>최선을 다하면, 말이지…</t>
-  </si>
-  <si>
-    <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
-  </si>
-  <si>
-    <t>그러게, 괜히 폼 같은 걸 잡아서…</t>
-  </si>
-  <si>
-    <t>잠깐 운동 갔다 올게요.</t>
-  </si>
-  <si>
-    <t>아침에 운동 갔다 왔잖아?</t>
-  </si>
-  <si>
-    <t>이건 조금 다른 거.</t>
-  </si>
-  <si>
-    <t>저녁 전에는 돌아와야 한다?</t>
-  </si>
-  <si>
-    <t>7시 전에는 돌아올거야.</t>
-  </si>
-  <si>
-    <t>다치지 말고~</t>
-  </si>
-  <si>
-    <t>다녀오겠습니다.</t>
-  </si>
-  <si>
-    <t>아.</t>
-  </si>
-  <si>
-    <t>아, 후유코. 잠시 괜찮아?</t>
-  </si>
-  <si>
-    <t>휴일에 업무 전화가 왔다는 것만 빼면 괜찮아.</t>
-  </si>
-  <si>
-    <t>미안. 오랜만에 얻은 휴일인데…</t>
-  </si>
-  <si>
-    <t>농담이야. 진지하게 받아들이지 마.</t>
-  </si>
-  <si>
-    <t>별 내용은 아니니까, 후유코가 불편하다면…</t>
-  </si>
-  <si>
-    <t>농담이라고 했잖아. 용건이나 말 해.</t>
-  </si>
-  <si>
-    <t>그냥, 달리기 연습은 잘 되고 있나 해서.</t>
-  </si>
-  <si>
-    <t>너… 가끔 감이 너무 좋아서 기분 나빠.</t>
-  </si>
-  <si>
-    <t>하하, 후유코는 하기 싫다고 말은 하지만,\n분명 보이지 않는 곳에서 노력하고 있을 테니까.</t>
-  </si>
-  <si>
-    <t>방금 거, 칭찬한 거 아니거든?</t>
-  </si>
-  <si>
-    <t>지금 이런 모습을 팬들이 볼 수 있으면, 더욱 좋아할텐데 말이야.</t>
-  </si>
-  <si>
-    <t>하아? 절대 싫거든.</t>
-  </si>
-  <si>
-    <t>너, 후유가 지금까지 쌓아온 이미지를 뭐라고 생각하는 거야…</t>
-  </si>
-  <si>
-    <t>물론 그건 알지만, 프로듀서 입장에서는 아쉽다고 할까…</t>
-  </si>
-  <si>
-    <t>용건 끝나셨으면 끊을게요, 프로듀서 님?</t>
-  </si>
-  <si>
-    <t>아, 미안. 그럼 마지막으로…</t>
-  </si>
-  <si>
-    <t>응, 뭔데.</t>
-  </si>
-  <si>
-    <t>후유코도 이미 알고 있겠지만, 사람들이 보고 싶어하는 건,\n항상 완벽한 모습 뿐이 아니라는 것</t>
-  </si>
-  <si>
-    <t>그것만은 잊지 말아줬으면 해.</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t>후유코는 이미 충분히 열심히 하고 있으니까.</t>
-  </si>
-  <si>
-    <t>가끔은 자신에게 솔직해져도 된다고 생각해.</t>
-  </si>
-  <si>
-    <t>아, 물론 후유코의 생각이나 판단에 대해서는 나도 동의하고 있고…</t>
-  </si>
-  <si>
-    <t>너도 바보네.</t>
-  </si>
-  <si>
-    <t>후유가 그걸 모르고 있을 것 같아?</t>
-  </si>
-  <si>
-    <t>응. 그렇다면 안심이야.</t>
-  </si>
-  <si>
-    <t>끊을게. 얼마만에 얻은 주말인데, 업무 전화에 설교까지…</t>
-  </si>
-  <si>
-    <t>확 사장님한테 일러버릴까보다.</t>
-  </si>
-  <si>
-    <t>하하, 그것만큼은 봐 줘.</t>
-  </si>
-  <si>
-    <t>후유, 다시 연습하러 갈 거니까.</t>
-  </si>
-  <si>
-    <t>응. 무슨 일 생기거나 하면 바로 연락 줘.</t>
-  </si>
-  <si>
-    <t>네 네~</t>
-  </si>
-  <si>
-    <t>사람들이 보고 싶어하는 건, 항상 완벽한 모습 뿐이 아니란 말이지…</t>
-  </si>
-  <si>
-    <t>… 하지만 그런 걸로는, 후유가 납득 못 한다고.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭠까?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유 때문에 1등 못해도 불평하지 마.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>상관 없슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 다 이길 거니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill3 face_serious lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 자신은 어디서 오는 지 몰라.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리들만 믿어, 후유코쨩!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩이 안 뛰고 걸어도 될 만큼 차이를 벌려줄게!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그건 역으로 다른 사람들 눈치 보이니까 그만 둬…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 face_jito</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 이어달리기에 출전하는 그룹들, 다 피지컬 좋기로 유명하니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 간단히 이길 수 있는 상대는 아니야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>에, 진심? 그럼 좀 위험한 거 아냐?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>객관적으로 봤을 때, 우리가 1등을 할 수 있을 확률이…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_rouka_run</t>
+  </si>
+  <si>
+    <t>잠깐, 아사히?!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐 다른 팀들 좀 보고 오겠슴다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하… 내가 따라가서 보고 올게.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 부탁할게.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>원래부터 목적은 두 사람을 돋보이게 하는 거였으니까…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유는 적당히 달리다가, 아사히한테 넘겨주면 돼.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1등같은 건…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>loop</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_zawa</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스터</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 그룹 대항 이어달리기!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>선수들 일제히 달려나가기 시작합니다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해설</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>코너를 지나면서 선두 그룹이 치고 나왔네요.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가장 앞에 있는 선수는…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트의 이즈미 메이!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>달리는 폼이 예사롭지 않네요.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 옆에서 바짝 쫓고 있는 ---선수.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 사람의 치열한 선두 싸움이 진행되고 있습니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>직선 코스에서 결착이 날 것 같은데요.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>말씀드리는 순간, 선두 그룹이 직선 코스에 진입!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 떨어진 곳에서 두번째 주자들이 몸을 푸는 모습이 보입니다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+  </si>
+  <si>
+    <t>팬</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이 님!!!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 조금…!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적당히 달리다가, 아사히한테 넘겨주면 되는데.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 face_close lip_cry</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 마지막 스퍼트!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이즈미 선수가 선두를 빼앗겼습니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 걸로 1등을 해도, 후유한테는 조금도 이득이…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashback</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아아, 정말.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>너희들 때문에,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>바보가 옮아 버렸잖아,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_smile lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_kansei</t>
+  </si>
+  <si>
+    <t>바통은 두 팀 모두 거의 동시에 넘겨받았습니다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두번째 주자 모두 달려나갑니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>선수들 모두 아주 필사적으로 달리네요.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>동료들과 팬들의 응원 소리 덕분에, 회장은 아주 열정적인 분위기입니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>말씀드리는 순간, 코너에 진입!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>(지금의 후유, 분명 귀엽지 않은 얼굴 하고 있어…)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>(그래도, 뭐 생각보다 차이가 나고 있지 않아서 다행이야.)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>(이대로 아사히한테 넘겨주기만 하면…)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유쨩!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>관객</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>야, 마유즈미 원래 저런 캐릭터였냐?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>관객 2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>평소 성격만 보면 저런 거 안 할것 같은데… 의외네.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 슬슬 직선 코스에 들어왔습니다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 주자의 뒷모습이 보이고 있습니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트가 뒤쳐져 있지만, 역전 불가능한 차이는 아닙니다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 교대 직전!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>선두가 먼저 교대했고, 그 다음으로…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히쨩, 미안…!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1 face_sad lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>격차가…!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>괜찮슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 정도면 충분하니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>하아… 하아…</t>
-  </si>
-  <si>
-    <t>슬슬 돌아가야…</t>
-  </si>
-  <si>
-    <t>벌써 시간이 이렇게…</t>
-  </si>
-  <si>
-    <t>[후유코쨩, 잠깐 통화 괜찮아?]</t>
-  </si>
-  <si>
-    <t>후유, 언제부터 이렇게 인기 만점이 됐는지 모르겠네.</t>
-  </si>
-  <si>
-    <t>아, 후유코쨩!</t>
-  </si>
-  <si>
-    <t>응, 무슨 일이야?</t>
-  </si>
-  <si>
-    <t>그… 하고 싶은 말이 있어서!</t>
-  </si>
-  <si>
-    <t>뭔데?</t>
-  </si>
-  <si>
-    <t>저번에 후유코쨩이랑 있을 때, 후유코쨩이 해준 이야기 말이야…</t>
-  </si>
-  <si>
-    <t>완벽하지 않은 모습을 보여주기 싫다는 이야기?</t>
-  </si>
-  <si>
-    <t>응. 근데 결국 이어달리기 나가게 돼서…</t>
-  </si>
-  <si>
-    <t>나, 열심히 생각해 봤어.</t>
-  </si>
-  <si>
-    <t>내가 할 수 있는 게 뭘까 하고.</t>
-  </si>
-  <si>
-    <t>나는 후유코쨩의 마음도 이해하고 있고,\n아사히쨩이 하고 싶다면 같이 하고 싶다고도 생각하니까.</t>
-  </si>
-  <si>
-    <t>어떻게 하면 해결할 수 있을까, 하고.</t>
-  </si>
-  <si>
-    <t>(그런 거, 그냥 후유의 고집을 뿐인데.)</t>
-  </si>
-  <si>
-    <t>(메이, 네가 고민하고 해결해야 할 이유같은 건 조금도…)</t>
-  </si>
-  <si>
-    <t>근데, 역시 모르겠더라고!</t>
-  </si>
-  <si>
-    <t>메이, 너 말이야…</t>
-  </si>
-  <si>
-    <t>아하하, 마법같이 짜잔~ 하고 해결할 방법같은 거,\n나한테는 안 떠오르더라고</t>
-  </si>
-  <si>
-    <t>그래서 말이야,</t>
-  </si>
-  <si>
-    <t>그냥 내가 할 수 있는 일을 하기로 했어!</t>
-  </si>
-  <si>
-    <t>할 수 있는 일?</t>
-  </si>
-  <si>
-    <t>아사히쨩은 이어달리기에서 1등을 하고 싶은 거잖아?</t>
-  </si>
-  <si>
-    <t>그리고 후유코쨩은 팬들 앞에서 진심으로 달리는 모습을 보이는 게 싫은 거고?</t>
-  </si>
-  <si>
-    <t>뭐, 완벽히 그렇다는 건 아니지만…</t>
-  </si>
-  <si>
-    <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼\n엄~청 빠르게 달리면 된다는 거잖아?</t>
-  </si>
-  <si>
-    <t>우리는 한 팀이니까!</t>
-  </si>
-  <si>
-    <t>그래서, 사실 지금 달리기 연습하는 중이거든!</t>
-  </si>
-  <si>
-    <t>남은 2주동안 매일매일 달리면 빨라지지 않을까?</t>
-  </si>
-  <si>
-    <t>그렇네…</t>
-  </si>
-  <si>
-    <t>대박인게, 오늘 하루 연습했는데도 왠지 엄청 빨라진 것 같은 기분이…</t>
-  </si>
-  <si>
-    <t>메이.</t>
-  </si>
-  <si>
-    <t>후유코쨩?</t>
-  </si>
-  <si>
-    <t>역시 너도 바보네.</t>
-  </si>
-  <si>
-    <t>엣, 어째서?!</t>
-  </si>
-  <si>
-    <t>네가 그렇게 이야기하면 후유가,\n'알겠어. 내 몫까지 죽을 힘을 다해서 달려줘.' 할 줄 알았어?</t>
-  </si>
-  <si>
-    <t>아하하, 그것도 그렇네!</t>
-  </si>
-  <si>
-    <t>그래도…</t>
-  </si>
-  <si>
-    <t>고마워.</t>
-  </si>
-  <si>
-    <t>그러고 보니, 후유코쨩은 지금 뭐 하고 있었어?</t>
-  </si>
-  <si>
-    <t>… 그냥, 잠깐 바람 쐬러 나왔어.</t>
-  </si>
-  <si>
-    <t>그렇구나… 아!</t>
-  </si>
-  <si>
-    <t>메이?</t>
-  </si>
-  <si>
-    <t>내일 라디오 QNA 쓰는 거 까먹고 있었다!</t>
-  </si>
-  <si>
-    <t>한가롭게 달리기나 할 때가 아니잖아…</t>
-  </si>
-  <si>
-    <t>진심 큰일날 뻔 했다... 그럼, 이만 끊을게 후유코쨩!</t>
-  </si>
-  <si>
-    <t>작가님이 불쌍하니까, 빨리 해서 보내.</t>
-  </si>
-  <si>
-    <t>응! 아, 후유코쨩!</t>
-  </si>
-  <si>
-    <t>또 뭔데?</t>
-  </si>
-  <si>
-    <t>저녁 맛있게 먹어!</t>
-  </si>
-  <si>
-    <t>… 메이 너도.</t>
-  </si>
-  <si>
-    <t>한 팀이니까…</t>
-  </si>
-  <si>
-    <t>아사히, 왜 그렇게 1등을 하고 싶어하는 거야?</t>
-  </si>
-  <si>
-    <t>후유코쨩은 1등하고 싶지 않은 검까?</t>
-  </si>
-  <si>
-    <t>그게 왜 그렇게 되는데…</t>
-  </si>
-  <si>
-    <t>후유도 가능하다면 1등을 하는 게 좋다고 생각해.</t>
-  </si>
-  <si>
-    <t>하지만 그렇다고 해서, 모든 것에서 1등을 해야 할 필요는 없잖아?</t>
-  </si>
-  <si>
-    <t>1등을 하는 건 최강이라는 검다.</t>
-  </si>
-  <si>
-    <t>그리고 스트레이라이트는 항상 최강을 목표로 함다.</t>
-  </si>
-  <si>
-    <t>그러니까, 저는 항상 1등을 하고 싶슴다. 스트레이라이트니까요.</t>
-  </si>
-  <si>
-    <t>진짜, 후유의 주위에는 바보들 뿐이네.</t>
-  </si>
-  <si>
-    <t>이러다가, 바보가 옮아 버리겠어.</t>
-  </si>
-  <si>
-    <t>S002001</t>
-  </si>
-  <si>
-    <t>S002002</t>
-  </si>
-  <si>
-    <t>S002007</t>
-  </si>
-  <si>
-    <t>S002008</t>
-  </si>
-  <si>
-    <t>S002015</t>
-  </si>
-  <si>
-    <t>S002016</t>
-  </si>
-  <si>
-    <t>S002034</t>
-  </si>
-  <si>
-    <t>S002048</t>
-  </si>
-  <si>
-    <t>S002049</t>
-  </si>
-  <si>
-    <t>S002050</t>
-  </si>
-  <si>
-    <t>S002051</t>
-  </si>
-  <si>
-    <t>S002052</t>
-  </si>
-  <si>
-    <t>S002053</t>
-  </si>
-  <si>
-    <t>S002054</t>
-  </si>
-  <si>
-    <t>S002055</t>
-  </si>
-  <si>
-    <t>S002104</t>
-  </si>
-  <si>
-    <t>S002105</t>
-  </si>
-  <si>
-    <t>S002113</t>
-  </si>
-  <si>
-    <t>S002114</t>
-  </si>
-  <si>
-    <t>fuyuko_homewear</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>fuyuko_sports_2</t>
-  </si>
-  <si>
-    <t>fuyuko_normal_9</t>
-  </si>
-  <si>
-    <t>center</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>left</t>
-  </si>
-  <si>
-    <t>wait2 face_serious</t>
-  </si>
-  <si>
-    <t>wait1 face_serious</t>
-  </si>
-  <si>
-    <t>wait2 lip_sad</t>
-  </si>
-  <si>
-    <t>normal</t>
-  </si>
-  <si>
-    <t>flashback</t>
-  </si>
-  <si>
-    <t>clean</t>
-  </si>
-  <si>
-    <t>zoom</t>
-  </si>
-  <si>
-    <t>wipe_left</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>BGM_77</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>bg_room_fuyuko</t>
-  </si>
-  <si>
-    <t>bg_phone</t>
-  </si>
-  <si>
-    <t>bg_living_fuyuko</t>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_cry</t>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>싫은 표정으로 한숨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱끼고 웃으며 농담</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_jito</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>한쪽 팔 올리고 정색</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_sad lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 올려서 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 벌리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 손 모아서 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱 끼고 아래 보기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shy1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 넓게 들고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 오른손 허리에 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 허리에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>sleep</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼팔 들고 들썩 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 좁게 들고 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 들고 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 들썩 후 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp2/3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>놀라서 들썩 (소/대)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 손가락 입에 가져다 대기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 가슴에 짚고 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>touch</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>만지지마</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤에서 앞으로</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>why</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 갸우뚱 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile2 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_close lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_jito lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug2 lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait2 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>think face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_sad lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>center</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug2 face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_jito lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_close lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>clean</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마따끄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 머리 갸우뚱 후 절레절레</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 목 뒤 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1과 동일</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞에서 피스</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손만 허리 짚고 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 허리 위로 살짝 올리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 앞에 들썩 후 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 엉덩이 뒤로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤는 맡길게, 아사히…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>eyeblink</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>fadeout</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>바통을 넘겨받은 스트레이라이트의 세리자와 아사히!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1등을 맹렬하게 추격!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 빠릅니다! 점점 차이가 줄어들고 있습니다!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1등 못하면 용서 안할거니까…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNS에서 후유코쨩이 좋은 얼굴을 하고 있다고 화제가 되고 있슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp4 face_serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하~ 열심히 달리길 잘 했네~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 왠지 열 받아.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도, 후유코쨩이 열심히 달려주지 않았다면 1등 못했을 테니까~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>진심 덕분에 살았어~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유의 목적은 애초에 1등하는 게 아니었긴 하지만…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito_lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐, 좋은 게 좋은 거려나…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile2 face_close3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 1등도 하고 좋은 반응도 얻었으니 다행이야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도, 간발의 차였슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩이 주말에 몰래 연습 안 했으면 졌을지도 모름다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>하? 아사히, 네가 그걸 어떻게…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp2 face_anger lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로듀서님이 전화로 알려줬슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩도 나름 열심히 하고 있으니까, 너무 그렇게…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 아사히…! 그건…!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로듀서 님~?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코, 들어 줘! 이건…!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>네, 전부 들어드릴 테니, 밖에서 이야기할까요~?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>네…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸네.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_serious lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_surp lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003001</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003002</t>
+  </si>
+  <si>
+    <t>S003003</t>
+  </si>
+  <si>
+    <t>S003004</t>
+  </si>
+  <si>
+    <t>S003005</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003006</t>
+  </si>
+  <si>
+    <t>S003007</t>
+  </si>
+  <si>
+    <t>S003008</t>
+  </si>
+  <si>
+    <t>S003009</t>
+  </si>
+  <si>
+    <t>S003010</t>
+  </si>
+  <si>
+    <t>S003011</t>
+  </si>
+  <si>
+    <t>S003012</t>
+  </si>
+  <si>
+    <t>S003013</t>
+  </si>
+  <si>
+    <t>S003014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003015</t>
+  </si>
+  <si>
+    <t>S003016</t>
+  </si>
+  <si>
+    <t>S003017</t>
+  </si>
+  <si>
+    <t>S003018</t>
+  </si>
+  <si>
+    <t>S003019</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003020</t>
+  </si>
+  <si>
+    <t>S003021</t>
+  </si>
+  <si>
+    <t>S003022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003023</t>
+  </si>
+  <si>
+    <t>S003024</t>
+  </si>
+  <si>
+    <t>S003025</t>
+  </si>
+  <si>
+    <t>S003026</t>
+  </si>
+  <si>
+    <t>S003027</t>
+  </si>
+  <si>
+    <t>S003028</t>
+  </si>
+  <si>
+    <t>S003029</t>
+  </si>
+  <si>
+    <t>S003030</t>
+  </si>
+  <si>
+    <t>S003031</t>
+  </si>
+  <si>
+    <t>S003032</t>
+  </si>
+  <si>
+    <t>S003033</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003034</t>
+  </si>
+  <si>
+    <t>S003035</t>
+  </si>
+  <si>
+    <t>S003036</t>
+  </si>
+  <si>
+    <t>S003037</t>
+  </si>
+  <si>
+    <t>S003038</t>
+  </si>
+  <si>
+    <t>S003039</t>
+  </si>
+  <si>
+    <t>S003040</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003041</t>
+  </si>
+  <si>
+    <t>S003043</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003044</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003045</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003047</t>
+  </si>
+  <si>
+    <t>S003048</t>
+  </si>
+  <si>
+    <t>S003049</t>
+  </si>
+  <si>
+    <t>S003050</t>
+  </si>
+  <si>
+    <t>S003052</t>
+  </si>
+  <si>
+    <t>S003053</t>
+  </si>
+  <si>
+    <t>S003054</t>
+  </si>
+  <si>
+    <t>S003055</t>
+  </si>
+  <si>
+    <t>S003056</t>
+  </si>
+  <si>
+    <t>S003057</t>
+  </si>
+  <si>
+    <t>S003058</t>
+  </si>
+  <si>
+    <t>S003059</t>
+  </si>
+  <si>
+    <t>S003061</t>
+  </si>
+  <si>
+    <t>S003062</t>
+  </si>
+  <si>
+    <t>S003063</t>
+  </si>
+  <si>
+    <t>S003064</t>
+  </si>
+  <si>
+    <t>S003067</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003068</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003069</t>
+  </si>
+  <si>
+    <t>S003070</t>
+  </si>
+  <si>
+    <t>S003071</t>
+  </si>
+  <si>
+    <t>S003072</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003073</t>
+  </si>
+  <si>
+    <t>S003074</t>
+  </si>
+  <si>
+    <t>S003075</t>
+  </si>
+  <si>
+    <t>S003076</t>
+  </si>
+  <si>
+    <t>S003077</t>
+  </si>
+  <si>
+    <t>S003078</t>
+  </si>
+  <si>
+    <t>S003079</t>
+  </si>
+  <si>
+    <t>S003080</t>
+  </si>
+  <si>
+    <t>S003081</t>
+  </si>
+  <si>
+    <t>S003082</t>
+  </si>
+  <si>
+    <t>S003083</t>
+  </si>
+  <si>
+    <t>S003084</t>
+  </si>
+  <si>
+    <t>S003085</t>
+  </si>
+  <si>
+    <t>S003086</t>
+  </si>
+  <si>
+    <t>S003087</t>
+  </si>
+  <si>
+    <t>S003088</t>
+  </si>
+  <si>
+    <t>S003089</t>
+  </si>
+  <si>
+    <t>S003090</t>
+  </si>
+  <si>
+    <t>S003091</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003092</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003093</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_101</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug2 face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>serious face_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_121</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 바보 같아.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트의 팬</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_80</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003042</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1 face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003046</t>
+  </si>
+  <si>
+    <t>S003051</t>
+  </si>
+  <si>
+    <t>S003060</t>
+  </si>
+  <si>
+    <t>S003065</t>
+  </si>
+  <si>
+    <t>S003066</t>
+  </si>
+  <si>
+    <t>wait2 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1 face_wait lip_smile</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2927,7 +2995,7 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>305</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -3077,10 +3145,10 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
-        <v>306</v>
+        <v>210</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>307</v>
+        <v>211</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>23</v>
@@ -3094,16 +3162,16 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>306</v>
+        <v>210</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -3111,36 +3179,36 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>306</v>
+        <v>210</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>309</v>
+        <v>213</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>310</v>
+        <v>214</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>306</v>
+        <v>210</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>313</v>
+        <v>217</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>315</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -3148,54 +3216,54 @@
         <v>19</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>316</v>
+        <v>220</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>318</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>321</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>322</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>302</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>304</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3275,7 +3343,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>354</v>
+        <v>257</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3287,18 +3355,16 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>513</v>
-      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>355</v>
+        <v>256</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3310,41 +3376,31 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="M4" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>378</v>
+      </c>
       <c r="O4" s="7"/>
-      <c r="P4" s="7" t="s">
-        <v>515</v>
-      </c>
+      <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="I5" s="7"/>
+        <v>338</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -3352,20 +3408,32 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>341</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -3373,20 +3441,32 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
-        <v>504</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -3394,46 +3474,60 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>345</v>
+      </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="L8" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="7" t="s">
-        <v>516</v>
-      </c>
+      <c r="P8" s="7"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>357</v>
+        <v>259</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>477</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7" t="s">
-        <v>511</v>
+        <v>91</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -3442,26 +3536,20 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>201</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
-        <v>511</v>
-      </c>
+      <c r="K10" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -3469,25 +3557,31 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>358</v>
+        <v>259</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+        <v>478</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>578</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7" t="s">
-        <v>511</v>
+        <v>91</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3496,25 +3590,31 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+        <v>479</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7" t="s">
-        <v>511</v>
+        <v>91</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3523,27 +3623,31 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>204</v>
+        <v>480</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -3552,43 +3656,58 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>481</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
-      <c r="K14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="L15" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -3596,20 +3715,32 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
-        <v>504</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="L16" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -3617,54 +3748,58 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="7" t="s">
-        <v>505</v>
-      </c>
+      <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="L17" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>163</v>
+        <v>485</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>347</v>
+        <v>317</v>
+      </c>
+      <c r="H18" t="s">
+        <v>304</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -3673,20 +3808,32 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7" t="s">
-        <v>504</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -3694,7 +3841,7 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>355</v>
+        <v>141</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -3702,20 +3849,20 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
+      <c r="I20" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="7" t="s">
-        <v>515</v>
-      </c>
+      <c r="P20" s="7"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -3724,67 +3871,71 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7" t="s">
-        <v>560</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
+      <c r="P21" s="7" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>519</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M22" s="7"/>
+      <c r="K22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7" t="s">
+        <v>364</v>
+      </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7" t="s">
-        <v>504</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
+      <c r="L23" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -3792,72 +3943,92 @@
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>488</v>
+      </c>
       <c r="F24" s="7"/>
-      <c r="G24" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="G24" s="7"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>509</v>
-      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="L24" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="7" t="s">
-        <v>515</v>
-      </c>
+      <c r="P24" s="7"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>279</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
-      <c r="K25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7" t="s">
-        <v>506</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H26" t="s">
+        <v>564</v>
+      </c>
+      <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
+      <c r="L26" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
@@ -3865,30 +4036,40 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7" t="s">
-        <v>146</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H27" t="s">
+        <v>275</v>
+      </c>
+      <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
+      <c r="L27" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
-      <c r="O27" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="O27" s="7"/>
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>355</v>
+        <v>140</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -3900,16 +4081,18 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="M28" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="O28" s="7"/>
-      <c r="P28" s="7" t="s">
-        <v>517</v>
-      </c>
+      <c r="P28" s="7"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>356</v>
+        <v>141</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -3918,7 +4101,7 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7" t="s">
-        <v>506</v>
+        <v>271</v>
       </c>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -3930,59 +4113,37 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>561</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
+      <c r="P30" s="7" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>205</v>
-      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="7" t="s">
-        <v>511</v>
-      </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
@@ -3990,31 +4151,25 @@
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>371</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>502</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -4023,16 +4178,16 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>372</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>207</v>
+        <v>493</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -4041,7 +4196,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7" t="s">
-        <v>511</v>
+        <v>91</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -4050,31 +4205,25 @@
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>373</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>501</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -4083,67 +4232,51 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>209</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
+      <c r="I35" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="7" t="s">
-        <v>511</v>
-      </c>
+      <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="O35" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>562</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
       <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
+      <c r="P36" s="7" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -4156,17 +4289,17 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7" t="s">
-        <v>147</v>
+        <v>565</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>94</v>
+        <v>378</v>
       </c>
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>144</v>
+        <v>375</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -4175,21 +4308,23 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>146</v>
+        <v>376</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="M38" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -4197,45 +4332,47 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
+      <c r="I39" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="7" t="s">
-        <v>295</v>
-      </c>
+      <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
-      <c r="K40" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="N40" s="7" t="s">
-        <v>514</v>
-      </c>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>356</v>
+        <v>141</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -4244,90 +4381,94 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>585</v>
+        <v>143</v>
       </c>
       <c r="J41" s="7"/>
-      <c r="K41" s="7" t="s">
-        <v>510</v>
-      </c>
+      <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
+      <c r="O41" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P41" s="7"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>496</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+        <v>411</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>363</v>
+      </c>
       <c r="K42" s="7"/>
-      <c r="L42" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
+      <c r="P42" s="7" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>496</v>
+      </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N43" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L43" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
       <c r="O43" s="7"/>
       <c r="P43" s="7"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>497</v>
+      </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
@@ -4335,16 +4476,16 @@
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4353,7 +4494,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4362,31 +4503,25 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>563</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -4395,16 +4530,16 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>213</v>
+        <v>500</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -4413,7 +4548,7 @@
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4422,31 +4557,25 @@
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>347</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4455,16 +4584,16 @@
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>215</v>
+        <v>502</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -4473,7 +4602,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4482,31 +4611,25 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>92</v>
+        <v>382</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>518</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4515,16 +4638,16 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>217</v>
+        <v>504</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -4533,7 +4656,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4542,31 +4665,25 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H52" t="s">
-        <v>523</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4575,26 +4692,20 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>219</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
+      <c r="I53" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
@@ -4602,59 +4713,39 @@
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+        <v>257</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
+      <c r="P54" s="7" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>220</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
+      <c r="I55" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
-      <c r="L55" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
@@ -4662,31 +4753,31 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>388</v>
+        <v>566</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>221</v>
+        <v>506</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>496</v>
+        <v>269</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>565</v>
+        <v>340</v>
+      </c>
+      <c r="H56" t="s">
+        <v>275</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
@@ -4695,25 +4786,27 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>92</v>
+        <v>567</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F57" s="7"/>
+        <v>507</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
@@ -4722,16 +4815,16 @@
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>357</v>
+        <v>567</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>223</v>
+        <v>508</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -4740,7 +4833,7 @@
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
@@ -4749,31 +4842,31 @@
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>224</v>
+        <v>509</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>496</v>
+        <v>269</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>337</v>
+        <v>340</v>
+      </c>
+      <c r="H59" t="s">
+        <v>397</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -4782,25 +4875,27 @@
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F60" s="7"/>
+        <v>510</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
       <c r="L60" s="7" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -4809,31 +4904,25 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>566</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -4842,25 +4931,31 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>357</v>
+        <v>90</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
+        <v>512</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H62" t="s">
+        <v>341</v>
+      </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7" t="s">
-        <v>499</v>
+        <v>91</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
@@ -4869,26 +4964,20 @@
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>481</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
+      <c r="I63" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
-      <c r="L63" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="L63" s="7"/>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -4896,86 +4985,66 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>346</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
-      <c r="L64" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L64" s="7"/>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
+      <c r="P64" s="7" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>229</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
+      <c r="I65" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="L65" s="7"/>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
+      <c r="P65" s="7" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>230</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
+      <c r="I66" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="K66" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -4983,16 +5052,16 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>357</v>
+        <v>258</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>399</v>
+        <v>261</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -5001,7 +5070,7 @@
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7" t="s">
-        <v>499</v>
+        <v>270</v>
       </c>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
@@ -5010,20 +5079,26 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
@@ -5031,32 +5106,20 @@
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="I69" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L69" s="7"/>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
@@ -5064,53 +5127,45 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>233</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
+      <c r="I70" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
-      <c r="L70" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L70" s="7"/>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
+      <c r="P70" s="7" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>234</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
+      <c r="I71" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="K71" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L71" s="7"/>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
@@ -5118,31 +5173,25 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>403</v>
+        <v>266</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>159</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
@@ -5151,27 +5200,25 @@
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>404</v>
+        <v>267</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
-      <c r="H73" s="7" t="s">
-        <v>563</v>
-      </c>
+      <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
@@ -5180,16 +5227,16 @@
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>357</v>
+        <v>259</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>405</v>
+        <v>268</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -5198,7 +5245,7 @@
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7" t="s">
-        <v>499</v>
+        <v>91</v>
       </c>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
@@ -5207,32 +5254,20 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="I75" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
-      <c r="L75" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
@@ -5240,59 +5275,45 @@
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>239</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="I76" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7" t="s">
-        <v>499</v>
-      </c>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
+      <c r="P76" s="7" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="I77" s="7"/>
+        <v>338</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="K77" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L77" s="7"/>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
@@ -5300,45 +5321,53 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N78" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L78" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>199</v>
+      </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
-        <v>506</v>
-      </c>
+      <c r="I79" s="7"/>
       <c r="J79" s="7"/>
-      <c r="K79" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
       <c r="O79" s="7"/>
@@ -5346,32 +5375,20 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="I80" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
-      <c r="L80" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L80" s="7"/>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
       <c r="O80" s="7"/>
@@ -5379,34 +5396,28 @@
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>483</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
+      <c r="P81" s="7" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -5414,22 +5425,22 @@
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
-      <c r="I82" s="7" t="s">
-        <v>146</v>
-      </c>
+      <c r="I82" s="7"/>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="M82" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="O82" s="7"/>
       <c r="P82" s="7"/>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5437,35 +5448,39 @@
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
+      <c r="I83" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="7" t="s">
-        <v>296</v>
-      </c>
+      <c r="P83" s="7"/>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>513</v>
+      </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="7" t="s">
-        <v>506</v>
-      </c>
+      <c r="I84" s="7"/>
       <c r="J84" s="7"/>
-      <c r="K84" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
       <c r="O84" s="7"/>
@@ -5473,25 +5488,31 @@
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
+        <v>514</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H85" t="s">
+        <v>244</v>
+      </c>
       <c r="I85" s="7"/>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
@@ -5500,25 +5521,29 @@
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
+        <v>316</v>
+      </c>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
@@ -5527,7 +5552,7 @@
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
-        <v>144</v>
+        <v>338</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -5535,9 +5560,7 @@
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
-      <c r="I87" s="7" t="s">
-        <v>504</v>
-      </c>
+      <c r="I87" s="7"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -5548,47 +5571,48 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
+      <c r="L88" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
-      <c r="P88" s="7" t="s">
-        <v>516</v>
-      </c>
+      <c r="P88" s="7"/>
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>486</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="K89" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="L89" s="7"/>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
       <c r="O89" s="7"/>
@@ -5596,25 +5620,31 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
+        <v>515</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H90" t="s">
+        <v>570</v>
+      </c>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
@@ -5623,7 +5653,7 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -5634,7 +5664,7 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7" t="s">
-        <v>510</v>
+        <v>348</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
@@ -5644,23 +5674,31 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
+        <v>409</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H92" t="s">
+        <v>410</v>
+      </c>
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
       <c r="L92" s="7" t="s">
-        <v>511</v>
+        <v>91</v>
       </c>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
@@ -5669,7 +5707,7 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>143</v>
+        <v>338</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -5680,21 +5718,17 @@
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
       <c r="K93" s="7" t="s">
-        <v>510</v>
+        <v>348</v>
       </c>
       <c r="L93" s="7"/>
-      <c r="M93" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="N93" s="7" t="s">
-        <v>514</v>
-      </c>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
       <c r="O93" s="7"/>
       <c r="P93" s="7"/>
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -5702,22 +5736,22 @@
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
-      <c r="I94" s="7" t="s">
-        <v>506</v>
-      </c>
+      <c r="I94" s="7"/>
       <c r="J94" s="7"/>
-      <c r="K94" s="7" t="s">
-        <v>510</v>
-      </c>
+      <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
+      <c r="N94" s="7" t="s">
+        <v>348</v>
+      </c>
       <c r="O94" s="7"/>
-      <c r="P94" s="7"/>
+      <c r="P94" s="7" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -5726,7 +5760,7 @@
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7" t="s">
-        <v>504</v>
+        <v>271</v>
       </c>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
@@ -5738,7 +5772,7 @@
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>355</v>
+        <v>257</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -5754,37 +5788,25 @@
       <c r="N96" s="7"/>
       <c r="O96" s="7"/>
       <c r="P96" s="7" t="s">
-        <v>296</v>
+        <v>392</v>
       </c>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I97" s="7"/>
+        <v>338</v>
+      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
-      <c r="L97" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
@@ -5792,43 +5814,53 @@
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>517</v>
+      </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N98" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L98" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
       <c r="O98" s="7"/>
       <c r="P98" s="7"/>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>571</v>
+      </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
-      <c r="K99" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
       <c r="O99" s="7"/>
@@ -5836,16 +5868,16 @@
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
@@ -5854,7 +5886,7 @@
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
@@ -5863,31 +5895,25 @@
     </row>
     <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>195</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -5896,16 +5922,16 @@
     </row>
     <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>242</v>
+        <v>520</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -5914,7 +5940,7 @@
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -5923,31 +5949,31 @@
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>419</v>
+        <v>263</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>496</v>
+        <v>269</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>570</v>
+        <v>317</v>
+      </c>
+      <c r="H103" t="s">
+        <v>275</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
@@ -5956,16 +5982,16 @@
     </row>
     <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>244</v>
+        <v>572</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -5974,7 +6000,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -5983,31 +6009,25 @@
     </row>
     <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>68</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -6016,16 +6036,16 @@
     </row>
     <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>246</v>
+        <v>523</v>
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
@@ -6034,7 +6054,7 @@
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M106" s="7"/>
       <c r="N106" s="7"/>
@@ -6043,25 +6063,27 @@
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F107" s="7"/>
+        <v>524</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
       <c r="L107" s="7" t="s">
-        <v>94</v>
+        <v>422</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
@@ -6070,16 +6092,16 @@
     </row>
     <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>424</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>248</v>
+        <v>525</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
@@ -6088,7 +6110,7 @@
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7" t="s">
-        <v>94</v>
+        <v>422</v>
       </c>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
@@ -6097,16 +6119,16 @@
     </row>
     <row r="109" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B109" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>249</v>
+        <v>526</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -6115,7 +6137,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7" t="s">
-        <v>94</v>
+        <v>422</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -6124,16 +6146,16 @@
     </row>
     <row r="110" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B110" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>250</v>
+        <v>527</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -6142,7 +6164,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -6151,27 +6173,25 @@
     </row>
     <row r="111" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B111" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>495</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="F111" s="7"/>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -6180,16 +6200,16 @@
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B112" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>92</v>
+        <v>382</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>252</v>
+        <v>529</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -6198,7 +6218,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -6207,20 +6227,25 @@
     </row>
     <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>573</v>
+      </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
-      <c r="K113" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
       <c r="O113" s="7"/>
@@ -6228,16 +6253,16 @@
     </row>
     <row r="114" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B114" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>253</v>
+        <v>530</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -6246,7 +6271,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
@@ -6255,31 +6280,25 @@
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>571</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
@@ -6288,25 +6307,31 @@
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
+        <v>532</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H116" t="s">
+        <v>433</v>
+      </c>
       <c r="I116" s="7"/>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
@@ -6315,25 +6340,24 @@
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>256</v>
+        <v>533</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
@@ -6342,25 +6366,27 @@
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>359</v>
+        <v>259</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="F118" s="7"/>
+        <v>574</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
@@ -6369,31 +6395,31 @@
     </row>
     <row r="119" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B119" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>258</v>
+        <v>575</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>496</v>
+        <v>343</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>498</v>
+        <v>317</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M119" s="7"/>
       <c r="N119" s="7"/>
@@ -6402,26 +6428,20 @@
     </row>
     <row r="120" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B120" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>259</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
+      <c r="I120" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="J120" s="7"/>
       <c r="K120" s="7"/>
-      <c r="L120" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L120" s="7"/>
       <c r="M120" s="7"/>
       <c r="N120" s="7"/>
       <c r="O120" s="7"/>
@@ -6429,59 +6449,41 @@
     </row>
     <row r="121" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B121" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>260</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
       <c r="K121" s="7"/>
-      <c r="L121" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L121" s="7"/>
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
       <c r="O121" s="7"/>
-      <c r="P121" s="7"/>
+      <c r="P121" s="7" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B122" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="I122" s="7"/>
+        <v>338</v>
+      </c>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
-      <c r="L122" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L122" s="7"/>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
       <c r="O122" s="7"/>
@@ -6489,25 +6491,24 @@
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B123" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>262</v>
+        <v>534</v>
       </c>
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
       <c r="K123" s="7"/>
       <c r="L123" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
@@ -6516,25 +6517,24 @@
     </row>
     <row r="124" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B124" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>263</v>
+        <v>535</v>
       </c>
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M124" s="7"/>
       <c r="N124" s="7"/>
@@ -6543,30 +6543,20 @@
     </row>
     <row r="125" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B125" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>573</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
       <c r="E125" s="7"/>
-      <c r="F125" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="I125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7" t="s">
+        <v>439</v>
+      </c>
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
-      <c r="L125" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L125" s="7"/>
       <c r="M125" s="7"/>
       <c r="N125" s="7"/>
       <c r="O125" s="7"/>
@@ -6574,26 +6564,20 @@
     </row>
     <row r="126" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B126" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>264</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
+      <c r="I126" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
-      <c r="L126" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L126" s="7"/>
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
       <c r="O126" s="7"/>
@@ -6601,26 +6585,19 @@
     </row>
     <row r="127" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B127" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>265</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
       <c r="F127" s="7"/>
       <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
+      <c r="I127" s="7" t="s">
+        <v>441</v>
+      </c>
       <c r="J127" s="7"/>
       <c r="K127" s="7"/>
-      <c r="L127" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L127" s="7"/>
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
       <c r="O127" s="7"/>
@@ -6628,31 +6605,25 @@
     </row>
     <row r="128" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B128" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>442</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="F128" s="7"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
@@ -6661,16 +6632,16 @@
     </row>
     <row r="129" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B129" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>443</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>267</v>
+        <v>537</v>
       </c>
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
@@ -6679,7 +6650,7 @@
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M129" s="7"/>
       <c r="N129" s="7"/>
@@ -6688,31 +6659,25 @@
     </row>
     <row r="130" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B130" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>92</v>
+        <v>379</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>444</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>575</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
       <c r="I130" s="7"/>
       <c r="J130" s="7"/>
       <c r="K130" s="7"/>
       <c r="L130" s="7" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="M130" s="7"/>
       <c r="N130" s="7"/>
@@ -6721,25 +6686,24 @@
     </row>
     <row r="131" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B131" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>445</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>269</v>
+        <v>539</v>
       </c>
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
       <c r="I131" s="7"/>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
@@ -6748,119 +6712,87 @@
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B132" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E132" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="I132" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
-      <c r="L132" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L132" s="7"/>
       <c r="M132" s="7"/>
       <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
+      <c r="O132" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P132" s="7"/>
     </row>
     <row r="133" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B133" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>271</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
-      <c r="L133" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L133" s="7"/>
       <c r="M133" s="7"/>
       <c r="N133" s="7"/>
       <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
+      <c r="P133" s="7" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="134" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B134" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>578</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
-      <c r="L134" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N134" s="7" t="s">
+        <v>378</v>
+      </c>
       <c r="O134" s="7"/>
       <c r="P134" s="7"/>
     </row>
     <row r="135" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B135" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>273</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
+      <c r="I135" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J135" s="7"/>
       <c r="K135" s="7"/>
-      <c r="L135" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L135" s="7"/>
       <c r="M135" s="7"/>
       <c r="N135" s="7"/>
       <c r="O135" s="7"/>
@@ -6868,31 +6800,31 @@
     </row>
     <row r="136" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B136" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>274</v>
+        <v>540</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>496</v>
+        <v>343</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>498</v>
+        <v>340</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>575</v>
+        <v>447</v>
       </c>
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
       <c r="K136" s="7"/>
       <c r="L136" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
@@ -6901,25 +6833,31 @@
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B137" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
+        <v>541</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>239</v>
+      </c>
       <c r="I137" s="7"/>
       <c r="J137" s="7"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M137" s="7"/>
       <c r="N137" s="7"/>
@@ -6928,25 +6866,31 @@
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B138" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
+        <v>542</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H138" t="s">
+        <v>450</v>
+      </c>
       <c r="I138" s="7"/>
       <c r="J138" s="7"/>
       <c r="K138" s="7"/>
       <c r="L138" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M138" s="7"/>
       <c r="N138" s="7"/>
@@ -6955,31 +6899,31 @@
     </row>
     <row r="139" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B139" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>277</v>
+        <v>543</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>496</v>
+        <v>353</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>498</v>
+        <v>317</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>579</v>
+        <v>237</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="7"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
@@ -6988,16 +6932,16 @@
     </row>
     <row r="140" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B140" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>359</v>
+        <v>260</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>278</v>
+        <v>544</v>
       </c>
       <c r="F140" s="7"/>
       <c r="G140" s="7"/>
@@ -7006,7 +6950,7 @@
       <c r="J140" s="7"/>
       <c r="K140" s="7"/>
       <c r="L140" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M140" s="7"/>
       <c r="N140" s="7"/>
@@ -7015,31 +6959,31 @@
     </row>
     <row r="141" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B141" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>279</v>
+        <v>545</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>496</v>
+        <v>269</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>346</v>
+        <v>369</v>
+      </c>
+      <c r="H141" t="s">
+        <v>454</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
       <c r="K141" s="7"/>
       <c r="L141" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M141" s="7"/>
       <c r="N141" s="7"/>
@@ -7048,25 +6992,31 @@
     </row>
     <row r="142" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B142" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D142" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H142" t="s">
         <v>456</v>
       </c>
-      <c r="E142" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
       <c r="K142" s="7"/>
       <c r="L142" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M142" s="7"/>
       <c r="N142" s="7"/>
@@ -7075,31 +7025,25 @@
     </row>
     <row r="143" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B143" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>457</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
       <c r="I143" s="7"/>
       <c r="J143" s="7"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7" t="s">
-        <v>94</v>
+        <v>270</v>
       </c>
       <c r="M143" s="7"/>
       <c r="N143" s="7"/>
@@ -7108,25 +7052,31 @@
     </row>
     <row r="144" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B144" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>359</v>
+        <v>259</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>458</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
+        <v>548</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I144" s="7"/>
       <c r="J144" s="7"/>
       <c r="K144" s="7"/>
       <c r="L144" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
@@ -7135,31 +7085,25 @@
     </row>
     <row r="145" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B145" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>459</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>580</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M145" s="7"/>
       <c r="N145" s="7"/>
@@ -7168,25 +7112,31 @@
     </row>
     <row r="146" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B146" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>460</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
+        <v>550</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H146" t="s">
+        <v>461</v>
+      </c>
       <c r="I146" s="7"/>
       <c r="J146" s="7"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M146" s="7"/>
       <c r="N146" s="7"/>
@@ -7195,31 +7145,31 @@
     </row>
     <row r="147" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B147" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>285</v>
+        <v>551</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>496</v>
+        <v>343</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>498</v>
+        <v>340</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>195</v>
+        <v>314</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="7"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
@@ -7228,16 +7178,16 @@
     </row>
     <row r="148" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B148" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>359</v>
+        <v>259</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>286</v>
+        <v>552</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -7246,7 +7196,7 @@
       <c r="J148" s="7"/>
       <c r="K148" s="7"/>
       <c r="L148" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
@@ -7255,31 +7205,25 @@
     </row>
     <row r="149" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B149" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="F149" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>579</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7"/>
       <c r="K149" s="7"/>
       <c r="L149" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M149" s="7"/>
       <c r="N149" s="7"/>
@@ -7288,45 +7232,61 @@
     </row>
     <row r="150" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B150" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
       <c r="I150" s="7"/>
       <c r="J150" s="7"/>
       <c r="K150" s="7"/>
-      <c r="L150" s="7"/>
-      <c r="M150" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L150" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="M150" s="7"/>
+      <c r="N150" s="7"/>
       <c r="O150" s="7"/>
       <c r="P150" s="7"/>
     </row>
     <row r="151" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B151" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-      <c r="I151" s="7" t="s">
-        <v>506</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H151" t="s">
+        <v>241</v>
+      </c>
+      <c r="I151" s="7"/>
       <c r="J151" s="7"/>
-      <c r="K151" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L151" s="7"/>
+      <c r="K151" s="7"/>
+      <c r="L151" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
       <c r="O151" s="7"/>
@@ -7334,31 +7294,25 @@
     </row>
     <row r="152" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B152" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>581</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
       <c r="I152" s="7"/>
       <c r="J152" s="7"/>
       <c r="K152" s="7"/>
       <c r="L152" s="7" t="s">
-        <v>94</v>
+        <v>270</v>
       </c>
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
@@ -7367,20 +7321,32 @@
     </row>
     <row r="153" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B153" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H153" t="s">
+        <v>189</v>
+      </c>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
-      <c r="K153" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="L153" s="7"/>
+      <c r="K153" s="7"/>
+      <c r="L153" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
       <c r="O153" s="7"/>
@@ -7388,20 +7354,26 @@
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B154" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>558</v>
+      </c>
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
-      <c r="I154" s="7" t="s">
-        <v>504</v>
-      </c>
+      <c r="I154" s="7"/>
       <c r="J154" s="7"/>
       <c r="K154" s="7"/>
-      <c r="L154" s="7"/>
+      <c r="L154" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
       <c r="O154" s="7"/>
@@ -7409,7 +7381,7 @@
     </row>
     <row r="155" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B155" s="7" t="s">
-        <v>355</v>
+        <v>140</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -7417,47 +7389,33 @@
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
-      <c r="I155" s="7" t="s">
-        <v>505</v>
-      </c>
+      <c r="I155" s="7"/>
       <c r="J155" s="7"/>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c r="M155" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="N155" s="7"/>
       <c r="O155" s="7"/>
-      <c r="P155" s="7" t="s">
-        <v>301</v>
-      </c>
+      <c r="P155" s="7"/>
     </row>
     <row r="156" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B156" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="I156" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="J156" s="7"/>
       <c r="K156" s="7"/>
-      <c r="L156" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L156" s="7"/>
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
       <c r="O156" s="7"/>
@@ -7465,65 +7423,41 @@
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B157" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>558</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
-      <c r="L157" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L157" s="7"/>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
       <c r="O157" s="7"/>
-      <c r="P157" s="7"/>
+      <c r="P157" s="7" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="158" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B158" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="F158" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="H158" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="I158" s="7"/>
+        <v>338</v>
+      </c>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="J158" s="7"/>
       <c r="K158" s="7"/>
-      <c r="L158" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L158" s="7"/>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
       <c r="O158" s="7"/>
@@ -7531,25 +7465,31 @@
     </row>
     <row r="159" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B159" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="7"/>
+        <v>559</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>471</v>
+      </c>
       <c r="I159" s="7"/>
       <c r="J159" s="7"/>
       <c r="K159" s="7"/>
       <c r="L159" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
@@ -7558,25 +7498,31 @@
     </row>
     <row r="160" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B160" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
+        <v>560</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>473</v>
+      </c>
       <c r="I160" s="7"/>
       <c r="J160" s="7"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
@@ -7585,104 +7531,70 @@
     </row>
     <row r="161" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B161" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D161" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="I161" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+      <c r="I161" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J161" s="7"/>
       <c r="K161" s="7"/>
-      <c r="L161" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L161" s="7"/>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
-      <c r="O161" s="7"/>
+      <c r="O161" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P161" s="7"/>
     </row>
     <row r="162" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B162" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="E162" s="7" t="s">
-        <v>293</v>
-      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="7"/>
       <c r="K162" s="7"/>
-      <c r="L162" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L162" s="7"/>
       <c r="M162" s="7"/>
       <c r="N162" s="7"/>
       <c r="O162" s="7"/>
       <c r="P162" s="7"/>
     </row>
     <row r="163" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B163" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>294</v>
-      </c>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
       <c r="J163" s="7"/>
       <c r="K163" s="7"/>
-      <c r="L163" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L163" s="7"/>
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
       <c r="O163" s="7"/>
       <c r="P163" s="7"/>
     </row>
     <row r="164" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B164" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="B164" s="7"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
-      <c r="I164" s="7" t="s">
-        <v>504</v>
-      </c>
+      <c r="I164" s="7"/>
       <c r="J164" s="7"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7692,9 +7604,7 @@
       <c r="P164" s="7"/>
     </row>
     <row r="165" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B165" s="7" t="s">
-        <v>355</v>
-      </c>
+      <c r="B165" s="7"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
@@ -7708,27 +7618,19 @@
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
       <c r="O165" s="7"/>
-      <c r="P165" s="7" t="s">
-        <v>296</v>
-      </c>
+      <c r="P165" s="7"/>
     </row>
     <row r="166" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B166" s="7" t="s">
-        <v>356</v>
-      </c>
+      <c r="B166" s="7"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
-      <c r="I166" s="7" t="s">
-        <v>506</v>
-      </c>
+      <c r="I166" s="7"/>
       <c r="J166" s="7"/>
-      <c r="K166" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
       <c r="N166" s="7"/>
@@ -7736,86 +7638,54 @@
       <c r="P166" s="7"/>
     </row>
     <row r="167" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B167" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H167" s="7" t="s">
-        <v>584</v>
-      </c>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
-      <c r="L167" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L167" s="7"/>
       <c r="M167" s="7"/>
       <c r="N167" s="7"/>
       <c r="O167" s="7"/>
       <c r="P167" s="7"/>
     </row>
     <row r="168" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B168" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C168" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D168" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>493</v>
-      </c>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
       <c r="I168" s="7"/>
       <c r="J168" s="7"/>
       <c r="K168" s="7"/>
-      <c r="L168" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="L168" s="7"/>
       <c r="M168" s="7"/>
       <c r="N168" s="7"/>
       <c r="O168" s="7"/>
       <c r="P168" s="7"/>
     </row>
     <row r="169" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B169" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
-      <c r="I169" s="7" t="s">
-        <v>508</v>
-      </c>
+      <c r="I169" s="7"/>
       <c r="J169" s="7"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
       <c r="N169" s="7"/>
-      <c r="O169" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="O169" s="7"/>
       <c r="P169" s="7"/>
     </row>
   </sheetData>
@@ -7834,579 +7704,579 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>323</v>
+        <v>227</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>586</v>
+        <v>320</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N3" t="s">
-        <v>530</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="G4" t="s">
-        <v>531</v>
+        <v>287</v>
       </c>
       <c r="H4" t="s">
-        <v>587</v>
+        <v>321</v>
       </c>
       <c r="M4" t="s">
-        <v>531</v>
+        <v>287</v>
       </c>
       <c r="N4" t="s">
-        <v>532</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>326</v>
+        <v>230</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>231</v>
       </c>
       <c r="G5" t="s">
-        <v>326</v>
+        <v>230</v>
       </c>
       <c r="H5" t="s">
-        <v>588</v>
+        <v>322</v>
       </c>
       <c r="M5" t="s">
-        <v>326</v>
+        <v>230</v>
       </c>
       <c r="N5" t="s">
-        <v>533</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>232</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>589</v>
+        <v>323</v>
       </c>
       <c r="M6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N6" t="s">
-        <v>534</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>329</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>590</v>
+        <v>324</v>
       </c>
       <c r="H7" t="s">
-        <v>591</v>
+        <v>325</v>
       </c>
       <c r="M7" t="s">
-        <v>535</v>
+        <v>291</v>
       </c>
       <c r="N7" t="s">
-        <v>536</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>535</v>
+        <v>291</v>
       </c>
       <c r="H8" t="s">
-        <v>592</v>
+        <v>326</v>
       </c>
       <c r="M8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" t="s">
-        <v>537</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>332</v>
+        <v>236</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>593</v>
+        <v>327</v>
       </c>
       <c r="M9" t="s">
-        <v>538</v>
+        <v>294</v>
       </c>
       <c r="N9" t="s">
-        <v>539</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="G10" t="s">
-        <v>538</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>594</v>
+        <v>328</v>
       </c>
       <c r="M10" t="s">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="N10" t="s">
-        <v>541</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>336</v>
+        <v>240</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="H11" t="s">
-        <v>591</v>
+        <v>325</v>
       </c>
       <c r="M11" t="s">
-        <v>542</v>
+        <v>298</v>
       </c>
       <c r="N11" t="s">
-        <v>543</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>337</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="G12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>595</v>
+        <v>329</v>
       </c>
       <c r="M12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N12" t="s">
-        <v>544</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>340</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
-        <v>341</v>
+        <v>245</v>
       </c>
       <c r="G13" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="H13" t="s">
-        <v>596</v>
+        <v>330</v>
       </c>
       <c r="M13" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="N13" t="s">
-        <v>532</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>342</v>
+        <v>246</v>
       </c>
       <c r="G14" t="s">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="H14" t="s">
-        <v>597</v>
+        <v>331</v>
       </c>
       <c r="M14" t="s">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="N14" t="s">
-        <v>545</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>343</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
-        <v>344</v>
+        <v>248</v>
       </c>
       <c r="G15" t="s">
-        <v>548</v>
+        <v>304</v>
       </c>
       <c r="H15" t="s">
-        <v>598</v>
+        <v>332</v>
       </c>
       <c r="M15" t="s">
-        <v>337</v>
+        <v>241</v>
       </c>
       <c r="N15" t="s">
-        <v>546</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
       <c r="G16" t="s">
-        <v>340</v>
+        <v>244</v>
       </c>
       <c r="H16" t="s">
-        <v>599</v>
+        <v>333</v>
       </c>
       <c r="M16" t="s">
-        <v>548</v>
+        <v>304</v>
       </c>
       <c r="N16" t="s">
-        <v>547</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>345</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>350</v>
+        <v>252</v>
       </c>
       <c r="G17" t="s">
-        <v>345</v>
+        <v>249</v>
       </c>
       <c r="H17" t="s">
-        <v>600</v>
+        <v>334</v>
       </c>
       <c r="M17" t="s">
-        <v>549</v>
+        <v>305</v>
       </c>
       <c r="N17" t="s">
-        <v>550</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="G18" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>601</v>
+        <v>335</v>
       </c>
       <c r="M18" t="s">
-        <v>551</v>
+        <v>307</v>
       </c>
       <c r="N18" t="s">
-        <v>552</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>352</v>
+        <v>254</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H19" t="s">
-        <v>602</v>
+        <v>336</v>
       </c>
       <c r="M19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>553</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>255</v>
       </c>
       <c r="M20" t="s">
-        <v>554</v>
+        <v>310</v>
       </c>
       <c r="N20" t="s">
-        <v>555</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>345</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s">
-        <v>556</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M22" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="N22" t="s">
-        <v>557</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>525</v>
+        <v>281</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
       </c>
       <c r="J23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M23" t="s">
-        <v>558</v>
+        <v>314</v>
       </c>
       <c r="N23" t="s">
-        <v>559</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>526</v>
+        <v>282</v>
       </c>
       <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" t="s">
         <v>87</v>
       </c>
-      <c r="G24" t="s">
-        <v>89</v>
-      </c>
       <c r="J24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M25" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P25" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" t="s">
+        <v>152</v>
+      </c>
+      <c r="J26" t="s">
         <v>153</v>
       </c>
-      <c r="E26" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" t="s">
-        <v>155</v>
-      </c>
-      <c r="J26" t="s">
-        <v>156</v>
-      </c>
       <c r="M26" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" t="s">
         <v>78</v>
-      </c>
-      <c r="P26" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="M27" t="s">
+        <v>79</v>
+      </c>
+      <c r="P27" t="s">
         <v>80</v>
-      </c>
-      <c r="P27" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M28" t="s">
+        <v>81</v>
+      </c>
+      <c r="P28" t="s">
         <v>82</v>
-      </c>
-      <c r="P28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="M29" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" t="s">
         <v>84</v>
-      </c>
-      <c r="P29" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P30" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>527</v>
+        <v>283</v>
       </c>
       <c r="E31" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="M31" t="s">
-        <v>157</v>
+        <v>577</v>
       </c>
       <c r="P31" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>528</v>
+        <v>284</v>
       </c>
       <c r="E32" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>529</v>
+        <v>285</v>
       </c>
       <c r="E33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>519</v>
+        <v>275</v>
       </c>
       <c r="E34" t="s">
-        <v>520</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>521</v>
+        <v>277</v>
       </c>
       <c r="E35" t="s">
-        <v>522</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="E36" t="s">
-        <v>524</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -8422,122 +8292,122 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
@@ -8545,7 +8415,7 @@
         <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
@@ -8553,81 +8423,81 @@
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -8643,74 +8513,74 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F10">
         <v>71</v>
@@ -8718,10 +8588,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F11">
         <v>73</v>
@@ -8729,7 +8599,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -8737,7 +8607,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F13">
         <v>77</v>
@@ -8745,10 +8615,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F14">
         <v>88</v>
@@ -8756,10 +8626,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -8767,7 +8637,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -8775,7 +8645,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F17">
         <v>101</v>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323DF7D-A18B-44A0-BFFE-C4CD47A3F4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DC1A2E-F0B8-4026-9E65-5E9AA264DA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="51495" yWindow="7095" windowWidth="16410" windowHeight="14505" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="578">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1033,9 +1033,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>BGM</t>
-  </si>
-  <si>
     <t>BG</t>
   </si>
   <si>
@@ -1390,10 +1387,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>skill3 face_serious lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>저 자신은 어디서 오는 지 몰라.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1596,10 +1589,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>BGM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>flashback</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1628,10 +1617,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>anger1 face_smile lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1743,18 +1728,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>eyeblink</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRANSITION</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>fadeout</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>바통을 넘겨받은 스트레이라이트의 세리자와 아사히!</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1767,10 +1740,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>1등 못하면 용서 안할거니까…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>SNS에서 후유코쨩이 좋은 얼굴을 하고 있다고 화제가 되고 있슴다.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1803,10 +1772,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>anger1 face_jito_lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>뭐, 좋은 게 좋은 거려나…</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1871,10 +1836,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>anger2 face_serious lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>가버렸슴다.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2196,10 +2157,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>smile1 face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>S003046</t>
   </si>
   <si>
@@ -2223,7 +2180,47 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>skill1 face_wait lip_smile</t>
+    <t>AUDIO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1 face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1 face_serious lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_taoreru</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 1등 못하면 용서 안할거니까…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_101</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_serious lip_smile1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -3343,7 +3340,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3359,12 +3356,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>256</v>
+        <v>567</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3373,21 +3370,23 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3396,7 +3395,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3414,19 +3413,19 @@
         <v>90</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3444,22 +3443,22 @@
         <v>89</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>214</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3480,19 +3479,19 @@
         <v>90</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -3510,16 +3509,16 @@
         <v>89</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -3536,7 +3535,7 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3547,7 +3546,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -3560,22 +3559,22 @@
         <v>89</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>214</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -3596,19 +3595,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -3626,19 +3625,19 @@
         <v>89</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H13" t="s">
         <v>81</v>
@@ -3659,13 +3658,13 @@
         <v>89</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -3688,19 +3687,19 @@
         <v>90</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -3721,19 +3720,19 @@
         <v>90</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -3754,10 +3753,10 @@
         <v>90</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -3778,22 +3777,22 @@
         <v>89</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -3814,19 +3813,19 @@
         <v>90</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -3850,7 +3849,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -3862,7 +3861,7 @@
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -3871,10 +3870,10 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -3882,7 +3881,7 @@
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -3902,7 +3901,7 @@
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -3916,16 +3915,16 @@
         <v>90</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>244</v>
@@ -3946,13 +3945,13 @@
         <v>89</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -3976,19 +3975,19 @@
         <v>90</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -4006,22 +4005,22 @@
         <v>89</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H26" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -4042,19 +4041,19 @@
         <v>90</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
@@ -4092,7 +4091,7 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>141</v>
+        <v>337</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -4100,9 +4099,7 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -4121,19 +4118,21 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
+      <c r="I30" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="7" t="s">
-        <v>337</v>
-      </c>
+      <c r="P30" s="7"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="7"/>
+      <c r="B31" s="7" t="s">
+        <v>256</v>
+      </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -4147,30 +4146,26 @@
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
+      <c r="P31" s="7" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>492</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
+      <c r="I32" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
@@ -4184,10 +4179,10 @@
         <v>90</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -4211,10 +4206,10 @@
         <v>90</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -4232,30 +4227,34 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="7" t="s">
-        <v>143</v>
-      </c>
+      <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
+      <c r="L35" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="O35" s="7"/>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -4263,16 +4262,18 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
+      <c r="I36" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7" t="s">
-        <v>374</v>
-      </c>
+      <c r="O36" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
@@ -4288,18 +4289,16 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
-      <c r="M37" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="N37" s="7" t="s">
-        <v>378</v>
-      </c>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
       <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
+      <c r="P37" s="7" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>375</v>
+        <v>567</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -4307,24 +4306,24 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="J38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
-        <v>377</v>
+        <v>555</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -4333,38 +4332,38 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J39" s="7"/>
+        <v>374</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
+      <c r="M39" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>376</v>
+      </c>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>495</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
+      <c r="I40" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
-      <c r="L40" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
@@ -4372,93 +4371,91 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="7" t="s">
-        <v>143</v>
-      </c>
+      <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="L41" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="O41" s="7"/>
       <c r="P41" s="7"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
-      <c r="G42" s="7" t="s">
-        <v>411</v>
-      </c>
+      <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>363</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="7" t="s">
-        <v>374</v>
-      </c>
+      <c r="P42" s="7"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>496</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
+      <c r="G43" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="I43" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="K43" s="7"/>
-      <c r="L43" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
+      <c r="P43" s="7" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -4467,7 +4464,7 @@
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4479,13 +4476,13 @@
         <v>89</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4494,7 +4491,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4506,13 +4503,13 @@
         <v>89</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -4521,7 +4518,7 @@
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -4533,13 +4530,13 @@
         <v>89</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -4548,7 +4545,7 @@
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4560,13 +4557,13 @@
         <v>89</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -4575,7 +4572,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4587,13 +4584,13 @@
         <v>89</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -4602,7 +4599,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4614,13 +4611,13 @@
         <v>89</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -4629,7 +4626,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4641,13 +4638,13 @@
         <v>89</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -4656,7 +4653,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4668,13 +4665,13 @@
         <v>89</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -4683,7 +4680,7 @@
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4692,20 +4689,26 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
+      <c r="L53" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
@@ -4713,7 +4716,7 @@
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4721,18 +4724,20 @@
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
+      <c r="I54" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="7" t="s">
-        <v>392</v>
-      </c>
+      <c r="P54" s="7"/>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -4740,45 +4745,31 @@
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
-      <c r="I55" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
+      <c r="P55" s="7" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H56" t="s">
-        <v>275</v>
-      </c>
-      <c r="I56" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -4789,24 +4780,28 @@
         <v>89</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>567</v>
+        <v>90</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>394</v>
+        <v>556</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
+        <v>268</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H57" t="s">
+        <v>274</v>
+      </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7" t="s">
-        <v>274</v>
+        <v>91</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
@@ -4818,22 +4813,24 @@
         <v>89</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="F58" s="7"/>
+        <v>497</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
@@ -4845,28 +4842,22 @@
         <v>89</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>90</v>
+        <v>557</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H59" t="s">
-        <v>397</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -4878,24 +4869,28 @@
         <v>89</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>379</v>
+        <v>90</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
+        <v>268</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H60" t="s">
+        <v>395</v>
+      </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
       <c r="L60" s="7" t="s">
-        <v>274</v>
+        <v>91</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -4907,22 +4902,24 @@
         <v>89</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="F61" s="7"/>
+        <v>500</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -4934,28 +4931,22 @@
         <v>89</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H62" t="s">
-        <v>341</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
@@ -4964,20 +4955,32 @@
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7" t="s">
-        <v>401</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H63" t="s">
+        <v>340</v>
+      </c>
+      <c r="I63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
+      <c r="L63" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -4985,7 +4988,7 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>402</v>
+        <v>141</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -4993,20 +4996,20 @@
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
+      <c r="I64" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
-      <c r="P64" s="7" t="s">
-        <v>347</v>
-      </c>
+      <c r="P64" s="7"/>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>257</v>
+        <v>567</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -5015,21 +5018,21 @@
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="J65" s="7"/>
+        <v>570</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
-      <c r="P65" s="7" t="s">
-        <v>203</v>
-      </c>
+      <c r="P65" s="7"/>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -5038,12 +5041,12 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7" t="s">
-        <v>348</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
@@ -5052,53 +5055,45 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>196</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
+      <c r="I67" s="7" t="s">
+        <v>400</v>
+      </c>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
-      <c r="L67" s="7" t="s">
-        <v>270</v>
-      </c>
+      <c r="L67" s="7"/>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
-      <c r="P67" s="7"/>
+      <c r="P67" s="7" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
+      <c r="I68" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7" t="s">
-        <v>270</v>
-      </c>
+      <c r="K68" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="L68" s="7"/>
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
@@ -5106,20 +5101,26 @@
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>196</v>
+      </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
-        <v>401</v>
-      </c>
+      <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
+      <c r="L69" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
@@ -5127,30 +5128,34 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
+      <c r="D70" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
-        <v>272</v>
-      </c>
+      <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
+      <c r="L70" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
-      <c r="P70" s="7" t="s">
-        <v>205</v>
-      </c>
+      <c r="P70" s="7"/>
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -5159,12 +5164,10 @@
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="J71" s="7"/>
-      <c r="K71" s="7" t="s">
-        <v>348</v>
-      </c>
+      <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
@@ -5173,53 +5176,45 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>200</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
+      <c r="I72" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
-      <c r="L72" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L72" s="7"/>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
       <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
+      <c r="P72" s="7" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>201</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
+      <c r="I73" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="K73" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="L73" s="7"/>
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
       <c r="O73" s="7"/>
@@ -5230,13 +5225,13 @@
         <v>89</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -5254,20 +5249,26 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
-      <c r="I75" s="7" t="s">
-        <v>401</v>
-      </c>
+      <c r="I75" s="7"/>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
+      <c r="L75" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
@@ -5275,30 +5276,34 @@
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>202</v>
+      </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
-      <c r="I76" s="7" t="s">
-        <v>272</v>
-      </c>
+      <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
+      <c r="L76" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
-      <c r="P76" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="P76" s="7"/>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -5307,12 +5312,10 @@
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="J77" s="7"/>
-      <c r="K77" s="7" t="s">
-        <v>348</v>
-      </c>
+      <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
@@ -5321,53 +5324,45 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>198</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
+      <c r="I78" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
-      <c r="L78" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L78" s="7"/>
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
+      <c r="P78" s="7" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>199</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
+      <c r="I79" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="K79" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="L79" s="7"/>
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
       <c r="O79" s="7"/>
@@ -5375,20 +5370,26 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
-      <c r="I80" s="7" t="s">
-        <v>401</v>
-      </c>
+      <c r="I80" s="7"/>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
+      <c r="L80" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
       <c r="O80" s="7"/>
@@ -5396,28 +5397,34 @@
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>199</v>
+      </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
+      <c r="L81" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
-      <c r="P81" s="7" t="s">
-        <v>374</v>
-      </c>
+      <c r="P81" s="7"/>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -5425,22 +5432,20 @@
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
+      <c r="I82" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="N82" s="7" t="s">
-        <v>378</v>
-      </c>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5448,72 +5453,58 @@
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I83" s="7"/>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
+      <c r="P83" s="7" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>513</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
-      <c r="J84" s="7"/>
+      <c r="J84" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="K84" s="7"/>
-      <c r="L84" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="N84" s="7" t="s">
+        <v>376</v>
+      </c>
       <c r="O84" s="7"/>
       <c r="P84" s="7"/>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H85" t="s">
-        <v>244</v>
-      </c>
-      <c r="I85" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
-      <c r="L85" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L85" s="7"/>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
       <c r="O85" s="7"/>
@@ -5524,21 +5515,17 @@
         <v>89</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>77</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5552,18 +5539,32 @@
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H87" t="s">
+        <v>244</v>
+      </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
-      <c r="L87" s="7"/>
+      <c r="L87" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
       <c r="O87" s="7"/>
@@ -5574,18 +5575,21 @@
         <v>89</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>90</v>
+        <v>259</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>569</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G88" s="7"/>
+        <v>351</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
@@ -5599,7 +5603,7 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -5609,9 +5613,7 @@
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
-      <c r="K89" s="7" t="s">
-        <v>348</v>
-      </c>
+      <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
@@ -5626,20 +5628,15 @@
         <v>90</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>515</v>
+        <v>559</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H90" t="s">
-        <v>570</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="G90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
@@ -5653,7 +5650,7 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -5664,7 +5661,7 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
@@ -5680,19 +5677,19 @@
         <v>90</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H92" t="s">
-        <v>410</v>
+        <v>276</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
@@ -5707,7 +5704,7 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -5718,7 +5715,7 @@
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
       <c r="K93" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
@@ -5728,30 +5725,40 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H94" t="s">
+        <v>571</v>
+      </c>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
+      <c r="L94" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M94" s="7"/>
-      <c r="N94" s="7" t="s">
-        <v>348</v>
-      </c>
+      <c r="N94" s="7"/>
       <c r="O94" s="7"/>
-      <c r="P94" s="7" t="s">
-        <v>412</v>
-      </c>
+      <c r="P94" s="7"/>
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
-        <v>141</v>
+        <v>337</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -5759,11 +5766,11 @@
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
-      <c r="I95" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I95" s="7"/>
       <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
+      <c r="K95" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
@@ -5772,7 +5779,7 @@
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>257</v>
+        <v>373</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -5785,15 +5792,17 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
+      <c r="N96" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O96" s="7"/>
       <c r="P96" s="7" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -5802,7 +5811,7 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -5814,80 +5823,68 @@
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>517</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
-      <c r="L98" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L98" s="7"/>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
+      <c r="P98" s="7" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>571</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="7"/>
+      <c r="I99" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="K99" s="7"/>
-      <c r="L99" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
+      <c r="L99" s="7"/>
+      <c r="M99" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="N99" s="7" t="s">
+        <v>376</v>
+      </c>
       <c r="O99" s="7"/>
       <c r="P99" s="7"/>
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>518</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
+      <c r="I100" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
-      <c r="L100" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L100" s="7"/>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
       <c r="O100" s="7"/>
@@ -5898,13 +5895,13 @@
         <v>89</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -5913,7 +5910,7 @@
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -5925,13 +5922,13 @@
         <v>89</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -5940,7 +5937,7 @@
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -5952,28 +5949,22 @@
         <v>89</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>263</v>
+        <v>411</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H103" t="s">
-        <v>275</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
@@ -5985,13 +5976,13 @@
         <v>89</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -6000,7 +5991,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -6012,13 +6003,13 @@
         <v>89</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
@@ -6027,7 +6018,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -6042,14 +6033,11 @@
         <v>90</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>420</v>
+        <v>262</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
+        <v>511</v>
+      </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -6066,24 +6054,28 @@
         <v>89</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>393</v>
+        <v>90</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
+        <v>268</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H107" t="s">
+        <v>274</v>
+      </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
       <c r="L107" s="7" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
@@ -6095,13 +6087,13 @@
         <v>89</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>423</v>
+        <v>90</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
@@ -6110,7 +6102,7 @@
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
@@ -6122,13 +6114,13 @@
         <v>89</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>425</v>
+        <v>90</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -6137,7 +6129,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -6149,22 +6141,24 @@
         <v>89</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="F110" s="7"/>
+        <v>514</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>274</v>
+        <v>418</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -6176,13 +6170,13 @@
         <v>89</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -6191,7 +6185,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7" t="s">
-        <v>274</v>
+        <v>418</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -6203,13 +6197,13 @@
         <v>89</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -6218,7 +6212,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>274</v>
+        <v>418</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -6230,21 +6224,22 @@
         <v>89</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>263</v>
+        <v>423</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
@@ -6256,13 +6251,13 @@
         <v>89</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -6271,7 +6266,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
@@ -6283,13 +6278,13 @@
         <v>89</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -6298,7 +6293,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
@@ -6313,20 +6308,13 @@
         <v>90</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H116" t="s">
-        <v>433</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
@@ -6343,21 +6331,22 @@
         <v>89</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
@@ -6369,24 +6358,22 @@
         <v>89</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>259</v>
+        <v>377</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>347</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
@@ -6398,22 +6385,22 @@
         <v>89</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>575</v>
+        <v>522</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>343</v>
+        <v>268</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>350</v>
+        <v>316</v>
+      </c>
+      <c r="H119" t="s">
+        <v>429</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
@@ -6428,20 +6415,25 @@
     </row>
     <row r="120" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B120" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>523</v>
+      </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I120" s="7"/>
       <c r="J120" s="7"/>
       <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
+      <c r="L120" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M120" s="7"/>
       <c r="N120" s="7"/>
       <c r="O120" s="7"/>
@@ -6449,41 +6441,61 @@
     </row>
     <row r="121" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B121" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
       <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
+      <c r="L121" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
       <c r="O121" s="7"/>
-      <c r="P121" s="7" t="s">
-        <v>392</v>
-      </c>
+      <c r="P121" s="7"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B122" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7" t="s">
-        <v>319</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="I122" s="7"/>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
+      <c r="L122" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
       <c r="O122" s="7"/>
@@ -6491,25 +6503,20 @@
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B123" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>534</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
-      <c r="I123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="J123" s="7"/>
       <c r="K123" s="7"/>
-      <c r="L123" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L123" s="7"/>
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
       <c r="O123" s="7"/>
@@ -6517,33 +6524,32 @@
     </row>
     <row r="124" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B124" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>535</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
-      <c r="L124" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
+      <c r="L124" s="7"/>
+      <c r="M124" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="N124" s="7" t="s">
+        <v>574</v>
+      </c>
       <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
+      <c r="P124" s="7" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="125" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B125" s="7" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -6552,7 +6558,7 @@
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
       <c r="I125" s="7" t="s">
-        <v>439</v>
+        <v>318</v>
       </c>
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
@@ -6564,20 +6570,25 @@
     </row>
     <row r="126" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B126" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>524</v>
+      </c>
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I126" s="7"/>
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
+      <c r="L126" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
       <c r="O126" s="7"/>
@@ -6585,19 +6596,25 @@
     </row>
     <row r="127" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B127" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>525</v>
+      </c>
       <c r="F127" s="7"/>
       <c r="G127" s="7"/>
-      <c r="I127" s="7" t="s">
-        <v>441</v>
-      </c>
+      <c r="I127" s="7"/>
       <c r="J127" s="7"/>
       <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
+      <c r="L127" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
       <c r="O127" s="7"/>
@@ -6605,26 +6622,17 @@
     </row>
     <row r="128" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B128" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>536</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
       <c r="F128" s="7"/>
       <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
-      <c r="L128" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L128" s="7"/>
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
       <c r="O128" s="7"/>
@@ -6632,26 +6640,20 @@
     </row>
     <row r="129" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B129" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>537</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
+      <c r="I129" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
-      <c r="L129" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L129" s="7"/>
       <c r="M129" s="7"/>
       <c r="N129" s="7"/>
       <c r="O129" s="7"/>
@@ -6659,26 +6661,20 @@
     </row>
     <row r="130" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B130" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>538</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
       <c r="F130" s="7"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
+      <c r="I130" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J130" s="7"/>
       <c r="K130" s="7"/>
-      <c r="L130" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="L130" s="7"/>
       <c r="M130" s="7"/>
       <c r="N130" s="7"/>
       <c r="O130" s="7"/>
@@ -6689,21 +6685,22 @@
         <v>89</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
       <c r="I131" s="7"/>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
@@ -6712,74 +6709,87 @@
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B132" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>527</v>
+      </c>
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
-      <c r="I132" s="7" t="s">
-        <v>143</v>
-      </c>
+      <c r="I132" s="7"/>
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
+      <c r="L132" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="M132" s="7"/>
       <c r="N132" s="7"/>
-      <c r="O132" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="O132" s="7"/>
       <c r="P132" s="7"/>
     </row>
     <row r="133" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B133" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>528</v>
+      </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
+      <c r="L133" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="M133" s="7"/>
       <c r="N133" s="7"/>
       <c r="O133" s="7"/>
-      <c r="P133" s="7" t="s">
-        <v>337</v>
-      </c>
+      <c r="P133" s="7"/>
     </row>
     <row r="134" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B134" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>529</v>
+      </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N134" s="7" t="s">
-        <v>378</v>
-      </c>
+      <c r="L134" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M134" s="7"/>
+      <c r="N134" s="7"/>
       <c r="O134" s="7"/>
       <c r="P134" s="7"/>
     </row>
     <row r="135" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B135" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -6787,9 +6797,7 @@
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
-      <c r="I135" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I135" s="7"/>
       <c r="J135" s="7"/>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6800,131 +6808,89 @@
     </row>
     <row r="136" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B136" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="I136" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="J136" s="7"/>
       <c r="K136" s="7"/>
-      <c r="L136" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L136" s="7"/>
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
+      <c r="O136" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P136" s="7"/>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B137" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D137" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E137" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>239</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
       <c r="I137" s="7"/>
       <c r="J137" s="7"/>
       <c r="K137" s="7"/>
-      <c r="L137" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L137" s="7"/>
       <c r="M137" s="7"/>
       <c r="N137" s="7"/>
       <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
+      <c r="P137" s="7" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B138" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="H138" t="s">
-        <v>450</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
       <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
+      <c r="J138" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="K138" s="7"/>
-      <c r="L138" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="N138" s="7" t="s">
+        <v>376</v>
+      </c>
       <c r="O138" s="7"/>
       <c r="P138" s="7"/>
     </row>
     <row r="139" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B139" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="I139" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J139" s="7"/>
       <c r="K139" s="7"/>
-      <c r="L139" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L139" s="7"/>
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
       <c r="O139" s="7"/>
@@ -6935,17 +6901,23 @@
         <v>89</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
+        <v>530</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>439</v>
+      </c>
       <c r="I140" s="7"/>
       <c r="J140" s="7"/>
       <c r="K140" s="7"/>
@@ -6962,22 +6934,22 @@
         <v>89</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>90</v>
+        <v>259</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="H141" t="s">
-        <v>454</v>
+        <v>316</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
@@ -6998,19 +6970,19 @@
         <v>90</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H142" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
@@ -7028,22 +7000,28 @@
         <v>89</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
+        <v>533</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="I143" s="7"/>
       <c r="J143" s="7"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7" t="s">
-        <v>270</v>
+        <v>91</v>
       </c>
       <c r="M143" s="7"/>
       <c r="N143" s="7"/>
@@ -7058,20 +7036,14 @@
         <v>259</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>318</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
       <c r="I144" s="7"/>
       <c r="J144" s="7"/>
       <c r="K144" s="7"/>
@@ -7088,17 +7060,23 @@
         <v>89</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
+        <v>535</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="H145" t="s">
+        <v>276</v>
+      </c>
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
       <c r="K145" s="7"/>
@@ -7118,19 +7096,19 @@
         <v>90</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H146" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="7"/>
@@ -7148,28 +7126,22 @@
         <v>89</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>314</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
       <c r="I147" s="7"/>
       <c r="J147" s="7"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
@@ -7181,17 +7153,23 @@
         <v>89</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
+        <v>538</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>317</v>
+      </c>
       <c r="I148" s="7"/>
       <c r="J148" s="7"/>
       <c r="K148" s="7"/>
@@ -7208,13 +7186,13 @@
         <v>89</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
@@ -7235,24 +7213,28 @@
         <v>89</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>258</v>
+        <v>90</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
+        <v>268</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="H150" t="s">
+        <v>452</v>
+      </c>
       <c r="I150" s="7"/>
       <c r="J150" s="7"/>
       <c r="K150" s="7"/>
       <c r="L150" s="7" t="s">
-        <v>270</v>
+        <v>91</v>
       </c>
       <c r="M150" s="7"/>
       <c r="N150" s="7"/>
@@ -7264,22 +7246,22 @@
         <v>89</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H151" t="s">
-        <v>241</v>
+        <v>339</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>313</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
@@ -7300,10 +7282,10 @@
         <v>258</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
@@ -7312,7 +7294,7 @@
       <c r="J152" s="7"/>
       <c r="K152" s="7"/>
       <c r="L152" s="7" t="s">
-        <v>270</v>
+        <v>91</v>
       </c>
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
@@ -7324,23 +7306,17 @@
         <v>89</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="F153" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H153" t="s">
-        <v>189</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
       <c r="K153" s="7"/>
@@ -7357,22 +7333,24 @@
         <v>89</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="F154" s="7"/>
+        <v>544</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
       <c r="K154" s="7"/>
       <c r="L154" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
@@ -7381,41 +7359,59 @@
     </row>
     <row r="155" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B155" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H155" t="s">
+        <v>241</v>
+      </c>
       <c r="I155" s="7"/>
       <c r="J155" s="7"/>
       <c r="K155" s="7"/>
-      <c r="L155" s="7"/>
-      <c r="M155" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="L155" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M155" s="7"/>
       <c r="N155" s="7"/>
       <c r="O155" s="7"/>
       <c r="P155" s="7"/>
     </row>
     <row r="156" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B156" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>546</v>
+      </c>
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
-      <c r="I156" s="7" t="s">
-        <v>401</v>
-      </c>
+      <c r="I156" s="7"/>
       <c r="J156" s="7"/>
       <c r="K156" s="7"/>
-      <c r="L156" s="7"/>
+      <c r="L156" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
       <c r="O156" s="7"/>
@@ -7423,41 +7419,59 @@
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B157" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H157" t="s">
+        <v>189</v>
+      </c>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
-      <c r="L157" s="7"/>
+      <c r="L157" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
       <c r="O157" s="7"/>
-      <c r="P157" s="7" t="s">
-        <v>337</v>
-      </c>
+      <c r="P157" s="7"/>
     </row>
     <row r="158" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B158" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>548</v>
+      </c>
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
-      <c r="I158" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I158" s="7"/>
       <c r="J158" s="7"/>
       <c r="K158" s="7"/>
-      <c r="L158" s="7"/>
+      <c r="L158" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
       <c r="O158" s="7"/>
@@ -7465,65 +7479,41 @@
     </row>
     <row r="159" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B159" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="F159" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>471</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
       <c r="I159" s="7"/>
       <c r="J159" s="7"/>
       <c r="K159" s="7"/>
-      <c r="L159" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M159" s="7"/>
+      <c r="L159" s="7"/>
+      <c r="M159" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="N159" s="7"/>
       <c r="O159" s="7"/>
       <c r="P159" s="7"/>
     </row>
     <row r="160" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B160" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D160" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E160" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="F160" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="I160" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="J160" s="7"/>
       <c r="K160" s="7"/>
-      <c r="L160" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L160" s="7"/>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
       <c r="O160" s="7"/>
@@ -7531,7 +7521,7 @@
     </row>
     <row r="161" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B161" s="7" t="s">
-        <v>141</v>
+        <v>256</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -7539,28 +7529,30 @@
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
-      <c r="I161" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="I161" s="7"/>
       <c r="J161" s="7"/>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
-      <c r="O161" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P161" s="7"/>
+      <c r="O161" s="7"/>
+      <c r="P161" s="7" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="162" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B162" s="7"/>
+      <c r="B162" s="7" t="s">
+        <v>337</v>
+      </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
-      <c r="I162" s="7"/>
+      <c r="I162" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="J162" s="7"/>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7570,54 +7562,92 @@
       <c r="P162" s="7"/>
     </row>
     <row r="163" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
+      <c r="B163" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>577</v>
+      </c>
       <c r="I163" s="7"/>
       <c r="J163" s="7"/>
       <c r="K163" s="7"/>
-      <c r="L163" s="7"/>
+      <c r="L163" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
       <c r="O163" s="7"/>
       <c r="P163" s="7"/>
     </row>
     <row r="164" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B164" s="7"/>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-      <c r="G164" s="7"/>
-      <c r="H164" s="7"/>
+      <c r="B164" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>463</v>
+      </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
       <c r="K164" s="7"/>
-      <c r="L164" s="7"/>
+      <c r="L164" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M164" s="7"/>
       <c r="N164" s="7"/>
       <c r="O164" s="7"/>
       <c r="P164" s="7"/>
     </row>
     <row r="165" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B165" s="7"/>
+      <c r="B165" s="7" t="s">
+        <v>141</v>
+      </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
       <c r="F165" s="7"/>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
-      <c r="I165" s="7"/>
+      <c r="I165" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="J165" s="7"/>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
-      <c r="O165" s="7"/>
+      <c r="O165" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="P165" s="7"/>
     </row>
     <row r="166" spans="2:16" x14ac:dyDescent="0.3">
@@ -7724,13 +7754,13 @@
         <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M3" t="s">
         <v>83</v>
       </c>
       <c r="N3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
@@ -7741,16 +7771,16 @@
         <v>229</v>
       </c>
       <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>320</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
         <v>287</v>
-      </c>
-      <c r="H4" t="s">
-        <v>321</v>
-      </c>
-      <c r="M4" t="s">
-        <v>287</v>
-      </c>
-      <c r="N4" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
@@ -7764,13 +7794,13 @@
         <v>230</v>
       </c>
       <c r="H5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M5" t="s">
         <v>230</v>
       </c>
       <c r="N5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -7784,13 +7814,13 @@
         <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M6" t="s">
         <v>77</v>
       </c>
       <c r="N6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
@@ -7801,16 +7831,16 @@
         <v>234</v>
       </c>
       <c r="G7" t="s">
+        <v>323</v>
+      </c>
+      <c r="H7" t="s">
         <v>324</v>
       </c>
-      <c r="H7" t="s">
-        <v>325</v>
-      </c>
       <c r="M7" t="s">
+        <v>290</v>
+      </c>
+      <c r="N7" t="s">
         <v>291</v>
-      </c>
-      <c r="N7" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
@@ -7821,16 +7851,16 @@
         <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M8" t="s">
         <v>81</v>
       </c>
       <c r="N8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
@@ -7844,13 +7874,13 @@
         <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M9" t="s">
+        <v>293</v>
+      </c>
+      <c r="N9" t="s">
         <v>294</v>
-      </c>
-      <c r="N9" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
@@ -7861,16 +7891,16 @@
         <v>238</v>
       </c>
       <c r="G10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M10" t="s">
+        <v>295</v>
+      </c>
+      <c r="N10" t="s">
         <v>296</v>
-      </c>
-      <c r="N10" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -7881,16 +7911,16 @@
         <v>240</v>
       </c>
       <c r="G11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M11" t="s">
+        <v>297</v>
+      </c>
+      <c r="N11" t="s">
         <v>298</v>
-      </c>
-      <c r="N11" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -7904,13 +7934,13 @@
         <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M12" t="s">
         <v>189</v>
       </c>
       <c r="N12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -7924,13 +7954,13 @@
         <v>237</v>
       </c>
       <c r="H13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M13" t="s">
         <v>237</v>
       </c>
       <c r="N13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
@@ -7944,13 +7974,13 @@
         <v>239</v>
       </c>
       <c r="H14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M14" t="s">
         <v>239</v>
       </c>
       <c r="N14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
@@ -7961,16 +7991,16 @@
         <v>248</v>
       </c>
       <c r="G15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M15" t="s">
         <v>241</v>
       </c>
       <c r="N15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -7984,13 +8014,13 @@
         <v>244</v>
       </c>
       <c r="H16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
@@ -8004,13 +8034,13 @@
         <v>249</v>
       </c>
       <c r="H17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M17" t="s">
+        <v>304</v>
+      </c>
+      <c r="N17" t="s">
         <v>305</v>
-      </c>
-      <c r="N17" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -8024,13 +8054,13 @@
         <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M18" t="s">
+        <v>306</v>
+      </c>
+      <c r="N18" t="s">
         <v>307</v>
-      </c>
-      <c r="N18" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
@@ -8044,13 +8074,13 @@
         <v>155</v>
       </c>
       <c r="H19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M19" t="s">
         <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -8061,10 +8091,10 @@
         <v>255</v>
       </c>
       <c r="M20" t="s">
+        <v>309</v>
+      </c>
+      <c r="N20" t="s">
         <v>310</v>
-      </c>
-      <c r="N20" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
@@ -8072,7 +8102,7 @@
         <v>249</v>
       </c>
       <c r="N21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -8092,12 +8122,12 @@
         <v>190</v>
       </c>
       <c r="N22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s">
         <v>71</v>
@@ -8109,15 +8139,15 @@
         <v>74</v>
       </c>
       <c r="M23" t="s">
+        <v>313</v>
+      </c>
+      <c r="N23" t="s">
         <v>314</v>
-      </c>
-      <c r="N23" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -8227,13 +8257,13 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E31" t="s">
         <v>193</v>
       </c>
       <c r="M31" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="P31" t="s">
         <v>154</v>
@@ -8241,7 +8271,7 @@
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E32" t="s">
         <v>194</v>
@@ -8249,7 +8279,7 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E33" t="s">
         <v>195</v>
@@ -8257,26 +8287,26 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
+        <v>274</v>
+      </c>
+      <c r="E34" t="s">
         <v>275</v>
-      </c>
-      <c r="E34" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
+        <v>276</v>
+      </c>
+      <c r="E35" t="s">
         <v>277</v>
-      </c>
-      <c r="E35" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E36" t="s">
         <v>279</v>
-      </c>
-      <c r="E36" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DC1A2E-F0B8-4026-9E65-5E9AA264DA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1486BF8C-27A0-47B4-95F1-47DDF08C1BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51495" yWindow="7095" windowWidth="16410" windowHeight="14505" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="453">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -613,9 +613,6 @@
     <t>iris</t>
   </si>
   <si>
-    <t>door_sime</t>
-  </si>
-  <si>
     <t>se_trans_out|se_trans_in</t>
   </si>
   <si>
@@ -806,36 +803,15 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>S002036</t>
-  </si>
-  <si>
-    <t>S002037</t>
-  </si>
-  <si>
     <t>S002077</t>
   </si>
   <si>
     <t>S002078</t>
   </si>
   <si>
-    <t>S002110</t>
-  </si>
-  <si>
-    <t>S002111</t>
-  </si>
-  <si>
-    <t>S002112</t>
-  </si>
-  <si>
-    <t>bg_hasisita_day</t>
-  </si>
-  <si>
     <t>bg_hasisita_sunset</t>
   </si>
   <si>
-    <t>bg_car_sunset</t>
-  </si>
-  <si>
     <t>Debug Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1045,1182 +1021,769 @@
     <t>메이</t>
   </si>
   <si>
-    <t>후유코는 이미 충분히 열심히 하고 있으니까.</t>
-  </si>
-  <si>
-    <t>가끔은 자신에게 솔직해져도 된다고 생각해.</t>
-  </si>
-  <si>
-    <t>하아… 하아…</t>
-  </si>
-  <si>
     <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼\n엄~청 빠르게 달리면 된다는 거잖아?</t>
   </si>
   <si>
+    <t>fuyuko_sports_2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>flashback</t>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_cry</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫은 표정으로 한숨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱끼고 웃으며 농담</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_jito</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한쪽 팔 올리고 정색</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_smile lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_sad lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 올려서 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 벌리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 손 모아서 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱 끼고 아래 보기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 넓게 들고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 오른손 허리에 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 허리에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleep</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼팔 들고 들썩 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 좁게 들고 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 들고 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 들썩 후 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp2/3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀라서 들썩 (소/대)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 손가락 입에 가져다 대기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 가슴에 짚고 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>touch</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만지지마</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 앞으로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>why</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 갸우뚱 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마따끄</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 머리 갸우뚱 후 절레절레</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 목 뒤 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1과 동일</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞에서 피스</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손만 허리 짚고 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 허리 위로 살짝 올리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 앞에 들썩 후 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 엉덩이 뒤로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭠까?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashback</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸네.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_surp lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003041</t>
+  </si>
+  <si>
+    <t>S003092</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003093</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUDIO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_serious lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_door_sime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_131</t>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히쨩.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004001</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004002</t>
+  </si>
+  <si>
+    <t>분해?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004003</t>
+  </si>
+  <si>
+    <t>bg_ceiling</t>
+  </si>
+  <si>
+    <t>se_sofa_sitdown</t>
+  </si>
+  <si>
+    <t>달리기 시작하면 바로 따라잡을 줄 알았슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004004</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>작년에 그랬던 것처럼.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004005</t>
+  </si>
+  <si>
+    <t>분명, 결승선 직전에 아슬아슬하게 추월했다고 했지.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004006</t>
+  </si>
+  <si>
+    <t>se_sofa_wait</t>
+  </si>
+  <si>
+    <t>저는 후유코쨩이나 메이쨩처럼 연습 같은 거 안 했슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004007</t>
+  </si>
+  <si>
+    <t>해야겠다는 생각도 안 했슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004008</t>
+  </si>
+  <si>
+    <t>만약 졌다고 하더라도,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004009</t>
+  </si>
+  <si>
+    <t>그건 아사히쨩의 책임이 아니야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004010</t>
+  </si>
+  <si>
+    <t>책임…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004011</t>
+  </si>
+  <si>
+    <t>se_sofa_wakeup</t>
+  </si>
+  <si>
+    <t>잠깐 뛰고 오겠슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004012</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004013</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_shy</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>현장 정리 중이니까 안 된다고 해야 되는데…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad2 lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_sports_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>우리는 한 팀이니까!</t>
-  </si>
-  <si>
-    <t>1등을 하는 건 최강이라는 검다.</t>
-  </si>
-  <si>
-    <t>그리고 스트레이라이트는 항상 최강을 목표로 함다.</t>
-  </si>
-  <si>
-    <t>그러니까, 저는 항상 1등을 하고 싶슴다. 스트레이라이트니까요.</t>
-  </si>
-  <si>
-    <t>fuyuko_sports_2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>normal</t>
-  </si>
-  <si>
-    <t>flashback</t>
-  </si>
-  <si>
-    <t>wipe_left</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>싫은 표정으로 한숨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱끼고 웃으며 농담</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_jito</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>한쪽 팔 올리고 정색</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_sad lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 올려서 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 벌리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 손 모아서 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱 끼고 아래 보기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shy1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 넓게 들고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 오른손 허리에 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 허리에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>sleep</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼팔 들고 들썩 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 좁게 들고 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 들고 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 들썩 후 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp2/3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>놀라서 들썩 (소/대)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 손가락 입에 가져다 대기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 가슴에 짚고 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>touch</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>만지지마</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤에서 앞으로</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>why</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 갸우뚱 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>center</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>clean</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마따끄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 머리 갸우뚱 후 절레절레</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 목 뒤 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1과 동일</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞에서 피스</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손만 허리 짚고 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 허리 위로 살짝 올리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 앞에 들썩 후 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 엉덩이 뒤로</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bg_hikaesitu2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004015</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad1 lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이렇게 큰 소리 쳐놓고 진 사람도 있는데 말이야…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004016</t>
+  </si>
+  <si>
+    <t>그 때, 후유코쨩의 표정…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004017</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 두 사람한테…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004018</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무런 도움도…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004019</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 역시 나도 뛰고 올래.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004020</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러니까, 그런 게…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_door_ake</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>어라?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>너, 어디 간다는 말 들었어?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004023</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 별다른 연락은…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_phone_long</t>
+  </si>
+  <si>
+    <t>bg_phone</t>
   </si>
   <si>
     <t>BREAK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>left</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭠까?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>asahi_sports_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유 때문에 1등 못해도 불평하지 마.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>상관 없슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>none</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>제가 다 이길 거니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>저 자신은 어디서 오는 지 몰라.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리들만 믿어, 후유코쨩!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>mei_sports_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩이 안 뛰고 걸어도 될 만큼 차이를 벌려줄게!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그건 역으로 다른 사람들 눈치 보이니까 그만 둬…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_jito</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그리고 이어달리기에 출전하는 그룹들, 다 피지컬 좋기로 유명하니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇게 간단히 이길 수 있는 상대는 아니야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>에, 진심? 그럼 좀 위험한 거 아냐?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>객관적으로 봤을 때, 우리가 1등을 할 수 있을 확률이…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>zoom</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_rouka_run</t>
-  </si>
-  <si>
-    <t>잠깐, 아사히?!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠깐 다른 팀들 좀 보고 오겠슴다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>하아?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아하하… 내가 따라가서 보고 올게.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>right</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>응, 부탁할게.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>원래부터 목적은 두 사람을 돋보이게 하는 거였으니까…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유는 적당히 달리다가, 아사히한테 넘겨주면 돼.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1등같은 건…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bg_runninTrack_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>loop</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_zawa</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스터</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 그룹 대항 이어달리기!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>선수들 일제히 달려나가기 시작합니다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>해설</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>코너를 지나면서 선두 그룹이 치고 나왔네요.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가장 앞에 있는 선수는…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트의 이즈미 메이!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>달리는 폼이 예사롭지 않네요.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 옆에서 바짝 쫓고 있는 ---선수.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 사람의 치열한 선두 싸움이 진행되고 있습니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>직선 코스에서 결착이 날 것 같은데요.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>말씀드리는 순간, 선두 그룹이 직선 코스에 진입!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 떨어진 곳에서 두번째 주자들이 몸을 푸는 모습이 보입니다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bg_runninTrack_1</t>
-  </si>
-  <si>
-    <t>팬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>메이 님!!!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞으로 조금…!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>적당히 달리다가, 아사히한테 넘겨주면 되는데.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_close lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 마지막 스퍼트!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이즈미 선수가 선두를 빼앗겼습니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이런 걸로 1등을 해도, 후유한테는 조금도 이득이…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashback</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BG</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>메이…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아아, 정말.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>너희들 때문에,</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>바보가 옮아 버렸잖아,</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_kansei</t>
-  </si>
-  <si>
-    <t>바통은 두 팀 모두 거의 동시에 넘겨받았습니다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두번째 주자 모두 달려나갑니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>선수들 모두 아주 필사적으로 달리네요.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>동료들과 팬들의 응원 소리 덕분에, 회장은 아주 열정적인 분위기입니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>말씀드리는 순간, 코너에 진입!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>(지금의 후유, 분명 귀엽지 않은 얼굴 하고 있어…)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>(그래도, 뭐 생각보다 차이가 나고 있지 않아서 다행이야.)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>(이대로 아사히한테 넘겨주기만 하면…)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유쨩!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>관객</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>야, 마유즈미 원래 저런 캐릭터였냐?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>관객 2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>평소 성격만 보면 저런 거 안 할것 같은데… 의외네.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 슬슬 직선 코스에 들어왔습니다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 주자의 뒷모습이 보이고 있습니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트가 뒤쳐져 있지만, 역전 불가능한 차이는 아닙니다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 교대 직전!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>선두가 먼저 교대했고, 그 다음으로…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히쨩, 미안…!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_sad lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>격차가…!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>괜찮슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 정도면 충분하니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>하아… 하아…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤는 맡길게, 아사히…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>바통을 넘겨받은 스트레이라이트의 세리자와 아사히!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1등을 맹렬하게 추격!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아, 빠릅니다! 점점 차이가 줄어들고 있습니다!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SNS에서 후유코쨩이 좋은 얼굴을 하고 있다고 화제가 되고 있슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp4 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아하하~ 열심히 달리길 잘 했네~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 왠지 열 받아.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도, 후유코쨩이 열심히 달려주지 않았다면 1등 못했을 테니까~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>진심 덕분에 살았어~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유의 목적은 애초에 1등하는 게 아니었긴 하지만…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭐, 좋은 게 좋은 거려나…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile2 face_close3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>하하, 1등도 하고 좋은 반응도 얻었으니 다행이야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도, 간발의 차였슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩이 주말에 몰래 연습 안 했으면 졌을지도 모름다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>하? 아사히, 네가 그걸 어떻게…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp2 face_anger lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로듀서님이 전화로 알려줬슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩도 나름 열심히 하고 있으니까, 너무 그렇게…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아, 아사히…! 그건…!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로듀서 님~?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코, 들어 줘! 이건…!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>네, 전부 들어드릴 테니, 밖에서 이야기할까요~?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>네…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가버렸네.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가버렸슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_surp lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003001</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003002</t>
-  </si>
-  <si>
-    <t>S003003</t>
-  </si>
-  <si>
-    <t>S003004</t>
-  </si>
-  <si>
-    <t>S003005</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003006</t>
-  </si>
-  <si>
-    <t>S003007</t>
-  </si>
-  <si>
-    <t>S003008</t>
-  </si>
-  <si>
-    <t>S003009</t>
-  </si>
-  <si>
-    <t>S003010</t>
-  </si>
-  <si>
-    <t>S003011</t>
-  </si>
-  <si>
-    <t>S003012</t>
-  </si>
-  <si>
-    <t>S003013</t>
-  </si>
-  <si>
-    <t>S003014</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003015</t>
-  </si>
-  <si>
-    <t>S003016</t>
-  </si>
-  <si>
-    <t>S003017</t>
-  </si>
-  <si>
-    <t>S003018</t>
-  </si>
-  <si>
-    <t>S003019</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003020</t>
-  </si>
-  <si>
-    <t>S003021</t>
-  </si>
-  <si>
-    <t>S003022</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003023</t>
-  </si>
-  <si>
-    <t>S003024</t>
-  </si>
-  <si>
-    <t>S003025</t>
-  </si>
-  <si>
-    <t>S003026</t>
-  </si>
-  <si>
-    <t>S003027</t>
-  </si>
-  <si>
-    <t>S003028</t>
-  </si>
-  <si>
-    <t>S003029</t>
-  </si>
-  <si>
-    <t>S003030</t>
-  </si>
-  <si>
-    <t>S003031</t>
-  </si>
-  <si>
-    <t>S003032</t>
-  </si>
-  <si>
-    <t>S003033</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003034</t>
-  </si>
-  <si>
-    <t>S003035</t>
-  </si>
-  <si>
-    <t>S003036</t>
-  </si>
-  <si>
-    <t>S003037</t>
-  </si>
-  <si>
-    <t>S003038</t>
-  </si>
-  <si>
-    <t>S003039</t>
-  </si>
-  <si>
-    <t>S003040</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003041</t>
-  </si>
-  <si>
-    <t>S003043</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003044</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003045</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003047</t>
-  </si>
-  <si>
-    <t>S003048</t>
-  </si>
-  <si>
-    <t>S003049</t>
-  </si>
-  <si>
-    <t>S003050</t>
-  </si>
-  <si>
-    <t>S003052</t>
-  </si>
-  <si>
-    <t>S003053</t>
-  </si>
-  <si>
-    <t>S003054</t>
-  </si>
-  <si>
-    <t>S003055</t>
-  </si>
-  <si>
-    <t>S003056</t>
-  </si>
-  <si>
-    <t>S003057</t>
-  </si>
-  <si>
-    <t>S003058</t>
-  </si>
-  <si>
-    <t>S003059</t>
-  </si>
-  <si>
-    <t>S003061</t>
-  </si>
-  <si>
-    <t>S003062</t>
-  </si>
-  <si>
-    <t>S003063</t>
-  </si>
-  <si>
-    <t>S003064</t>
-  </si>
-  <si>
-    <t>S003067</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003068</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003069</t>
-  </si>
-  <si>
-    <t>S003070</t>
-  </si>
-  <si>
-    <t>S003071</t>
-  </si>
-  <si>
-    <t>S003072</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003073</t>
-  </si>
-  <si>
-    <t>S003074</t>
-  </si>
-  <si>
-    <t>S003075</t>
-  </si>
-  <si>
-    <t>S003076</t>
-  </si>
-  <si>
-    <t>S003077</t>
-  </si>
-  <si>
-    <t>S003078</t>
-  </si>
-  <si>
-    <t>S003079</t>
-  </si>
-  <si>
-    <t>S003080</t>
-  </si>
-  <si>
-    <t>S003081</t>
-  </si>
-  <si>
-    <t>S003082</t>
-  </si>
-  <si>
-    <t>S003083</t>
-  </si>
-  <si>
-    <t>S003084</t>
-  </si>
-  <si>
-    <t>S003085</t>
-  </si>
-  <si>
-    <t>S003086</t>
-  </si>
-  <si>
-    <t>S003087</t>
-  </si>
-  <si>
-    <t>S003088</t>
-  </si>
-  <si>
-    <t>S003089</t>
-  </si>
-  <si>
-    <t>S003090</t>
-  </si>
-  <si>
-    <t>S003091</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003092</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003093</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_101</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug2 face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>serious face_smile1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_121</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 바보 같아.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트의 팬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_80</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003042</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003046</t>
-  </si>
-  <si>
-    <t>S003051</t>
-  </si>
-  <si>
-    <t>S003060</t>
-  </si>
-  <si>
-    <t>S003065</t>
-  </si>
-  <si>
-    <t>S003066</t>
-  </si>
-  <si>
-    <t>wait2 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUDIO</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>stop</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill1 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_taoreru</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 1등 못하면 용서 안할거니까…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_101</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2 face_serious lip_smile1</t>
+  </si>
+  <si>
+    <t>후유코, 이거.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004026</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔데?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004027</t>
+  </si>
+  <si>
+    <t>두 사람, 지금 트랙에서 달리기 중이라나 봐.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004028</t>
+  </si>
+  <si>
+    <t>메이, 이런 건 네가 말리란 말이야…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004029</t>
+  </si>
+  <si>
+    <t>anger1 face_close3 lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유한테는 큰 소리 쳤으면서,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004030</t>
+  </si>
+  <si>
+    <t>진짜 바보들이라니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004031</t>
+  </si>
+  <si>
+    <t>후유코.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004032</t>
+  </si>
+  <si>
+    <t>알고 있어.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004033</t>
+  </si>
+  <si>
+    <t>smile1 face_serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 가게나 예약해 놔.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004034</t>
+  </si>
+  <si>
+    <t>예약…?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004035</t>
+  </si>
+  <si>
+    <t>담당 아이돌이 열심히 노력해서 1등을 했는데, 회식 정도는 해야 하지 않겠어?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004036</t>
+  </si>
+  <si>
+    <t>그, 그렇네…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004037</t>
+  </si>
+  <si>
+    <t>물론, 프로듀서 님이 쏘시는 거죠?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004038</t>
+  </si>
+  <si>
+    <t>후유는 소고기가 먹고싶은데~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004039</t>
+  </si>
+  <si>
+    <t>… 맡겨줘.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004040</t>
+  </si>
+  <si>
+    <t>1.7</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_serious lip_anger2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_smile</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2400,7 +1963,52 @@
     <cellStyle name="Title" xfId="2" xr:uid="{29B85624-08FE-4DDC-B250-B42E27D66566}"/>
     <cellStyle name="표준" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="16">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2456,52 +2064,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P169" tableType="xml" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P169" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P116" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P116" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type">
+    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name">
+    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text">
+    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="11">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="10">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG">
+    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@CG" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position">
+    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Position" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation">
+    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Animation" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect">
+    <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Effect" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2C783B40-3686-4969-B9A9-74472F998668}" uniqueName="Value" name="Value">
+    <tableColumn id="9" xr3:uid="{2C783B40-3686-4969-B9A9-74472F998668}" uniqueName="Value" name="Value" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7C434785-78DE-4265-81AB-F66F688FF0FE}" uniqueName="Duration" name="Duration">
+    <tableColumn id="10" xr3:uid="{7C434785-78DE-4265-81AB-F66F688FF0FE}" uniqueName="Duration" name="Duration" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Duration" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F6E13514-3140-425B-B085-594C866D0BE4}" uniqueName="SpeakerType" name="SpeakerType">
+    <tableColumn id="11" xr3:uid="{F6E13514-3140-425B-B085-594C866D0BE4}" uniqueName="SpeakerType" name="SpeakerType" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@SpeakerType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{81AD69B1-A848-4447-AE83-9939AF9AADE2}" uniqueName="Track" name="Track">
+    <tableColumn id="12" xr3:uid="{81AD69B1-A848-4447-AE83-9939AF9AADE2}" uniqueName="Track" name="Track" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Track" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{22867833-2213-4504-85D6-75D89AEE42DB}" uniqueName="Volume" name="Volume">
+    <tableColumn id="13" xr3:uid="{22867833-2213-4504-85D6-75D89AEE42DB}" uniqueName="Volume" name="Volume" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Volume" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{09054161-AA65-4541-ADB6-9558E5C44DF4}" uniqueName="SE" name="SE">
+    <tableColumn id="14" xr3:uid="{09054161-AA65-4541-ADB6-9558E5C44DF4}" uniqueName="SE" name="SE" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@SE" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E0ADDA94-13D5-450F-B917-8EC04E0E722E}" uniqueName="Key" name="Key">
+    <tableColumn id="15" xr3:uid="{E0ADDA94-13D5-450F-B917-8EC04E0E722E}" uniqueName="Key" name="Key" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Key" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -2992,7 +2600,7 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -3142,10 +2750,10 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>23</v>
@@ -3159,16 +2767,16 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -3176,36 +2784,36 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="H44" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -3213,54 +2821,54 @@
         <v>19</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3271,7 +2879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
-  <dimension ref="B2:P169"/>
+  <dimension ref="B2:P116"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -3340,7 +2948,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3356,12 +2964,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>567</v>
+        <v>345</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3371,22 +2979,22 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>568</v>
+        <v>346</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>551</v>
+        <v>350</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3395,7 +3003,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3410,22 +3018,22 @@
         <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>90</v>
+        <v>251</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>464</v>
+        <v>341</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3443,22 +3051,22 @@
         <v>89</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>465</v>
+        <v>342</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>565</v>
+        <v>339</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3473,32 +3081,20 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="I8" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -3506,36 +3102,34 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G9" s="7"/>
+        <v>248</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>449</v>
+      </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
+      <c r="P9" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3543,11 +3137,11 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J10" s="7"/>
-      <c r="K10" s="7" t="s">
-        <v>347</v>
-      </c>
+      <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -3559,23 +3153,17 @@
         <v>89</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>569</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -3592,23 +3180,17 @@
         <v>89</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>552</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -3625,23 +3207,17 @@
         <v>89</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H13" t="s">
-        <v>81</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -3658,16 +3234,15 @@
         <v>89</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>471</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -3681,32 +3256,18 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>354</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -3714,32 +3275,20 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="I16" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -3747,92 +3296,62 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>474</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H18" t="s">
-        <v>303</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7" t="s">
+        <v>358</v>
+      </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="I19" s="7"/>
+        <v>319</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L19" s="7"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -3840,20 +3359,26 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="7" t="s">
-        <v>270</v>
-      </c>
+      <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="L20" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -3861,82 +3386,77 @@
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>362</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>361</v>
-      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+      <c r="L21" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="7" t="s">
-        <v>336</v>
-      </c>
+      <c r="P21" s="7"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>364</v>
+      </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="7"/>
+      <c r="L22" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7" t="s">
-        <v>362</v>
-      </c>
+      <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>244</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
@@ -3945,13 +3465,13 @@
         <v>89</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>478</v>
+        <v>367</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -3972,23 +3492,17 @@
         <v>89</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>278</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -4005,23 +3519,14 @@
         <v>89</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H26" t="s">
-        <v>554</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -4038,23 +3543,17 @@
         <v>89</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>90</v>
+        <v>251</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H27" t="s">
-        <v>274</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -4068,41 +3567,53 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="N28" s="7" t="s">
+      <c r="L28" s="7" t="s">
         <v>91</v>
       </c>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>375</v>
+      </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
+      <c r="L29" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
@@ -4119,7 +3630,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7" t="s">
-        <v>270</v>
+        <v>332</v>
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -4131,7 +3642,7 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -4147,12 +3658,12 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -4160,39 +3671,35 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
+      <c r="M32" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>482</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
+      <c r="I33" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -4203,17 +3710,23 @@
         <v>89</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+        <v>378</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -4230,17 +3743,23 @@
         <v>89</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>90</v>
+        <v>251</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+        <v>381</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>382</v>
+      </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
@@ -4254,7 +3773,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -4262,43 +3781,45 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="7" t="s">
-        <v>143</v>
-      </c>
+      <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="M36" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>256</v>
+        <v>401</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="F37" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
+      <c r="L37" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
       <c r="O37" s="7"/>
-      <c r="P37" s="7" t="s">
-        <v>372</v>
-      </c>
+      <c r="P37" s="7"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>567</v>
+        <v>319</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -4306,64 +3827,72 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K38" s="7"/>
+      <c r="I38" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="L38" s="7"/>
-      <c r="M38" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>376</v>
-      </c>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>407</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
       <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="N39" s="7" t="s">
-        <v>376</v>
-      </c>
+      <c r="L39" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>298</v>
+      </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
+      <c r="L40" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
@@ -4371,26 +3900,20 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>485</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
+      <c r="I41" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
@@ -4398,7 +3921,7 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -4407,7 +3930,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
@@ -4415,56 +3938,60 @@
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
+      <c r="P42" s="7" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>256</v>
+        <v>319</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="7" t="s">
-        <v>407</v>
-      </c>
+      <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="K43" s="7"/>
+        <v>300</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
-      <c r="P43" s="7" t="s">
-        <v>372</v>
-      </c>
+      <c r="P43" s="7"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>377</v>
+        <v>251</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>379</v>
+        <v>252</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>188</v>
+      </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4476,13 +4003,13 @@
         <v>89</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>380</v>
+        <v>251</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>487</v>
+        <v>196</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4491,7 +4018,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4500,26 +4027,20 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>488</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
+      <c r="I46" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -4527,53 +4048,43 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>489</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
+      <c r="P47" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>490</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
+      <c r="I48" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="K48" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
@@ -4584,22 +4095,28 @@
         <v>89</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>377</v>
+        <v>251</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
+        <v>389</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>390</v>
+      </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4611,13 +4128,13 @@
         <v>89</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>377</v>
+        <v>251</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>492</v>
+        <v>392</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -4626,7 +4143,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4635,26 +4152,20 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>493</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
+      <c r="I51" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="7"/>
@@ -4662,61 +4173,51 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>494</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
-      <c r="L52" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
+      <c r="P52" s="7" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>495</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>141</v>
+        <v>319</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4725,7 +4226,7 @@
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
@@ -4737,26 +4238,34 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>394</v>
+      </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
       <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
+      <c r="L55" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
-      <c r="P55" s="7" t="s">
-        <v>390</v>
-      </c>
+      <c r="P55" s="7"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>337</v>
+        <v>141</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4765,7 +4274,7 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
@@ -4777,61 +4286,43 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H57" t="s">
-        <v>274</v>
-      </c>
-      <c r="I57" s="7"/>
+        <v>334</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
-      <c r="L57" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
-      <c r="P57" s="7"/>
+      <c r="P57" s="7" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>346</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
+      <c r="I58" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
-      <c r="L58" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
@@ -4842,22 +4333,28 @@
         <v>89</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>557</v>
+        <v>90</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>393</v>
+        <v>335</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
+        <v>340</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H59" t="s">
+        <v>236</v>
+      </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -4866,32 +4363,20 @@
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H60" t="s">
-        <v>395</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="K60" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L60" s="7"/>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
       <c r="O60" s="7"/>
@@ -4899,28 +4384,20 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>346</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
+      <c r="I61" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
-      <c r="L61" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L61" s="7"/>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
@@ -4928,59 +4405,43 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>501</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
-      <c r="L62" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L62" s="7"/>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
+      <c r="P62" s="7" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H63" t="s">
-        <v>340</v>
-      </c>
-      <c r="I63" s="7"/>
+        <v>319</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="K63" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L63" s="7"/>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -4988,20 +4449,26 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>396</v>
+      </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-      <c r="I64" s="7" t="s">
-        <v>399</v>
-      </c>
+      <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
+      <c r="L64" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
@@ -5009,22 +4476,26 @@
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>398</v>
+      </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
-      <c r="I65" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>568</v>
-      </c>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
+      <c r="L65" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
@@ -5032,7 +4503,7 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>567</v>
+        <v>141</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -5041,11 +4512,9 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>407</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
@@ -5055,7 +4524,7 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -5063,9 +4532,7 @@
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-      <c r="I67" s="7" t="s">
-        <v>400</v>
-      </c>
+      <c r="I67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -5073,12 +4540,12 @@
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
       <c r="P67" s="7" t="s">
-        <v>203</v>
+        <v>318</v>
       </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -5086,41 +4553,35 @@
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="N68" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>196</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
+      <c r="I69" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7" t="s">
-        <v>269</v>
-      </c>
+      <c r="L69" s="7"/>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
@@ -5131,22 +4592,28 @@
         <v>89</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>261</v>
+        <v>399</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
+        <v>400</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>450</v>
+      </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7" t="s">
-        <v>269</v>
+        <v>91</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
@@ -5155,20 +4622,22 @@
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
-        <v>141</v>
+        <v>401</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
+      <c r="F71" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
-      <c r="I71" s="7" t="s">
-        <v>399</v>
-      </c>
+      <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
+      <c r="L71" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
@@ -5176,7 +4645,7 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -5184,22 +4653,22 @@
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
-      <c r="I72" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I72" s="7"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
+      <c r="M72" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N72" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O72" s="7"/>
-      <c r="P72" s="7" t="s">
-        <v>205</v>
-      </c>
+      <c r="P72" s="7"/>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -5208,11 +4677,11 @@
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="J73" s="7"/>
       <c r="K73" s="7" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
@@ -5222,80 +4691,64 @@
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>200</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
+      <c r="I74" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
-      <c r="L74" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L74" s="7"/>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="O74" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="P74" s="7"/>
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>201</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
-      <c r="L75" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
-      <c r="P75" s="7"/>
+      <c r="P75" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>202</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="I76" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
@@ -5303,20 +4756,32 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7" t="s">
-        <v>399</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H77" t="s">
+        <v>336</v>
+      </c>
+      <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
+      <c r="L77" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
@@ -5324,7 +4789,7 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -5332,22 +4797,22 @@
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
-      <c r="I78" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="I78" s="7"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
+      <c r="M78" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="N78" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O78" s="7"/>
-      <c r="P78" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="P78" s="7"/>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -5355,12 +4820,10 @@
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="I79" s="7"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
@@ -5373,13 +4836,13 @@
         <v>89</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>263</v>
+        <v>405</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>198</v>
+        <v>406</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
@@ -5388,7 +4851,7 @@
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
@@ -5397,26 +4860,20 @@
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>199</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
+      <c r="I81" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
@@ -5424,28 +4881,34 @@
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
+      <c r="G82" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="J82" s="7"/>
+        <v>326</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>327</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
       <c r="O82" s="7"/>
-      <c r="P82" s="7"/>
+      <c r="P82" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>401</v>
+        <v>319</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5453,20 +4916,22 @@
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
+      <c r="I83" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
+      <c r="K83" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="7" t="s">
-        <v>372</v>
-      </c>
+      <c r="P83" s="7"/>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>567</v>
+        <v>141</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -5474,24 +4939,20 @@
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="7" t="s">
-        <v>568</v>
-      </c>
+      <c r="I84" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
-      <c r="M84" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="N84" s="7" t="s">
-        <v>376</v>
-      </c>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
       <c r="O84" s="7"/>
       <c r="P84" s="7"/>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -5499,33 +4960,39 @@
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
-      <c r="I85" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="I85" s="7"/>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
       <c r="O85" s="7"/>
-      <c r="P85" s="7"/>
+      <c r="P85" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
+        <v>409</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H86" t="s">
+        <v>343</v>
+      </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5542,28 +5009,22 @@
         <v>89</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>90</v>
+        <v>249</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H87" t="s">
-        <v>244</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
@@ -5575,26 +5036,22 @@
         <v>89</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>77</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -5603,7 +5060,7 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -5613,36 +5070,35 @@
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
+      <c r="K89" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
+      <c r="M89" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="N89" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>346</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
       <c r="G90" s="7"/>
-      <c r="I90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
-      <c r="L90" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L90" s="7"/>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
       <c r="O90" s="7"/>
@@ -5650,7 +5106,7 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -5660,43 +5116,31 @@
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
-      <c r="K91" s="7" t="s">
-        <v>347</v>
-      </c>
+      <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
       <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
+      <c r="P91" s="7" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H92" t="s">
-        <v>276</v>
-      </c>
-      <c r="I92" s="7"/>
+        <v>416</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
-      <c r="L92" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L92" s="7"/>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
       <c r="O92" s="7"/>
@@ -5704,20 +5148,26 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
-      <c r="K93" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="L93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
       <c r="O93" s="7"/>
@@ -5731,20 +5181,13 @@
         <v>90</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H94" t="s">
-        <v>571</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
@@ -5758,20 +5201,26 @@
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>422</v>
+      </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
-      <c r="K95" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="L95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
       <c r="O95" s="7"/>
@@ -5779,112 +5228,120 @@
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>373</v>
+        <v>141</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
+      <c r="I96" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
-      <c r="N96" s="7" t="s">
-        <v>347</v>
-      </c>
+      <c r="N96" s="7"/>
       <c r="O96" s="7"/>
-      <c r="P96" s="7" t="s">
-        <v>408</v>
-      </c>
+      <c r="P96" s="7"/>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
-      <c r="I97" s="7" t="s">
-        <v>270</v>
-      </c>
+      <c r="I97" s="7"/>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
-      <c r="P97" s="7"/>
+      <c r="P97" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H98" t="s">
+        <v>236</v>
+      </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
+      <c r="L98" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
-      <c r="P98" s="7" t="s">
-        <v>390</v>
-      </c>
+      <c r="P98" s="7"/>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
-        <v>567</v>
+        <v>416</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>407</v>
-      </c>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
-      <c r="M99" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="N99" s="7" t="s">
-        <v>376</v>
-      </c>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
       <c r="O99" s="7"/>
       <c r="P99" s="7"/>
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7" t="s">
-        <v>318</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H100" t="s">
+        <v>425</v>
+      </c>
+      <c r="I100" s="7"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
-      <c r="L100" s="7"/>
+      <c r="L100" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
       <c r="O100" s="7"/>
@@ -5895,22 +5352,21 @@
         <v>89</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>507</v>
+        <v>427</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -5922,22 +5378,28 @@
         <v>89</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
+        <v>429</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H102" t="s">
+        <v>451</v>
+      </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -5946,26 +5408,17 @@
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>508</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
-      <c r="L103" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="L103" s="7"/>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
       <c r="O103" s="7"/>
@@ -5976,13 +5429,13 @@
         <v>89</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>377</v>
+        <v>249</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>509</v>
+        <v>431</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -5991,7 +5444,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -6003,22 +5456,28 @@
         <v>89</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
+        <v>433</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H105" t="s">
+        <v>434</v>
+      </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -6027,56 +5486,41 @@
     </row>
     <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>511</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
-      <c r="L106" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="N106" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O106" s="7"/>
       <c r="P106" s="7"/>
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H107" t="s">
-        <v>274</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="K107" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L107" s="7"/>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
       <c r="O107" s="7"/>
@@ -6090,14 +5534,16 @@
         <v>90</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
+      <c r="H108" t="s">
+        <v>452</v>
+      </c>
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
@@ -6114,13 +5560,13 @@
         <v>89</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>90</v>
+        <v>249</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>513</v>
+        <v>438</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -6129,7 +5575,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -6141,24 +5587,25 @@
         <v>89</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>391</v>
+        <v>90</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
+        <v>253</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>299</v>
+      </c>
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>418</v>
+        <v>91</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -6170,13 +5617,13 @@
         <v>89</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>419</v>
+        <v>249</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>515</v>
+        <v>442</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -6185,7 +5632,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7" t="s">
-        <v>418</v>
+        <v>254</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -6197,22 +5644,28 @@
         <v>89</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>421</v>
+        <v>90</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
+        <v>444</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H112" t="s">
+        <v>233</v>
+      </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>418</v>
+        <v>91</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -6224,22 +5677,21 @@
         <v>89</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>517</v>
+        <v>446</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
@@ -6251,13 +5703,13 @@
         <v>89</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>377</v>
+        <v>249</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -6266,7 +5718,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
@@ -6275,1448 +5727,47 @@
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>519</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
-      <c r="L115" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
+      <c r="L115" s="7"/>
+      <c r="M115" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N115" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="O115" s="7"/>
       <c r="P115" s="7"/>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>562</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
-      <c r="I116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
-      <c r="L116" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="L116" s="7"/>
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
       <c r="O116" s="7"/>
       <c r="P116" s="7"/>
-    </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B117" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7"/>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
-      <c r="O117" s="7"/>
-      <c r="P117" s="7"/>
-    </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B118" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="7"/>
-      <c r="P118" s="7"/>
-    </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B119" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H119" t="s">
-        <v>429</v>
-      </c>
-      <c r="I119" s="7"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-    </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B120" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-    </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B121" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="7"/>
-    </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="7"/>
-    </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="7"/>
-    </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B124" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="N124" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B125" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-    </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B126" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-    </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B127" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-    </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B128" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-    </row>
-    <row r="129" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B129" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-    </row>
-    <row r="130" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B130" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-    </row>
-    <row r="131" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B131" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-    </row>
-    <row r="132" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B132" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E132" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-    </row>
-    <row r="133" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B133" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-    </row>
-    <row r="134" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B134" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-    </row>
-    <row r="135" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B135" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-    </row>
-    <row r="136" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B136" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P136" s="7"/>
-    </row>
-    <row r="137" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B137" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="138" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B138" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="N138" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="O138" s="7"/>
-      <c r="P138" s="7"/>
-    </row>
-    <row r="139" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B139" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J139" s="7"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-    </row>
-    <row r="140" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B140" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7"/>
-    </row>
-    <row r="141" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B141" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I141" s="7"/>
-      <c r="J141" s="7"/>
-      <c r="K141" s="7"/>
-      <c r="L141" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M141" s="7"/>
-      <c r="N141" s="7"/>
-      <c r="O141" s="7"/>
-      <c r="P141" s="7"/>
-    </row>
-    <row r="142" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B142" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H142" t="s">
-        <v>442</v>
-      </c>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M142" s="7"/>
-      <c r="N142" s="7"/>
-      <c r="O142" s="7"/>
-      <c r="P142" s="7"/>
-    </row>
-    <row r="143" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B143" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="I143" s="7"/>
-      <c r="J143" s="7"/>
-      <c r="K143" s="7"/>
-      <c r="L143" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M143" s="7"/>
-      <c r="N143" s="7"/>
-      <c r="O143" s="7"/>
-      <c r="P143" s="7"/>
-    </row>
-    <row r="144" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B144" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
-      <c r="K144" s="7"/>
-      <c r="L144" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M144" s="7"/>
-      <c r="N144" s="7"/>
-      <c r="O144" s="7"/>
-      <c r="P144" s="7"/>
-    </row>
-    <row r="145" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B145" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D145" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E145" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H145" t="s">
-        <v>276</v>
-      </c>
-      <c r="I145" s="7"/>
-      <c r="J145" s="7"/>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M145" s="7"/>
-      <c r="N145" s="7"/>
-      <c r="O145" s="7"/>
-      <c r="P145" s="7"/>
-    </row>
-    <row r="146" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B146" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E146" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H146" t="s">
-        <v>447</v>
-      </c>
-      <c r="I146" s="7"/>
-      <c r="J146" s="7"/>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M146" s="7"/>
-      <c r="N146" s="7"/>
-      <c r="O146" s="7"/>
-      <c r="P146" s="7"/>
-    </row>
-    <row r="147" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B147" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-    </row>
-    <row r="148" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B148" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="F148" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="I148" s="7"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="7"/>
-    </row>
-    <row r="149" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B149" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-      <c r="I149" s="7"/>
-      <c r="J149" s="7"/>
-      <c r="K149" s="7"/>
-      <c r="L149" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M149" s="7"/>
-      <c r="N149" s="7"/>
-      <c r="O149" s="7"/>
-      <c r="P149" s="7"/>
-    </row>
-    <row r="150" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B150" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C150" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H150" t="s">
-        <v>452</v>
-      </c>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
-      <c r="K150" s="7"/>
-      <c r="L150" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M150" s="7"/>
-      <c r="N150" s="7"/>
-      <c r="O150" s="7"/>
-      <c r="P150" s="7"/>
-    </row>
-    <row r="151" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B151" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
-      <c r="K151" s="7"/>
-      <c r="L151" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M151" s="7"/>
-      <c r="N151" s="7"/>
-      <c r="O151" s="7"/>
-      <c r="P151" s="7"/>
-    </row>
-    <row r="152" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B152" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
-      <c r="K152" s="7"/>
-      <c r="L152" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M152" s="7"/>
-      <c r="N152" s="7"/>
-      <c r="O152" s="7"/>
-      <c r="P152" s="7"/>
-    </row>
-    <row r="153" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B153" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-      <c r="I153" s="7"/>
-      <c r="J153" s="7"/>
-      <c r="K153" s="7"/>
-      <c r="L153" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M153" s="7"/>
-      <c r="N153" s="7"/>
-      <c r="O153" s="7"/>
-      <c r="P153" s="7"/>
-    </row>
-    <row r="154" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B154" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="F154" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G154" s="7"/>
-      <c r="H154" s="7"/>
-      <c r="I154" s="7"/>
-      <c r="J154" s="7"/>
-      <c r="K154" s="7"/>
-      <c r="L154" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="M154" s="7"/>
-      <c r="N154" s="7"/>
-      <c r="O154" s="7"/>
-      <c r="P154" s="7"/>
-    </row>
-    <row r="155" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B155" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="F155" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H155" t="s">
-        <v>241</v>
-      </c>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7"/>
-      <c r="K155" s="7"/>
-      <c r="L155" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M155" s="7"/>
-      <c r="N155" s="7"/>
-      <c r="O155" s="7"/>
-      <c r="P155" s="7"/>
-    </row>
-    <row r="156" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B156" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
-      <c r="I156" s="7"/>
-      <c r="J156" s="7"/>
-      <c r="K156" s="7"/>
-      <c r="L156" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="M156" s="7"/>
-      <c r="N156" s="7"/>
-      <c r="O156" s="7"/>
-      <c r="P156" s="7"/>
-    </row>
-    <row r="157" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B157" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H157" t="s">
-        <v>189</v>
-      </c>
-      <c r="I157" s="7"/>
-      <c r="J157" s="7"/>
-      <c r="K157" s="7"/>
-      <c r="L157" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M157" s="7"/>
-      <c r="N157" s="7"/>
-      <c r="O157" s="7"/>
-      <c r="P157" s="7"/>
-    </row>
-    <row r="158" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B158" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
-      <c r="K158" s="7"/>
-      <c r="L158" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="M158" s="7"/>
-      <c r="N158" s="7"/>
-      <c r="O158" s="7"/>
-      <c r="P158" s="7"/>
-    </row>
-    <row r="159" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B159" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="7"/>
-      <c r="I159" s="7"/>
-      <c r="J159" s="7"/>
-      <c r="K159" s="7"/>
-      <c r="L159" s="7"/>
-      <c r="M159" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="N159" s="7"/>
-      <c r="O159" s="7"/>
-      <c r="P159" s="7"/>
-    </row>
-    <row r="160" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B160" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
-      <c r="I160" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="J160" s="7"/>
-      <c r="K160" s="7"/>
-      <c r="L160" s="7"/>
-      <c r="M160" s="7"/>
-      <c r="N160" s="7"/>
-      <c r="O160" s="7"/>
-      <c r="P160" s="7"/>
-    </row>
-    <row r="161" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B161" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="7"/>
-      <c r="K161" s="7"/>
-      <c r="L161" s="7"/>
-      <c r="M161" s="7"/>
-      <c r="N161" s="7"/>
-      <c r="O161" s="7"/>
-      <c r="P161" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="162" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B162" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-      <c r="G162" s="7"/>
-      <c r="H162" s="7"/>
-      <c r="I162" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J162" s="7"/>
-      <c r="K162" s="7"/>
-      <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
-      <c r="N162" s="7"/>
-      <c r="O162" s="7"/>
-      <c r="P162" s="7"/>
-    </row>
-    <row r="163" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B163" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G163" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H163" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="I163" s="7"/>
-      <c r="J163" s="7"/>
-      <c r="K163" s="7"/>
-      <c r="L163" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M163" s="7"/>
-      <c r="N163" s="7"/>
-      <c r="O163" s="7"/>
-      <c r="P163" s="7"/>
-    </row>
-    <row r="164" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B164" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C164" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="E164" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="F164" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H164" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="I164" s="7"/>
-      <c r="J164" s="7"/>
-      <c r="K164" s="7"/>
-      <c r="L164" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M164" s="7"/>
-      <c r="N164" s="7"/>
-      <c r="O164" s="7"/>
-      <c r="P164" s="7"/>
-    </row>
-    <row r="165" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B165" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-      <c r="I165" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="J165" s="7"/>
-      <c r="K165" s="7"/>
-      <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
-      <c r="N165" s="7"/>
-      <c r="O165" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P165" s="7"/>
-    </row>
-    <row r="166" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
-      <c r="K166" s="7"/>
-      <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
-      <c r="N166" s="7"/>
-      <c r="O166" s="7"/>
-      <c r="P166" s="7"/>
-    </row>
-    <row r="167" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
-      <c r="K167" s="7"/>
-      <c r="L167" s="7"/>
-      <c r="M167" s="7"/>
-      <c r="N167" s="7"/>
-      <c r="O167" s="7"/>
-      <c r="P167" s="7"/>
-    </row>
-    <row r="168" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
-      <c r="I168" s="7"/>
-      <c r="J168" s="7"/>
-      <c r="K168" s="7"/>
-      <c r="L168" s="7"/>
-      <c r="M168" s="7"/>
-      <c r="N168" s="7"/>
-      <c r="O168" s="7"/>
-      <c r="P168" s="7"/>
-    </row>
-    <row r="169" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
-      <c r="I169" s="7"/>
-      <c r="J169" s="7"/>
-      <c r="K169" s="7"/>
-      <c r="L169" s="7"/>
-      <c r="M169" s="7"/>
-      <c r="N169" s="7"/>
-      <c r="O169" s="7"/>
-      <c r="P169" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7748,59 +5799,59 @@
         <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G3" t="s">
         <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="M3" t="s">
         <v>83</v>
       </c>
       <c r="N3" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G4" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="M4" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="N4" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H5" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="M5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="N5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -7808,39 +5859,39 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G6" t="s">
         <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="M6" t="s">
         <v>77</v>
       </c>
       <c r="N6" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G7" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="H7" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="M7" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="N7" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
@@ -7848,261 +5899,261 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="H8" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="M8" t="s">
         <v>81</v>
       </c>
       <c r="N8" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
         <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="M9" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="N9" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G10" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="H10" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="M10" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="N10" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G11" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="H11" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="M11" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="N11" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="M12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N12" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G13" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H13" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="M13" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="N13" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H14" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="M14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="N14" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G15" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="H15" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="M15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="N15" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H16" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="M16" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="N16" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G17" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H17" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="M17" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="N17" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H18" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="M18" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="N18" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H19" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="M19" t="s">
         <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="M20" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="N20" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -8119,15 +6170,15 @@
         <v>73</v>
       </c>
       <c r="M22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E23" t="s">
         <v>71</v>
@@ -8139,15 +6190,15 @@
         <v>74</v>
       </c>
       <c r="M23" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="N23" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -8161,16 +6212,16 @@
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G25" t="s">
+        <v>145</v>
+      </c>
+      <c r="J25" t="s">
         <v>146</v>
-      </c>
-      <c r="J25" t="s">
-        <v>147</v>
       </c>
       <c r="M25" t="s">
         <v>92</v>
@@ -8181,16 +6232,16 @@
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" t="s">
         <v>152</v>
-      </c>
-      <c r="J26" t="s">
-        <v>153</v>
       </c>
       <c r="M26" t="s">
         <v>77</v>
@@ -8201,10 +6252,10 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" t="s">
         <v>157</v>
-      </c>
-      <c r="E27" t="s">
-        <v>158</v>
       </c>
       <c r="M27" t="s">
         <v>79</v>
@@ -8218,7 +6269,7 @@
         <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M28" t="s">
         <v>81</v>
@@ -8229,10 +6280,10 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
         <v>187</v>
-      </c>
-      <c r="E29" t="s">
-        <v>188</v>
       </c>
       <c r="M29" t="s">
         <v>83</v>
@@ -8243,70 +6294,70 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s">
+        <v>147</v>
+      </c>
+      <c r="P30" t="s">
         <v>148</v>
-      </c>
-      <c r="P30" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s">
-        <v>566</v>
+        <v>344</v>
       </c>
       <c r="P31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="E34" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="E36" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -8543,74 +6594,74 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>159</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F10">
         <v>71</v>
@@ -8618,10 +6669,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F11">
         <v>73</v>
@@ -8629,7 +6680,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -8637,7 +6688,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F13">
         <v>77</v>
@@ -8645,10 +6696,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="F14">
         <v>88</v>
@@ -8656,10 +6707,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -8667,7 +6718,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -8675,7 +6726,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F17">
         <v>101</v>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1486BF8C-27A0-47B4-95F1-47DDF08C1BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA420E8-04F9-4A1C-BA37-4ACC630A7901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="454">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -270,10 +270,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>* BGM과SE는 타입만 다르고 엘리멘트는 동일합니다. 파일 명의 시작만 BGM_/SE_ 규칙에 맞게 작성해주시면 됩니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1784,6 +1780,14 @@
   </si>
   <si>
     <t>anger3 face_serious lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다. DialogBox 비표시를 원할 때에는 0으로 입력합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2067,25 +2071,25 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P116" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
   <autoFilter ref="B2:P116" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="11">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="10">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@CG" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Position" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Animation" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect" dataDxfId="7">
@@ -2595,12 +2599,12 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -2637,12 +2641,12 @@
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
@@ -2691,17 +2695,17 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
@@ -2739,21 +2743,21 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P39" s="6"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>23</v>
@@ -2767,16 +2771,16 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -2784,36 +2788,36 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -2821,54 +2825,54 @@
         <v>19</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2948,7 +2952,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2964,12 +2968,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2979,22 +2983,22 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3003,7 +3007,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3015,31 +3019,31 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -3048,31 +3052,31 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -3081,7 +3085,7 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3090,7 +3094,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -3102,21 +3106,21 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -3124,12 +3128,12 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3138,7 +3142,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -3150,16 +3154,16 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>353</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -3168,7 +3172,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3177,16 +3181,16 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -3195,7 +3199,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3204,16 +3208,16 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>356</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -3222,7 +3226,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -3231,13 +3235,13 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3247,7 +3251,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -3256,7 +3260,7 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -3275,7 +3279,7 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -3284,7 +3288,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -3296,7 +3300,7 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -3312,12 +3316,12 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -3330,7 +3334,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -3338,7 +3342,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -3347,7 +3351,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -3359,16 +3363,16 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>360</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -3377,7 +3381,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -3386,16 +3390,16 @@
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>361</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>362</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3404,7 +3408,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -3413,16 +3417,16 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -3431,7 +3435,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -3440,7 +3444,7 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -3452,26 +3456,26 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>367</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -3480,7 +3484,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -3489,16 +3493,16 @@
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>368</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>369</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -3507,7 +3511,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -3516,13 +3520,13 @@
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -3531,7 +3535,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -3540,16 +3544,16 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -3558,7 +3562,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -3567,16 +3571,16 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D28" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>373</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -3585,7 +3589,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -3594,16 +3598,16 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -3612,7 +3616,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
@@ -3621,7 +3625,7 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3630,7 +3634,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -3642,7 +3646,7 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -3658,12 +3662,12 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -3676,17 +3680,17 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -3695,7 +3699,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -3707,31 +3711,31 @@
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="F34" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="H34" s="7" t="s">
         <v>378</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>379</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3740,31 +3744,31 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -3773,7 +3777,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -3786,23 +3790,23 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -3810,7 +3814,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>323</v>
+        <v>453</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -3819,7 +3823,7 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -3828,11 +3832,11 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -3842,31 +3846,31 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D39" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="F39" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>385</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -3875,13 +3879,13 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -3891,7 +3895,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -3900,7 +3904,7 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -3909,7 +3913,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
@@ -3921,7 +3925,7 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -3930,7 +3934,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
@@ -3939,12 +3943,12 @@
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
       <c r="P42" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -3953,11 +3957,11 @@
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J43" s="7"/>
       <c r="K43" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
@@ -3967,31 +3971,31 @@
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>252</v>
-      </c>
       <c r="E44" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4000,16 +4004,16 @@
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4018,7 +4022,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4027,7 +4031,7 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -4036,7 +4040,7 @@
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
       <c r="I46" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
@@ -4048,7 +4052,7 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -4064,12 +4068,12 @@
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
       <c r="P47" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -4078,11 +4082,11 @@
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
       <c r="I48" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J48" s="7"/>
       <c r="K48" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
@@ -4092,31 +4096,31 @@
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="F49" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>390</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4125,16 +4129,16 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D50" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -4143,7 +4147,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4152,7 +4156,7 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -4161,7 +4165,7 @@
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
       <c r="I51" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
@@ -4173,7 +4177,7 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -4189,12 +4193,12 @@
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
       <c r="P52" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4207,17 +4211,17 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4226,7 +4230,7 @@
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
@@ -4238,16 +4242,16 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -4256,7 +4260,7 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -4265,7 +4269,7 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4274,7 +4278,7 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
@@ -4286,7 +4290,7 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -4295,7 +4299,7 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
@@ -4304,12 +4308,12 @@
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
       <c r="P57" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -4318,7 +4322,7 @@
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
@@ -4330,31 +4334,31 @@
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D59" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -4363,7 +4367,7 @@
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -4374,7 +4378,7 @@
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
@@ -4384,7 +4388,7 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -4393,7 +4397,7 @@
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
@@ -4405,7 +4409,7 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -4421,12 +4425,12 @@
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
       <c r="P62" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -4435,11 +4439,11 @@
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J63" s="7"/>
       <c r="K63" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
@@ -4449,16 +4453,16 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D64" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>396</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -4467,7 +4471,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
@@ -4476,16 +4480,16 @@
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D65" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -4494,7 +4498,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
@@ -4503,7 +4507,7 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -4512,7 +4516,7 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
@@ -4524,7 +4528,7 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -4540,12 +4544,12 @@
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
       <c r="P67" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -4558,17 +4562,17 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c r="M68" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -4577,7 +4581,7 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
@@ -4589,31 +4593,31 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D70" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>400</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
@@ -4622,13 +4626,13 @@
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -4636,7 +4640,7 @@
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7" t="s">
-        <v>323</v>
+        <v>453</v>
       </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
@@ -4645,7 +4649,7 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -4658,17 +4662,17 @@
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -4677,11 +4681,11 @@
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J73" s="7"/>
       <c r="K73" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
@@ -4691,7 +4695,7 @@
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -4700,7 +4704,7 @@
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
@@ -4708,13 +4712,13 @@
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P74" s="7"/>
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -4730,12 +4734,12 @@
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
       <c r="P75" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -4744,7 +4748,7 @@
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
@@ -4756,31 +4760,31 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D77" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>403</v>
-      </c>
       <c r="F77" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
@@ -4789,7 +4793,7 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -4802,17 +4806,17 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c r="M78" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -4823,7 +4827,7 @@
       <c r="I79" s="7"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
@@ -4833,16 +4837,16 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D80" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E80" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>406</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
@@ -4851,7 +4855,7 @@
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
@@ -4860,7 +4864,7 @@
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -4869,7 +4873,7 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
@@ -4881,21 +4885,21 @@
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
       <c r="G82" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="J82" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>327</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4903,12 +4907,12 @@
       <c r="N82" s="7"/>
       <c r="O82" s="7"/>
       <c r="P82" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -4917,11 +4921,11 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J83" s="7"/>
       <c r="K83" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
@@ -4931,7 +4935,7 @@
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -4940,7 +4944,7 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
@@ -4952,7 +4956,7 @@
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -4968,36 +4972,36 @@
       <c r="N85" s="7"/>
       <c r="O85" s="7"/>
       <c r="P85" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C86" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D86" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E86" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>409</v>
-      </c>
       <c r="F86" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H86" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
@@ -5006,16 +5010,16 @@
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D87" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>410</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>411</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -5024,7 +5028,7 @@
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
@@ -5033,16 +5037,16 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D88" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>413</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -5051,7 +5055,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -5060,7 +5064,7 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -5071,21 +5075,21 @@
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N89" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -5094,7 +5098,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
@@ -5106,7 +5110,7 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -5122,12 +5126,12 @@
       <c r="N91" s="7"/>
       <c r="O91" s="7"/>
       <c r="P91" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -5136,7 +5140,7 @@
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
@@ -5148,16 +5152,16 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D93" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="E93" s="7" t="s">
         <v>417</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>418</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -5166,7 +5170,7 @@
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
       <c r="L93" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
@@ -5175,16 +5179,16 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C94" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D94" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E94" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>420</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -5192,7 +5196,7 @@
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
@@ -5201,16 +5205,16 @@
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D95" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E95" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>422</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -5219,7 +5223,7 @@
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
       <c r="L95" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
@@ -5228,7 +5232,7 @@
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -5236,7 +5240,7 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
@@ -5248,7 +5252,7 @@
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -5263,33 +5267,33 @@
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
       <c r="P97" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D98" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>299</v>
-      </c>
       <c r="H98" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
@@ -5298,7 +5302,7 @@
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -5316,31 +5320,31 @@
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C100" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D100" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E100" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="F100" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H100" t="s">
         <v>424</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="H100" t="s">
-        <v>425</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
@@ -5349,16 +5353,16 @@
     </row>
     <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C101" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D101" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E101" s="7" t="s">
         <v>426</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -5366,7 +5370,7 @@
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -5375,31 +5379,31 @@
     </row>
     <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C102" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D102" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="E102" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>429</v>
-      </c>
       <c r="F102" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H102" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -5408,7 +5412,7 @@
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -5426,16 +5430,16 @@
     </row>
     <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D104" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="E104" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -5444,7 +5448,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -5453,31 +5457,31 @@
     </row>
     <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C105" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D105" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E105" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="F105" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H105" t="s">
         <v>433</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="H105" t="s">
-        <v>434</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -5486,7 +5490,7 @@
     </row>
     <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -5498,17 +5502,17 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N106" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O106" s="7"/>
       <c r="P106" s="7"/>
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -5518,7 +5522,7 @@
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
@@ -5528,27 +5532,27 @@
     </row>
     <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C108" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D108" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E108" s="7" t="s">
         <v>435</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
       <c r="H108" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
@@ -5557,16 +5561,16 @@
     </row>
     <row r="109" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B109" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D109" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="E109" s="7" t="s">
         <v>437</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>438</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -5575,7 +5579,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -5584,28 +5588,31 @@
     </row>
     <row r="110" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B110" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C110" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D110" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E110" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>440</v>
-      </c>
       <c r="F110" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
+      </c>
+      <c r="H110" t="s">
+        <v>258</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -5614,16 +5621,16 @@
     </row>
     <row r="111" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B111" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D111" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E111" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>442</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -5632,7 +5639,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -5641,31 +5648,31 @@
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B112" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C112" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D112" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E112" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>444</v>
-      </c>
       <c r="F112" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -5674,16 +5681,16 @@
     </row>
     <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C113" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="D113" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="E113" s="7" t="s">
         <v>445</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>446</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
@@ -5691,7 +5698,7 @@
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
@@ -5700,16 +5707,16 @@
     </row>
     <row r="114" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B114" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D114" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="E114" s="7" t="s">
         <v>447</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>448</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -5718,7 +5725,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
@@ -5727,7 +5734,7 @@
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -5740,17 +5747,17 @@
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N115" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="7"/>
       <c r="P115" s="7"/>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -5759,7 +5766,7 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
@@ -5785,579 +5792,579 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" t="s">
         <v>220</v>
       </c>
-      <c r="C4" t="s">
-        <v>221</v>
-      </c>
       <c r="G4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H4" t="s">
+        <v>301</v>
+      </c>
+      <c r="M4" t="s">
+        <v>268</v>
+      </c>
+      <c r="N4" t="s">
         <v>269</v>
-      </c>
-      <c r="H4" t="s">
-        <v>302</v>
-      </c>
-      <c r="M4" t="s">
-        <v>269</v>
-      </c>
-      <c r="N4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" t="s">
         <v>222</v>
       </c>
-      <c r="C5" t="s">
-        <v>223</v>
-      </c>
       <c r="G5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
         <v>225</v>
       </c>
-      <c r="C7" t="s">
-        <v>226</v>
-      </c>
       <c r="G7" t="s">
+        <v>304</v>
+      </c>
+      <c r="H7" t="s">
         <v>305</v>
       </c>
-      <c r="H7" t="s">
-        <v>306</v>
-      </c>
       <c r="M7" t="s">
+        <v>272</v>
+      </c>
+      <c r="N7" t="s">
         <v>273</v>
-      </c>
-      <c r="N7" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M9" t="s">
+        <v>275</v>
+      </c>
+      <c r="N9" t="s">
         <v>276</v>
-      </c>
-      <c r="N9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
         <v>229</v>
       </c>
-      <c r="C10" t="s">
-        <v>230</v>
-      </c>
       <c r="G10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M10" t="s">
+        <v>277</v>
+      </c>
+      <c r="N10" t="s">
         <v>278</v>
-      </c>
-      <c r="N10" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" t="s">
         <v>231</v>
       </c>
-      <c r="C11" t="s">
-        <v>232</v>
-      </c>
       <c r="G11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
+        <v>279</v>
+      </c>
+      <c r="N11" t="s">
         <v>280</v>
-      </c>
-      <c r="N11" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
         <v>233</v>
       </c>
-      <c r="C12" t="s">
-        <v>234</v>
-      </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" t="s">
         <v>236</v>
       </c>
-      <c r="C13" t="s">
-        <v>237</v>
-      </c>
       <c r="G13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" t="s">
         <v>239</v>
       </c>
-      <c r="C15" t="s">
-        <v>240</v>
-      </c>
       <c r="G15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M17" t="s">
+        <v>286</v>
+      </c>
+      <c r="N17" t="s">
         <v>287</v>
-      </c>
-      <c r="N17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M18" t="s">
+        <v>288</v>
+      </c>
+      <c r="N18" t="s">
         <v>289</v>
-      </c>
-      <c r="N18" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M20" t="s">
+        <v>291</v>
+      </c>
+      <c r="N20" t="s">
         <v>292</v>
-      </c>
-      <c r="N20" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M23" t="s">
+        <v>295</v>
+      </c>
+      <c r="N23" t="s">
         <v>296</v>
-      </c>
-      <c r="N23" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" t="s">
         <v>87</v>
-      </c>
-      <c r="J24" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" t="s">
+        <v>144</v>
+      </c>
+      <c r="J25" t="s">
         <v>145</v>
       </c>
-      <c r="J25" t="s">
-        <v>146</v>
-      </c>
       <c r="M25" t="s">
+        <v>91</v>
+      </c>
+      <c r="P25" t="s">
         <v>92</v>
-      </c>
-      <c r="P25" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G26" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" t="s">
         <v>151</v>
       </c>
-      <c r="J26" t="s">
-        <v>152</v>
-      </c>
       <c r="M26" t="s">
+        <v>76</v>
+      </c>
+      <c r="P26" t="s">
         <v>77</v>
-      </c>
-      <c r="P26" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" t="s">
         <v>156</v>
       </c>
-      <c r="E27" t="s">
-        <v>157</v>
-      </c>
       <c r="M27" t="s">
+        <v>78</v>
+      </c>
+      <c r="P27" t="s">
         <v>79</v>
-      </c>
-      <c r="P27" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M28" t="s">
+        <v>80</v>
+      </c>
+      <c r="P28" t="s">
         <v>81</v>
-      </c>
-      <c r="P28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" t="s">
         <v>186</v>
       </c>
-      <c r="E29" t="s">
-        <v>187</v>
-      </c>
       <c r="M29" t="s">
+        <v>82</v>
+      </c>
+      <c r="P29" t="s">
         <v>83</v>
-      </c>
-      <c r="P29" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s">
+        <v>146</v>
+      </c>
+      <c r="P30" t="s">
         <v>147</v>
-      </c>
-      <c r="P30" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" t="s">
         <v>257</v>
-      </c>
-      <c r="E34" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
+        <v>258</v>
+      </c>
+      <c r="E35" t="s">
         <v>259</v>
-      </c>
-      <c r="E35" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" t="s">
         <v>261</v>
-      </c>
-      <c r="E36" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6373,212 +6380,212 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
         <v>105</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
         <v>109</v>
       </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
       <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
         <v>136</v>
-      </c>
-      <c r="E15" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
         <v>116</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
         <v>121</v>
       </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
         <v>124</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -6594,74 +6601,74 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>168</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F10">
         <v>71</v>
@@ -6669,10 +6676,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F11">
         <v>73</v>
@@ -6680,7 +6687,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -6688,7 +6695,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F13">
         <v>77</v>
@@ -6696,10 +6703,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="F14">
         <v>88</v>
@@ -6707,10 +6714,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -6718,7 +6725,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -6726,7 +6733,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F17">
         <v>101</v>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA420E8-04F9-4A1C-BA37-4ACC630A7901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB0CE12-920D-41C4-8B2E-E05D0BBBB7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="451">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -399,9 +399,6 @@
     <t>TEXT</t>
   </si>
   <si>
-    <t>후유코</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -597,21 +594,9 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>TRANSITION</t>
-  </si>
-  <si>
     <t>shrug face_serious lip_sad</t>
   </si>
   <si>
-    <t>iris</t>
-  </si>
-  <si>
-    <t>se_trans_out|se_trans_in</t>
-  </si>
-  <si>
     <t>wait1 face_serious lip_anger2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -799,15 +784,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>S002077</t>
-  </si>
-  <si>
-    <t>S002078</t>
-  </si>
-  <si>
-    <t>bg_hasisita_sunset</t>
-  </si>
-  <si>
     <t>Debug Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1008,794 +984,834 @@
     <t>BG</t>
   </si>
   <si>
+    <t>아사히</t>
+  </si>
+  <si>
+    <t>메이</t>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_cry</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫은 표정으로 한숨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱끼고 웃으며 농담</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_jito</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한쪽 팔 올리고 정색</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_smile lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_sad lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>face_jito lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 올려서 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 벌리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 손 모아서 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔짱 끼고 아래 보기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 넓게 들고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 가슴에 오른손 허리에 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손 허리에 짚고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleep</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼팔 들고 들썩 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔 좁게 들고 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양 팔 들고 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 들썩 후 손가락</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp2/3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀라서 들썩 (소/대)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 손가락 입에 가져다 대기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 가슴에 짚고 갸우뚱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>touch</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만지지마</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 앞으로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>why</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 올리고 갸우뚱 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마따끄</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 머리 갸우뚱 후 절레절레</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 목 뒤 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1과 동일</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞에서 피스</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩 후 오른손 입 앞</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손만 허리 짚고 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 허리 위로 살짝 올리고 들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 입 앞에 들썩 후 기울어짐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른손 엉덩이 뒤로</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUDIO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다. DialogBox 비표시를 원할 때에는 0으로 입력합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 뭠까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_normal_sr2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어제 이야기했잖아, 아사히쨩?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT002</t>
+  </si>
+  <si>
+    <t>fuyuko_normal_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에 개장하는 극장에 대한 PR 오퍼래.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT003</t>
+  </si>
+  <si>
+    <t>mei_normal_8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤에-</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT004</t>
+  </si>
+  <si>
+    <t>wait3 face_wait lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>straylight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 사람 다 준비 됐어? 인사할게?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요. 저희는,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트입니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT007 OT008 OT009</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>개장 축하드립니다~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT011</t>
+  </si>
+  <si>
+    <t>smile4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>축하드림다~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT012</t>
+  </si>
+  <si>
+    <t>축하드립니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT013</t>
+  </si>
+  <si>
+    <t>smile3 face_smile2 lip_smile1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT014</t>
+  </si>
+  <si>
+    <t>이 작품은 빛의…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT015</t>
+  </si>
+  <si>
+    <t>이거 뭐라고 읽는 검까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT016</t>
+  </si>
+  <si>
+    <t>OT017</t>
+  </si>
+  <si>
+    <t>smile1 face_serious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(이 자식, 그렇게 대본 읽어두라고 했는데…!)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT018</t>
+  </si>
+  <si>
+    <t>관성이라는 뜻이라고 함다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT019</t>
+  </si>
+  <si>
+    <t>아, 그러고보니 스시 1접시 할 때의 한자랑 닮았슴다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT020</t>
+  </si>
+  <si>
+    <t>오, 확실히…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT021</t>
+  </si>
+  <si>
+    <t>surp2 lip_smile2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛에는 원래 관성이 없는데, 빛의 관성이라니 무슨 의미일지 궁금하네요~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT022</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 후유코쨩이 제 대사 뺏어갔슴다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT023</t>
+  </si>
+  <si>
+    <t>두 사람은 촬영하면서 기억나는 장면이라던가, 있어?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT024</t>
+  </si>
+  <si>
+    <t>think face_smile lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT025</t>
+  </si>
+  <si>
+    <t>smile2 face_serious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT026</t>
+  </si>
+  <si>
+    <t>뛰는 장면을 찍을 때, 두 시간 넘게 계속 뛰니까 힘들었슴다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT027</t>
+  </si>
+  <si>
+    <t>anger1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완성된 장면을 봤을 때, 뛰는 건 10분도 안나왔는데…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT028</t>
+  </si>
+  <si>
+    <t>아사히쨩, 좋았던 기억은…?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT029</t>
+  </si>
+  <si>
+    <t>surp1 face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>음…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT030</t>
+  </si>
+  <si>
+    <t>아, 끝나고 먹은 소고기가 맛있었슴다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT031</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>후, 후유도 예전에 대운동회에 나갔을 때의 생각이 났어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT032</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile4 face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 때와 비교하면, 지금은 굉장히 많은 게 달라졌구나… 하고.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT033</t>
+  </si>
+  <si>
+    <t>OT034</t>
+  </si>
+  <si>
+    <t>어떤 건 전혀 달라지지 않았구나, 하고.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT035</t>
+  </si>
+  <si>
+    <t>만약 그 시절의 대운동회 방송을 기억하시는 분들이 계신다면, \n이번의 저희의 모습과 비교해서 보시는 것도 재밌을 것 같아요!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT036</t>
+  </si>
+  <si>
     <t>프로듀서</t>
-  </si>
-  <si>
-    <t>아사히</t>
-  </si>
-  <si>
-    <t>메이</t>
-  </si>
-  <si>
-    <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼\n엄~청 빠르게 달리면 된다는 거잖아?</t>
-  </si>
-  <si>
-    <t>fuyuko_sports_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(슬슬 마무리하자)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도, 재밌었슴다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT037</t>
+  </si>
+  <si>
+    <t>응, 그렇네.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT038</t>
+  </si>
+  <si>
+    <t>네, 저희가 이렇게 재미있게 촬영한 작품과, 이번에 새로 개장하는 극장까지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT039</t>
+  </si>
+  <si>
+    <t>skill1 face_smile lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>모두들, 많은 관심 부탁드립니다~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT040</t>
+  </si>
+  <si>
+    <t>구독이랑, 좋아요도 부탁드림다~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT041</t>
+  </si>
+  <si>
+    <t>아사히쨩? 유튜브 같은 게 아니니까…!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT042</t>
+  </si>
+  <si>
+    <t>shrug face_bitter_smile lip_bitter_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글도 많이 달아주세요.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT043</t>
+  </si>
+  <si>
+    <t>정말~ 메이쨩까지!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT044</t>
+  </si>
+  <si>
+    <t>OT045</t>
+  </si>
+  <si>
+    <t>anger3 face_smile lip_smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이라이트였습니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT046 OT047 OT048</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>normal</t>
-  </si>
-  <si>
-    <t>flashback</t>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_cry</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>싫은 표정으로 한숨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱끼고 웃으며 농담</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_jito</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>한쪽 팔 올리고 정색</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_smile lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_sad lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>face_jito lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 올려서 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 벌리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 손 모아서 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔짱 끼고 아래 보기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shy1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 넓게 들고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 가슴에 오른손 허리에 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손 허리에 짚고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>sleep</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼팔 들고 들썩 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>팔 좁게 들고 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>양 팔 들고 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 들썩 후 손가락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp2/3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>놀라서 들썩 (소/대)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 손가락 입에 가져다 대기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 가슴에 짚고 갸우뚱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>touch</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>만지지마</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤에서 앞으로</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>why</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 올리고 갸우뚱 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>center</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고했어. 이대로 써도 될 것 같아.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT049</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히, 후유가 어제부터 대본 훑어보라고 했지!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT050</t>
+  </si>
+  <si>
+    <t>우왓, 왜 잡으러 오는 검까!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT051</t>
+  </si>
+  <si>
+    <t>메이! 그 쪽으로 가면 잡아!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT052</t>
+  </si>
+  <si>
+    <t>아하하, 후유코쨩. 일단 진정하자~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT053</t>
+  </si>
+  <si>
+    <t>아사히, 너 잡히기만 해!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OT054</t>
+  </si>
+  <si>
+    <t>smile2 face_wait lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>개장하고 가장 첫 상영은, \n저희 스트레이라이트가 출연한 InertiaLucis라는 작품이라고 합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>'관성' 이라고 읽는 거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_ira</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile3 lip_surp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>surp2 face_wait lip_smile2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>se_rouka_run</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>처음에 메이쨩이 말했듯이, 이번에 새롭게 개장하신다는 소식을 듣고\n축하 영상을 보내드립니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>why face_anger lip_anger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예전에 운동회에 나갔을 땐 서로 다른 팀이었는데,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 같이 뛸 수 있어서 기뻤어.</t>
   </si>
   <si>
     <t>clean</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 &gt; 가슴 순으로 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마따끄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 머리 갸우뚱 후 절레절레</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 목 뒤 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1과 동일</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞에서 피스</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 축 모으기, 오른쪽 눈 윙크</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 눈 앞 윙크, 입 앞에서 피스 후 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 가슴 &gt; 입, 갸우뚱하면서 웃기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손으로 오른손 받치고 턱 괴며 웃음</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 오른손 입 앞</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손만 허리 짚고 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 허리 위로 살짝 올리고 들썩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 입 앞에 들썩 후 기울어짐</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른손 엉덩이 뒤로</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bg_hikaesitu2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BREAK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>left</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭠까?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>asahi_sports_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>none</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>mei_sports_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>zoom</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>right</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bg_runninTrack_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashback</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BG</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>메이…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait5 face_jito lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가버렸네.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가버렸슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait3 face_surp lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003041</t>
-  </si>
-  <si>
-    <t>S003092</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S003093</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUDIO</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2 face_serious lip_smile1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_door_sime</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_131</t>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히쨩.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004001</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004002</t>
-  </si>
-  <si>
-    <t>분해?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004003</t>
-  </si>
-  <si>
-    <t>bg_ceiling</t>
-  </si>
-  <si>
-    <t>se_sofa_sitdown</t>
-  </si>
-  <si>
-    <t>달리기 시작하면 바로 따라잡을 줄 알았슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004004</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>작년에 그랬던 것처럼.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004005</t>
-  </si>
-  <si>
-    <t>분명, 결승선 직전에 아슬아슬하게 추월했다고 했지.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004006</t>
-  </si>
-  <si>
-    <t>se_sofa_wait</t>
-  </si>
-  <si>
-    <t>저는 후유코쨩이나 메이쨩처럼 연습 같은 거 안 했슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004007</t>
-  </si>
-  <si>
-    <t>해야겠다는 생각도 안 했슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004008</t>
-  </si>
-  <si>
-    <t>만약 졌다고 하더라도,</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004009</t>
-  </si>
-  <si>
-    <t>그건 아사히쨩의 책임이 아니야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004010</t>
-  </si>
-  <si>
-    <t>책임…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004011</t>
-  </si>
-  <si>
-    <t>se_sofa_wakeup</t>
-  </si>
-  <si>
-    <t>잠깐 뛰고 오겠슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004012</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shy1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>응…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004013</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_serious lip_shy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>현장 정리 중이니까 안 된다고 해야 되는데…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004014</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>sad2 lip_smile1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>mei_sports_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리는 한 팀이니까!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아하하…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004015</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>sad1 lip_smile1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이렇게 큰 소리 쳐놓고 진 사람도 있는데 말이야…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004016</t>
-  </si>
-  <si>
-    <t>그 때, 후유코쨩의 표정…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004017</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 두 사람한테…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004018</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무런 도움도…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004019</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 역시 나도 뛰고 올래.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004020</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러니까, 그런 게…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004021</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_door_ake</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>어라?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004022</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>너, 어디 간다는 말 들었어?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004023</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아니, 별다른 연락은…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004024</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아,</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004025</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_phone_long</t>
-  </si>
-  <si>
-    <t>bg_phone</t>
-  </si>
-  <si>
-    <t>BREAK</t>
-  </si>
-  <si>
-    <t>후유코, 이거.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004026</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭔데?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004027</t>
-  </si>
-  <si>
-    <t>두 사람, 지금 트랙에서 달리기 중이라나 봐.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004028</t>
-  </si>
-  <si>
-    <t>메이, 이런 건 네가 말리란 말이야…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004029</t>
-  </si>
-  <si>
-    <t>anger1 face_close3 lip_bitter_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유한테는 큰 소리 쳤으면서,</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004030</t>
-  </si>
-  <si>
-    <t>진짜 바보들이라니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004031</t>
-  </si>
-  <si>
-    <t>후유코.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004032</t>
-  </si>
-  <si>
-    <t>알고 있어.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004033</t>
-  </si>
-  <si>
-    <t>smile1 face_serious</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>너는 가게나 예약해 놔.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004034</t>
-  </si>
-  <si>
-    <t>예약…?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004035</t>
-  </si>
-  <si>
-    <t>담당 아이돌이 열심히 노력해서 1등을 했는데, 회식 정도는 해야 하지 않겠어?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004036</t>
-  </si>
-  <si>
-    <t>그, 그렇네…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004037</t>
-  </si>
-  <si>
-    <t>물론, 프로듀서 님이 쏘시는 거죠?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004038</t>
-  </si>
-  <si>
-    <t>후유는 소고기가 먹고싶은데~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004039</t>
-  </si>
-  <si>
-    <t>… 맡겨줘.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S004040</t>
-  </si>
-  <si>
-    <t>1.7</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_serious lip_anger2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait4 face_close3 lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_serious lip_smile</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다. DialogBox 비표시를 원할 때에는 0으로 입력합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>......</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀적으로도, 개인적으로, 굉장히 많은 게 달라지고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>smile2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="넥슨Lv2고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>lip_surp</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무튼! 지금까지,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1880,6 +1896,27 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1910,7 +1947,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1920,8 +1957,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1961,11 +2001,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="HeadLine" xfId="1" xr:uid="{E4A97682-4FCD-4053-8CB5-ED3783212F4A}"/>
     <cellStyle name="Title" xfId="2" xr:uid="{29B85624-08FE-4DDC-B250-B42E27D66566}"/>
     <cellStyle name="표준" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="표준 2" xfId="3" xr:uid="{F716A373-FC02-46B6-A291-7E2AB7D74B7C}"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -2002,6 +2049,9 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -2068,8 +2118,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P116" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P116" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P70" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P70" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
@@ -2080,7 +2130,7 @@
     <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="11" dataCellStyle="표준 2">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="10">
@@ -2599,12 +2649,12 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>452</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -2754,10 +2804,10 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>23</v>
@@ -2771,16 +2821,16 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -2788,36 +2838,36 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="H44" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -2825,54 +2875,54 @@
         <v>19</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2883,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
-  <dimension ref="B2:P116"/>
+  <dimension ref="B2:P70"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -2952,7 +3002,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2968,12 +3018,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2983,22 +3033,22 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3007,7 +3057,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3022,28 +3072,28 @@
         <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>319</v>
+        <v>199</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -3055,28 +3105,28 @@
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>327</v>
+        <v>201</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -3085,20 +3135,32 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
-        <v>331</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="L8" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -3106,44 +3168,56 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>311</v>
+      </c>
       <c r="G9" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>448</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C10" s="7"/>
+        <v>193</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>325</v>
+      </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="F10" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -3154,26 +3228,26 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+        <v>325</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -3181,26 +3255,26 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D12" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -3211,22 +3285,28 @@
         <v>88</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>202</v>
+      </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -3238,12 +3318,14 @@
         <v>88</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14" s="7"/>
+        <v>329</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>330</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -3251,7 +3333,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -3259,40 +3341,50 @@
       <c r="P14" s="7"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>334</v>
+      </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
-        <v>331</v>
-      </c>
+      <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="L16" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -3300,62 +3392,96 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="L17" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="7" t="s">
-        <v>356</v>
-      </c>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7" t="s">
-        <v>299</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -3366,22 +3492,28 @@
         <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+        <v>343</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>344</v>
+      </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -3393,13 +3525,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3408,7 +3540,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -3420,22 +3552,28 @@
         <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+        <v>347</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>440</v>
+      </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -3444,23 +3582,28 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>349</v>
+      </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="L23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
@@ -3469,22 +3612,28 @@
         <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>365</v>
+        <v>30</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>433</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+        <v>350</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -3496,22 +3645,24 @@
         <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>367</v>
+        <v>30</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>352</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F25" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>334</v>
+      </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -3523,19 +3674,28 @@
         <v>88</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+        <v>354</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -3547,22 +3707,28 @@
         <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+        <v>357</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -3574,22 +3740,28 @@
         <v>88</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+        <v>359</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -3598,34 +3770,30 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>374</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>441</v>
+      </c>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3634,10 +3802,12 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7" t="s">
-        <v>331</v>
+        <v>444</v>
       </c>
       <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
+      <c r="K30" s="7" t="s">
+        <v>435</v>
+      </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -3645,65 +3815,83 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>339</v>
+      </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="L32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>364</v>
+      </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
+      <c r="L33" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -3714,28 +3902,28 @@
         <v>88</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>376</v>
+        <v>30</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>365</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>319</v>
+        <v>199</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3747,28 +3935,28 @@
         <v>88</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -3777,44 +3965,58 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>370</v>
+      </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="L36" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>372</v>
+      </c>
       <c r="F37" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+        <v>311</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>453</v>
+        <v>89</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -3823,22 +4025,26 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>375</v>
+      </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="I38" s="7"/>
       <c r="J38" s="7"/>
-      <c r="K38" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
@@ -3849,28 +4055,28 @@
         <v>88</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>382</v>
+        <v>30</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>376</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>327</v>
+        <v>199</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -3882,20 +4088,28 @@
         <v>88</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
+        <v>379</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -3904,7 +4118,7 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -3912,11 +4126,11 @@
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="7" t="s">
-        <v>331</v>
-      </c>
+      <c r="I41" s="7"/>
       <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
+      <c r="K41" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -3925,77 +4139,91 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7" t="s">
-        <v>255</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="L42" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="7" t="s">
-        <v>196</v>
-      </c>
+      <c r="P42" s="7"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B43" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
+      <c r="B43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>251</v>
+        <v>30</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>383</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>194</v>
+        <v>384</v>
       </c>
       <c r="F44" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>187</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4007,22 +4235,28 @@
         <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D45" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>386</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
+        <v>387</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>367</v>
+      </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4031,20 +4265,30 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
-        <v>331</v>
-      </c>
+      <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
+      <c r="L46" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -4052,102 +4296,122 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
+      <c r="L47" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="P47" s="7"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
-        <v>299</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="I48" s="7"/>
       <c r="J48" s="7"/>
-      <c r="K48" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
       <c r="P48" s="7"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
+      <c r="B49" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
+        <v>397</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>436</v>
+      </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4156,20 +4420,32 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7" t="s">
-        <v>331</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
+      <c r="L51" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="7"/>
@@ -4177,64 +4453,92 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
+      <c r="L52" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
-      <c r="P52" s="7" t="s">
-        <v>356</v>
-      </c>
+      <c r="P52" s="7"/>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>404</v>
+      </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="N53" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="L53" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7" t="s">
-        <v>299</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="I54" s="7"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
+      <c r="L54" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
@@ -4245,22 +4549,28 @@
         <v>88</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>392</v>
+        <v>30</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>407</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+        <v>408</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>409</v>
+      </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -4269,20 +4579,32 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7" t="s">
-        <v>331</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
+      <c r="L56" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -4290,105 +4612,121 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
+      <c r="L57" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
-      <c r="P57" s="7" t="s">
-        <v>328</v>
-      </c>
+      <c r="P57" s="7"/>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7" t="s">
-        <v>299</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="I58" s="7"/>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
+      <c r="L58" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
       <c r="P58" s="7"/>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>334</v>
+      <c r="B59" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>416</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H59" t="s">
-        <v>235</v>
-      </c>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
+        <v>417</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B60" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="7"/>
+      <c r="B60" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -4397,10 +4735,12 @@
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7" t="s">
-        <v>331</v>
+        <v>444</v>
       </c>
       <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
+      <c r="K61" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -4408,44 +4748,54 @@
       <c r="P61" s="7"/>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B62" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7" t="s">
-        <v>356</v>
-      </c>
+      <c r="B62" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
-      <c r="I63" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="I63" s="7"/>
       <c r="J63" s="7"/>
-      <c r="K63" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -4453,53 +4803,45 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>395</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="13"/>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
+      <c r="K64" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>450</v>
+      </c>
       <c r="O64" s="7"/>
       <c r="P64" s="7"/>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>397</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="K65" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="L65" s="7"/>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
@@ -4507,20 +4849,26 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>424</v>
+      </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
-      <c r="I66" s="7" t="s">
-        <v>331</v>
-      </c>
+      <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
+      <c r="L66" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -4528,1253 +4876,105 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>426</v>
+      </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
+      <c r="L67" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
-      <c r="P67" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="P67" s="7"/>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>428</v>
+      </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="N68" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="L68" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7"/>
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>430</v>
+      </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
-        <v>299</v>
-      </c>
+      <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
+      <c r="L69" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B70" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B71" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="7"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B72" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="N72" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="7"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B74" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="P74" s="7"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B75" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B76" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B77" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H77" t="s">
-        <v>335</v>
-      </c>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="7"/>
-    </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B78" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="N78" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B79" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="7"/>
-    </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B80" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-    </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B81" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-    </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B82" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B83" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
-      <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
-    </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B84" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="P84" s="7"/>
-    </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B85" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B86" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H86" t="s">
-        <v>342</v>
-      </c>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="7"/>
-    </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B87" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="7"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M87" s="7"/>
-      <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="7"/>
-    </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B88" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="7"/>
-    </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B89" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="N89" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
-    </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B90" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
-      <c r="O90" s="7"/>
-      <c r="P90" s="7"/>
-    </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B91" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B92" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-    </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B93" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
-    </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B94" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" s="7" t="s">
+      <c r="B70" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="7"/>
-    </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B95" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M95" s="7"/>
-      <c r="N95" s="7"/>
-      <c r="O95" s="7"/>
-      <c r="P95" s="7"/>
-    </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B96" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="J96" s="7"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
-      <c r="P96" s="7"/>
-    </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B97" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
-      <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B98" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H98" t="s">
-        <v>235</v>
-      </c>
-      <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M98" s="7"/>
-      <c r="N98" s="7"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
-    </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B99" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="7"/>
-      <c r="K99" s="7"/>
-      <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="7"/>
-    </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B100" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H100" t="s">
-        <v>424</v>
-      </c>
-      <c r="I100" s="7"/>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7"/>
-      <c r="L100" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M100" s="7"/>
-      <c r="N100" s="7"/>
-      <c r="O100" s="7"/>
-      <c r="P100" s="7"/>
-    </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B101" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M101" s="7"/>
-      <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
-    </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B102" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H102" t="s">
-        <v>450</v>
-      </c>
-      <c r="I102" s="7"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M102" s="7"/>
-      <c r="N102" s="7"/>
-      <c r="O102" s="7"/>
-      <c r="P102" s="7"/>
-    </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B103" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
-      <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
-      <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="7"/>
-    </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B104" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M104" s="7"/>
-      <c r="N104" s="7"/>
-      <c r="O104" s="7"/>
-      <c r="P104" s="7"/>
-    </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B105" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H105" t="s">
-        <v>433</v>
-      </c>
-      <c r="I105" s="7"/>
-      <c r="J105" s="7"/>
-      <c r="K105" s="7"/>
-      <c r="L105" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M105" s="7"/>
-      <c r="N105" s="7"/>
-      <c r="O105" s="7"/>
-      <c r="P105" s="7"/>
-    </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B106" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="N106" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="O106" s="7"/>
-      <c r="P106" s="7"/>
-    </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B107" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="7"/>
-      <c r="K107" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="7"/>
-    </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B108" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" t="s">
-        <v>451</v>
-      </c>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="7"/>
-    </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B109" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="7"/>
-    </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B110" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H110" t="s">
-        <v>258</v>
-      </c>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="7"/>
-    </row>
-    <row r="111" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B111" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="7"/>
-    </row>
-    <row r="112" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B112" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="H112" t="s">
-        <v>232</v>
-      </c>
-      <c r="I112" s="7"/>
-      <c r="J112" s="7"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
-      <c r="O112" s="7"/>
-      <c r="P112" s="7"/>
-    </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B113" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="7"/>
-      <c r="P113" s="7"/>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B114" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="7"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
-      <c r="O114" s="7"/>
-      <c r="P114" s="7"/>
-    </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B115" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="N115" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O115" s="7"/>
-      <c r="P115" s="7"/>
-    </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B116" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="7"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+      <c r="P70" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -5806,59 +5006,59 @@
         <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G3" t="s">
         <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="M3" t="s">
         <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G4" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="H4" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="M4" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="N4" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H5" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="M5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="N5" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -5866,39 +5066,39 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G6" t="s">
         <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="M6" t="s">
         <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G7" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="H7" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="M7" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="N7" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
@@ -5906,261 +5106,261 @@
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G8" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="H8" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="M8" t="s">
         <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="M9" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="N9" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G10" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="H10" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="M10" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="N10" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G11" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="H11" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="M11" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="N11" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="M12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N12" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H13" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="M13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="N13" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G14" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H14" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="M14" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="N14" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G15" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="H15" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="M15" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="N15" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H16" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="M16" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="N16" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C17" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G17" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="M17" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="N17" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G18" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H18" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="M18" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="N18" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G19" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="M19" t="s">
         <v>78</v>
       </c>
       <c r="N19" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C20" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="N20" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -6177,15 +5377,15 @@
         <v>72</v>
       </c>
       <c r="M22" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N22" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="E23" t="s">
         <v>70</v>
@@ -6197,15 +5397,15 @@
         <v>73</v>
       </c>
       <c r="M23" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="N23" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="E24" t="s">
         <v>84</v>
@@ -6219,36 +5419,36 @@
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M25" t="s">
+        <v>90</v>
+      </c>
+      <c r="P25" t="s">
         <v>91</v>
-      </c>
-      <c r="P25" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J26" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M26" t="s">
         <v>76</v>
@@ -6259,10 +5459,10 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M27" t="s">
         <v>78</v>
@@ -6273,10 +5473,10 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s">
         <v>80</v>
@@ -6287,10 +5487,10 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M29" t="s">
         <v>82</v>
@@ -6301,70 +5501,70 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M31" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="E36" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -6380,122 +5580,122 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
         <v>104</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
         <v>108</v>
       </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
       <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
         <v>135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
         <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
@@ -6503,7 +5703,7 @@
         <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
@@ -6511,73 +5711,73 @@
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
         <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
         <v>120</v>
       </c>
-      <c r="C27" t="s">
-        <v>121</v>
-      </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" t="s">
         <v>123</v>
-      </c>
-      <c r="C29" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
@@ -6585,7 +5785,7 @@
         <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -6601,74 +5801,74 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F10">
         <v>71</v>
@@ -6676,10 +5876,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F11">
         <v>73</v>
@@ -6687,7 +5887,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -6695,7 +5895,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F13">
         <v>77</v>
@@ -6703,10 +5903,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F14">
         <v>88</v>
@@ -6714,10 +5914,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -6725,7 +5925,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -6733,7 +5933,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F17">
         <v>101</v>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB0CE12-920D-41C4-8B2E-E05D0BBBB7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B88485-E0F2-48AB-A2C1-463FAB38E153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="536">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1154,10 +1154,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>clean</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>오른손 입 &gt; 가슴 순으로 들썩</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1226,592 +1222,780 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>bg_hikaesitu2</t>
+    <t>0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUDIO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다. DialogBox 비표시를 원할 때에는 0으로 입력합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_rouka</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>se_jihannki</t>
+  </si>
+  <si>
+    <t>아 후유코쨩, 그거 들었어?</t>
+  </si>
+  <si>
+    <t>s001001</t>
+  </si>
+  <si>
+    <t>mei_idol_3</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>wait1</t>
+  </si>
+  <si>
+    <t>후유코</t>
+  </si>
+  <si>
+    <t>그거?</t>
+  </si>
+  <si>
+    <t>s001002</t>
+  </si>
+  <si>
+    <t>fuyuko_idol_3</t>
+  </si>
+  <si>
+    <t>다음 달에 있는 운동회 이야기!</t>
+  </si>
+  <si>
+    <t>s001003</t>
+  </si>
+  <si>
+    <t>wait2</t>
+  </si>
+  <si>
+    <t>아 그러고보니…</t>
+  </si>
+  <si>
+    <t>s001004</t>
+  </si>
+  <si>
+    <t>think</t>
+  </si>
+  <si>
+    <t>이번에는 유닛 별로 종목을 고를 수 있대~</t>
+  </si>
+  <si>
+    <t>s001005</t>
+  </si>
+  <si>
+    <t>smile2</t>
+  </si>
+  <si>
+    <t>후유코쨩은 뭐 나가고 싶어?</t>
+  </si>
+  <si>
+    <t>s001006</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>zoom</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>se_tansan</t>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>음… 그러네…</t>
+  </si>
+  <si>
+    <t>s001007</t>
+  </si>
+  <si>
+    <t>계주라던가, 어때?</t>
+  </si>
+  <si>
+    <t>s001008</t>
+  </si>
+  <si>
+    <t>아… 최악이야. 계주같은 건, 죽어도 사양이야</t>
+  </si>
+  <si>
+    <t>s001009</t>
+  </si>
+  <si>
+    <t>에, 정말? 계주는 운동회의 꽃이잖아?</t>
+  </si>
+  <si>
+    <t>s001010</t>
+  </si>
+  <si>
+    <t>surp1</t>
+  </si>
+  <si>
+    <t>그러니까 싫은 거야. 그렇게 보는 눈이 많은 곳에서 넘어지기라도 해 봐.</t>
+  </si>
+  <si>
+    <t>s001011</t>
+  </si>
+  <si>
+    <t>애초에 후유, 달리기 그렇게 잘 하는 편이 아니니까…</t>
+  </si>
+  <si>
+    <t>s001012</t>
+  </si>
+  <si>
+    <t>팬들에게 완벽하지 않은 모습은 보여주고 싶지 않아.</t>
+  </si>
+  <si>
+    <t>s001013</t>
+  </si>
+  <si>
+    <t>그렇구나… 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
+  </si>
+  <si>
+    <t>s001014</t>
+  </si>
+  <si>
+    <t>아, 근데 아사히쨩은 분명 이어달리기 나가고 싶어할 텐데…</t>
+  </si>
+  <si>
+    <t>s001015</t>
+  </si>
+  <si>
+    <t>skill2 face_sad</t>
+  </si>
+  <si>
+    <t>그 녀석 성격 상, 무조건 그렇겠지…</t>
+  </si>
+  <si>
+    <t>s001016</t>
+  </si>
+  <si>
+    <t>wait2 face_serious lip_sad</t>
+  </si>
+  <si>
+    <t>잠깐만, 메이.</t>
+  </si>
+  <si>
+    <t>s001017</t>
+  </si>
+  <si>
+    <t>후유코쨩?</t>
+  </si>
+  <si>
+    <t>s001018</t>
+  </si>
+  <si>
+    <t>wait1 face_surp</t>
+  </si>
+  <si>
+    <t>왠지 불길한 기분이 들어… 빨리 돌아가자.</t>
+  </si>
+  <si>
+    <t>s001019</t>
+  </si>
+  <si>
+    <t>wait4 face_jito lip_anger</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>se_rouka_run</t>
+  </si>
+  <si>
+    <t>자, 잠깐만 후유코쨩!</t>
+  </si>
+  <si>
+    <t>s001020</t>
+  </si>
+  <si>
+    <t>iris</t>
+  </si>
+  <si>
+    <t>se_trans_out|se_trans_in</t>
+  </si>
+  <si>
+    <t>asahi_idol_3</t>
+  </si>
+  <si>
+    <t>center</t>
+  </si>
+  <si>
+    <t>wait1 face_smile</t>
+  </si>
+  <si>
+    <t>방송 PD</t>
+  </si>
+  <si>
+    <t>와하하! 좋네, 그거!</t>
+  </si>
+  <si>
+    <t>s001021</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>아사히쨩이 달리는 거, 분명 그림이 될 테니까!</t>
+  </si>
+  <si>
+    <t>s001022</t>
+  </si>
+  <si>
+    <t>작년 방송이 꽤 화제가 돼서 말이야.</t>
+  </si>
+  <si>
+    <t>s001023</t>
+  </si>
+  <si>
+    <t>이번에는 이어달리기용 원샷 카메라도 준비해뒀다고!</t>
+  </si>
+  <si>
+    <t>s001024</t>
+  </si>
+  <si>
+    <t>그거, 본 적 있슴다!</t>
+  </si>
+  <si>
+    <t>s001025</t>
+  </si>
+  <si>
+    <t>smile3 lip_wait</t>
+  </si>
+  <si>
+    <t>카메라 감독님이 카메라를 들고 선수보다 빨리 뛰는 거!</t>
+  </si>
+  <si>
+    <t>s001026</t>
+  </si>
+  <si>
+    <t>아니, 아무리 그래도 직접 들고 뛰진 않지~</t>
+  </si>
+  <si>
+    <t>s001027</t>
+  </si>
+  <si>
+    <t>뭐야, 직접 뛰는 건 줄 알았슴다…</t>
+  </si>
+  <si>
+    <t>s001028</t>
+  </si>
+  <si>
+    <t>sad2 lip_anger</t>
+  </si>
+  <si>
+    <t>뭐, 옛날에는 직접 들고 뛰었을지도 모르겠지만</t>
+  </si>
+  <si>
+    <t>s001029</t>
+  </si>
+  <si>
+    <t>지금은 보통 트랙 러너 카메라라는 녀석으로 찍거든</t>
+  </si>
+  <si>
+    <t>s001030</t>
+  </si>
+  <si>
+    <t>그 트랙 러너 카메라라는 거, 빠른 검까?</t>
+  </si>
+  <si>
+    <t>s001031</t>
+  </si>
+  <si>
+    <t>think1</t>
+  </si>
+  <si>
+    <t>그야 달리는 선수들을 찍어야 하니까 당연히…</t>
+  </si>
+  <si>
+    <t>s001032</t>
+  </si>
+  <si>
+    <t>그럼, 그 녀석을 이기면 제가 1등인 거네요?</t>
+  </si>
+  <si>
+    <t>s001033</t>
+  </si>
+  <si>
+    <t>skill1</t>
+  </si>
+  <si>
+    <t>아하하! 그렇네, 아사히쨩이 이길 수 있다면 말이지!</t>
+  </si>
+  <si>
+    <t>s001034</t>
+  </si>
+  <si>
+    <t>그 트랙… 무슨 카메라는 지금 어디있슴까?</t>
+  </si>
+  <si>
+    <t>s001035</t>
+  </si>
+  <si>
+    <t>빨리 승부하고 싶슴다!</t>
+  </si>
+  <si>
+    <t>s001036</t>
+  </si>
+  <si>
+    <t>아쉽게도 다음 달 대여 예정이라서</t>
+  </si>
+  <si>
+    <t>s001037</t>
+  </si>
+  <si>
+    <t>se_door_ake</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BREAK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUDIO</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 화자 타입으로 말풍선의 색과 SD 아이콘을 결정합니다. 1은 아이돌, 2가 프로듀서, 3이 기타입니다. 반드시 입력되어야 합니다. DialogBox 비표시를 원할 때에는 0으로 입력합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건 뭠까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>asahi_normal_sr2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>think1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>어제 이야기했잖아, 아사히쨩?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT002</t>
-  </si>
-  <si>
-    <t>fuyuko_normal_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하십니다~</t>
+  </si>
+  <si>
+    <t>s001038</t>
   </si>
   <si>
     <t>smile1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에 개장하는 극장에 대한 PR 오퍼래.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT003</t>
-  </si>
-  <si>
-    <t>mei_normal_8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하십니다.</t>
+  </si>
+  <si>
+    <t>s001039</t>
+  </si>
+  <si>
+    <t>다음 달까지는 못 기다림다~</t>
+  </si>
+  <si>
+    <t>s001040</t>
+  </si>
+  <si>
+    <t>anger1</t>
+  </si>
+  <si>
+    <t>저기, 프로듀서 님… 이건…?</t>
+  </si>
+  <si>
+    <t>s001041</t>
+  </si>
+  <si>
+    <t>wait1 face_smile lip_bitter_smile</t>
+  </si>
+  <si>
+    <t>프로듀서</t>
+  </si>
+  <si>
+    <t>아 후유코, 메이. 어서 와.</t>
+  </si>
+  <si>
+    <t>s001042</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PD님이랑 아사히가 다음 달에 나갈 운동회 이야기를 하고 있던 중이었는데…</t>
+  </si>
+  <si>
+    <t>s001043</t>
+  </si>
+  <si>
+    <t>어, 마침 잘 왔네!</t>
+  </si>
+  <si>
+    <t>s001044</t>
+  </si>
+  <si>
+    <t>스트레이라이트한테는 꼭 이어달리기에 나가줬으면 해서!</t>
+  </si>
+  <si>
+    <t>s001045</t>
+  </si>
+  <si>
+    <t>두 사람도 괜찮지? 운동 잘 하잖아?</t>
+  </si>
+  <si>
+    <t>s001046</t>
+  </si>
+  <si>
+    <t>P, PD님, 잠시…</t>
+  </si>
+  <si>
+    <t>s001047</t>
+  </si>
+  <si>
+    <t>아, 그건…</t>
+  </si>
+  <si>
+    <t>s001048</t>
+  </si>
+  <si>
+    <t>네. 저희한테 맡겨주세요.</t>
+  </si>
+  <si>
+    <t>s001049</t>
+  </si>
+  <si>
+    <t>후, 후유코쨩…?</t>
+  </si>
+  <si>
+    <t>s001050</t>
+  </si>
+  <si>
+    <t>후유코…?</t>
+  </si>
+  <si>
+    <t>s001051</t>
+  </si>
+  <si>
+    <t>아하하, 좋네! 그럼 다음 달에 잘 부탁해!</t>
+  </si>
+  <si>
+    <t>s001052</t>
+  </si>
+  <si>
+    <t>네, 잘 부탁드립니다~</t>
+  </si>
+  <si>
+    <t>s001053</t>
+  </si>
+  <si>
+    <t>se_door_sime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUIDO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_100</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩, 정말 괜찮아?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001054</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>괜찮을 리가 없잖아.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001055</t>
   </si>
   <si>
     <t>right</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤에-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT004</t>
-  </si>
-  <si>
-    <t>wait3 face_wait lip_surp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>straylight</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 사람 다 준비 됐어? 인사할게?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕하세요. 저희는,</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT006</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트입니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT007 OT008 OT009</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug2 lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 후유가 이 녀석 때문에 이어달리기에 나가야 되는 건데</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001056</t>
+  </si>
+  <si>
+    <t>그치만 나가겠다고 한 건 후유코쨩임다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001057</t>
+  </si>
+  <si>
+    <t>wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 분위기에서 나가기 싫다고 할 수 있겠냐고!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001058</t>
+  </si>
+  <si>
+    <t>나가는 종목에 대해서는 조금 더 생각해보겠다고 지금이라도 이야기하면…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001059</t>
+  </si>
+  <si>
+    <t>아니.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001060</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>none</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>개장 축하드립니다~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT011</t>
-  </si>
-  <si>
-    <t>smile4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>축하드림다~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT012</t>
-  </si>
-  <si>
-    <t>축하드립니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT013</t>
-  </si>
-  <si>
-    <t>smile3 face_smile2 lip_smile1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT014</t>
-  </si>
-  <si>
-    <t>이 작품은 빛의…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT015</t>
-  </si>
-  <si>
-    <t>이거 뭐라고 읽는 검까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT016</t>
-  </si>
-  <si>
-    <t>OT017</t>
-  </si>
-  <si>
-    <t>smile1 face_serious</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(이 자식, 그렇게 대본 읽어두라고 했는데…!)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT018</t>
-  </si>
-  <si>
-    <t>관성이라는 뜻이라고 함다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT019</t>
-  </si>
-  <si>
-    <t>아, 그러고보니 스시 1접시 할 때의 한자랑 닮았슴다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT020</t>
-  </si>
-  <si>
-    <t>오, 확실히…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT021</t>
-  </si>
-  <si>
-    <t>surp2 lip_smile2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>빛에는 원래 관성이 없는데, 빛의 관성이라니 무슨 의미일지 궁금하네요~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT022</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아, 후유코쨩이 제 대사 뺏어갔슴다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT023</t>
-  </si>
-  <si>
-    <t>두 사람은 촬영하면서 기억나는 장면이라던가, 있어?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT024</t>
-  </si>
-  <si>
-    <t>think face_smile lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT025</t>
-  </si>
-  <si>
-    <t>smile2 face_serious</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT026</t>
-  </si>
-  <si>
-    <t>뛰는 장면을 찍을 때, 두 시간 넘게 계속 뛰니까 힘들었슴다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT027</t>
-  </si>
-  <si>
-    <t>anger1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>완성된 장면을 봤을 때, 뛰는 건 10분도 안나왔는데…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT028</t>
-  </si>
-  <si>
-    <t>아사히쨩, 좋았던 기억은…?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT029</t>
-  </si>
-  <si>
-    <t>surp1 face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>음…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT030</t>
-  </si>
-  <si>
-    <t>아, 끝나고 먹은 소고기가 맛있었슴다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>후, 후유도 예전에 대운동회에 나갔을 때의 생각이 났어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT032</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile4 face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 때와 비교하면, 지금은 굉장히 많은 게 달라졌구나… 하고.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT033</t>
-  </si>
-  <si>
-    <t>OT034</t>
-  </si>
-  <si>
-    <t>어떤 건 전혀 달라지지 않았구나, 하고.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT035</t>
-  </si>
-  <si>
-    <t>만약 그 시절의 대운동회 방송을 기억하시는 분들이 계신다면, \n이번의 저희의 모습과 비교해서 보시는 것도 재밌을 것 같아요!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT036</t>
-  </si>
-  <si>
-    <t>프로듀서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(슬슬 마무리하자)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유가 좋고 싫고 이전에, 이건 확실히 좋은 기회야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001061</t>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이가 이야기했듯이, 이어달리기는 운동회의 꽃이니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001062</t>
+  </si>
+  <si>
+    <t>거기에 이번에는 원샷 카메라까지 받을 수 있다며?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001063</t>
+  </si>
+  <si>
+    <t>PD님이 이야기한 것처럼, 이 녀석이 주목 받을 건 거의 확실하니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001064</t>
+  </si>
+  <si>
+    <t>스트레이라이트의 인지도를 올릴 좋은 기회야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001065</t>
+  </si>
+  <si>
+    <t>괜히 나중에 말을 바꿔서 나쁜 인상을 주고 싶지도 않고.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001066</t>
+  </si>
+  <si>
+    <t>anger2 face_cry lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그치만 후유코쨩이…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001067</t>
+  </si>
+  <si>
+    <t>wait3 face_sad lip_anger2</t>
+  </si>
+  <si>
+    <t>후유코쨩.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001068</t>
+  </si>
+  <si>
+    <t>하기 싫은데 억지로 나가는 건, 이상함다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001069</t>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런 거, 전혀 재미있지 않슴다…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001070</t>
   </si>
   <si>
     <t>2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도, 재밌었슴다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT037</t>
-  </si>
-  <si>
-    <t>응, 그렇네.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT038</t>
-  </si>
-  <si>
-    <t>네, 저희가 이렇게 재미있게 촬영한 작품과, 이번에 새로 개장하는 극장까지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT039</t>
-  </si>
-  <si>
-    <t>skill1 face_smile lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>모두들, 많은 관심 부탁드립니다~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT040</t>
-  </si>
-  <si>
-    <t>구독이랑, 좋아요도 부탁드림다~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT041</t>
-  </si>
-  <si>
-    <t>아사히쨩? 유튜브 같은 게 아니니까…!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT042</t>
-  </si>
-  <si>
-    <t>shrug face_bitter_smile lip_bitter_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>댓글도 많이 달아주세요.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT043</t>
-  </si>
-  <si>
-    <t>정말~ 메이쨩까지!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT044</t>
-  </si>
-  <si>
-    <t>OT045</t>
-  </si>
-  <si>
-    <t>anger3 face_smile lip_smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스트레이라이트였습니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT046 OT047 OT048</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>수고했어. 이대로 써도 될 것 같아.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT049</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아사히, 후유가 어제부터 대본 훑어보라고 했지!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT050</t>
-  </si>
-  <si>
-    <t>우왓, 왜 잡으러 오는 검까!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT051</t>
-  </si>
-  <si>
-    <t>메이! 그 쪽으로 가면 잡아!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT052</t>
-  </si>
-  <si>
-    <t>아하하, 후유코쨩. 일단 진정하자~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT053</t>
-  </si>
-  <si>
-    <t>아사히, 너 잡히기만 해!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT054</t>
-  </si>
-  <si>
-    <t>smile2 face_wait lip_surp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>개장하고 가장 첫 상영은, \n저희 스트레이라이트가 출연한 InertiaLucis라는 작품이라고 합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>'관성' 이라고 읽는 거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_ira</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile3 lip_surp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>surp2 face_wait lip_smile2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>se_rouka_run</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>처음에 메이쨩이 말했듯이, 이번에 새롭게 개장하신다는 소식을 듣고\n축하 영상을 보내드립니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>why face_anger lip_anger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>예전에 운동회에 나갔을 땐 서로 다른 팀이었는데,</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 같이 뛸 수 있어서 기뻤어.</t>
-  </si>
-  <si>
-    <t>clean</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>......</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>팀적으로도, 개인적으로, 굉장히 많은 게 달라지고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>smile2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="넥슨Lv2고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>lip_surp</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무튼! 지금까지,</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코쨩이 하기 싫은 거라면…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001071</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>바보네.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001072</t>
+  </si>
+  <si>
+    <t>어른에게는 하기 싫어도 해야 하는 일이라는 게 있거든.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001073</t>
+  </si>
+  <si>
+    <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001074</t>
+  </si>
+  <si>
+    <t>… 잘 모르겠슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001075</t>
+  </si>
+  <si>
+    <t>think1 lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>몰라도 돼, 너는.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001076</t>
+  </si>
+  <si>
+    <t>재밌게 달리기만 하면 되니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001077</t>
+  </si>
+  <si>
+    <t>자, 이거.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001078</t>
+  </si>
+  <si>
+    <t>감사함다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001079</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그치만, 후유코쨩 느리니까 1등은 못할 것 같슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001080</t>
+  </si>
+  <si>
+    <t>시끄러! 알고 있거든!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001081</t>
+  </si>
+  <si>
+    <t>아하하, 후유코쨩… 진정 진정~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001082</t>
+  </si>
+  <si>
+    <t>에~ 1등 아니면 재미 없슴다~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001083</t>
+  </si>
+  <si>
+    <t>너가 그만큼 열심히 달리면 되잖아!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001084</t>
+  </si>
+  <si>
+    <t>무리임다, 그런 거~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001085</t>
+  </si>
+  <si>
+    <t>wipe_left</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1904,18 +2088,11 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="넥슨Lv2고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1938,11 +2115,31 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1961,7 +2158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2001,10 +2198,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2118,8 +2324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P70" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P70" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P113" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P113" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
@@ -2649,7 +2855,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -2933,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
-  <dimension ref="B2:P70"/>
+  <dimension ref="B2:P113"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -3002,7 +3208,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3011,19 +3217,23 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>303</v>
+      </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="M3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="O3" s="7"/>
-      <c r="P3" s="7" t="s">
-        <v>301</v>
-      </c>
+      <c r="P3" s="7"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3032,23 +3242,19 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="7" t="s">
-        <v>306</v>
-      </c>
+      <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>303</v>
-      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
       <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3056,13 +3262,13 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="7" t="s">
-        <v>283</v>
-      </c>
+      <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>307</v>
+      </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -3072,19 +3278,19 @@
         <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>199</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>312</v>
@@ -3105,22 +3311,22 @@
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>30</v>
+        <v>313</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3147,13 +3353,13 @@
         <v>318</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>321</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -3171,22 +3377,22 @@
         <v>88</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -3201,26 +3407,32 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>326</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="L10" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -3228,26 +3440,26 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H11" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>326</v>
       </c>
+      <c r="E11" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -3255,23 +3467,17 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>325</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="I12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -3282,108 +3488,112 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>331</v>
+      </c>
       <c r="K13" s="7"/>
-      <c r="L13" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>330</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
+      <c r="B15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>337</v>
+      </c>
       <c r="F16" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+        <v>310</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
-        <v>335</v>
+        <v>89</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -3395,22 +3605,22 @@
         <v>88</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>313</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>439</v>
+        <v>338</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>316</v>
+        <v>67</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -3428,53 +3638,55 @@
         <v>88</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>337</v>
+        <v>241</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>201</v>
+        <v>311</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
+        <v>342</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>431</v>
+        <v>67</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -3492,23 +3704,17 @@
         <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>344</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -3525,13 +3731,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>432</v>
+        <v>347</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3552,22 +3758,22 @@
         <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>199</v>
-      </c>
       <c r="H22" s="7" t="s">
-        <v>440</v>
+        <v>325</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -3585,17 +3791,23 @@
         <v>88</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+        <v>352</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>353</v>
+      </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -3612,22 +3824,22 @@
         <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>433</v>
+        <v>313</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
@@ -3645,19 +3857,23 @@
         <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>352</v>
+        <v>313</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+        <v>316</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -3674,22 +3890,22 @@
         <v>88</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>199</v>
-      </c>
       <c r="H26" s="7" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -3707,22 +3923,22 @@
         <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
@@ -3737,32 +3953,20 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="I28" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
@@ -3770,30 +3974,30 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>17</v>
+        <v>239</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="G29" s="7" t="s">
+        <v>365</v>
+      </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>441</v>
-      </c>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
+      <c r="P29" s="7" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3801,156 +4005,134 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
-        <v>444</v>
-      </c>
+      <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7" t="s">
-        <v>435</v>
+        <v>89</v>
       </c>
       <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c r="M30" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
+      <c r="B31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I32" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
+        <v>369</v>
+      </c>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="O32" s="7" t="s">
+        <v>370</v>
+      </c>
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>364</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="J33" s="7" t="s">
+        <v>303</v>
+      </c>
       <c r="K33" s="7"/>
-      <c r="L33" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>367</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L34" s="7"/>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
+      <c r="P34" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>368</v>
-      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
@@ -3968,13 +4150,13 @@
         <v>88</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>241</v>
+        <v>374</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -3983,7 +4165,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
@@ -3995,28 +4177,22 @@
         <v>88</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>240</v>
+        <v>374</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>373</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -4028,13 +4204,13 @@
         <v>88</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>240</v>
+        <v>374</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -4043,7 +4219,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -4055,28 +4231,22 @@
         <v>88</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>378</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -4091,19 +4261,19 @@
         <v>240</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
@@ -4118,20 +4288,26 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>388</v>
+      </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
-      <c r="K41" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="L41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
@@ -4142,28 +4318,22 @@
         <v>88</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>240</v>
+        <v>374</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>436</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
@@ -4171,59 +4341,59 @@
       <c r="P42" s="7"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
+      <c r="B43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>383</v>
+        <v>374</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>394</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>385</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4235,28 +4405,22 @@
         <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>386</v>
+        <v>374</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>396</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>367</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4268,21 +4432,23 @@
         <v>88</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>447</v>
+        <v>240</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H46" s="7"/>
+        <v>372</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>400</v>
+      </c>
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
@@ -4299,28 +4465,22 @@
         <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>389</v>
+        <v>374</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>316</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4332,22 +4492,22 @@
         <v>88</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>391</v>
+        <v>240</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
@@ -4361,29 +4521,31 @@
       <c r="P48" s="7"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B49" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
+      <c r="B49" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
@@ -4393,19 +4555,19 @@
         <v>240</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>199</v>
+        <v>372</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>436</v>
+        <v>386</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
@@ -4423,23 +4585,17 @@
         <v>88</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>437</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
@@ -4456,28 +4612,22 @@
         <v>88</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>400</v>
+        <v>374</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>412</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>402</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4486,125 +4636,81 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>404</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
+      <c r="I53" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
-    <row r="54" spans="2:16" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>448</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
+      <c r="P54" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>409</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
-      <c r="L55" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>344</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -4615,22 +4721,22 @@
         <v>88</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>412</v>
+        <v>313</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>416</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>201</v>
+        <v>311</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
@@ -4648,22 +4754,22 @@
         <v>88</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>449</v>
+        <v>241</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>415</v>
+        <v>319</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
@@ -4677,115 +4783,137 @@
       <c r="P58" s="7"/>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B59" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>416</v>
+      <c r="B59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>421</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
+        <v>422</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B60" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
+      <c r="B60" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>429</v>
+      </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
-      <c r="I61" s="7" t="s">
-        <v>444</v>
-      </c>
+      <c r="I61" s="7"/>
       <c r="J61" s="7"/>
-      <c r="K61" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="L61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7" t="s">
+        <v>430</v>
+      </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B62" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
+      <c r="B62" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>422</v>
+        <v>374</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>434</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -4794,7 +4922,7 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
@@ -4803,45 +4931,53 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="13"/>
+        <v>88</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>436</v>
+      </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
-      <c r="K64" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="N64" s="7" t="s">
-        <v>450</v>
-      </c>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="M64" s="7"/>
+      <c r="N64" s="7"/>
       <c r="O64" s="7"/>
       <c r="P64" s="7"/>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
-      <c r="K65" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="L65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
@@ -4852,13 +4988,13 @@
         <v>88</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>240</v>
+        <v>427</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>424</v>
+        <v>439</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>440</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -4867,7 +5003,7 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7" t="s">
-        <v>89</v>
+        <v>430</v>
       </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
@@ -4879,17 +5015,23 @@
         <v>88</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
@@ -4906,17 +5048,23 @@
         <v>88</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
+        <v>443</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -4933,17 +5081,23 @@
         <v>88</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
@@ -4956,25 +5110,1214 @@
       <c r="P69" s="7"/>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B70" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13" t="s">
+      <c r="B70" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B71" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B72" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H72" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
-      <c r="P70" s="13"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B73" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B74" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B75" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="P75" s="7"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B76" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="N76" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B77" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B78" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H78" t="s">
+        <v>139</v>
+      </c>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
+      <c r="O78" s="7"/>
+      <c r="P78" s="7"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+    </row>
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B80" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D80" t="s">
+        <v>463</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="L80" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B81" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+    </row>
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B82" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+    </row>
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B83" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+      <c r="P83" s="7"/>
+    </row>
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B84" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B85" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F85" t="s">
+        <v>474</v>
+      </c>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
+      <c r="P85" s="7"/>
+    </row>
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B86" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D86" t="s">
+        <v>475</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B87" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D87" t="s">
+        <v>479</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B88" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D88" t="s">
+        <v>481</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B89" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M89" s="7"/>
+      <c r="N89" s="7"/>
+      <c r="O89" s="7"/>
+      <c r="P89" s="7"/>
+    </row>
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B90" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M90" s="7"/>
+      <c r="N90" s="7"/>
+      <c r="O90" s="7"/>
+      <c r="P90" s="7"/>
+    </row>
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B91" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M91" s="7"/>
+      <c r="N91" s="7"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
+    </row>
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B92" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M92" s="7"/>
+      <c r="N92" s="7"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7"/>
+    </row>
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B93" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="F93" t="s">
+        <v>474</v>
+      </c>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+    </row>
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B94" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M94" s="7"/>
+      <c r="N94" s="7"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+    </row>
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B95" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="17"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M95" s="7"/>
+      <c r="N95" s="7"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+    </row>
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B96" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
+      <c r="N96" s="7"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B97" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="F97" t="s">
+        <v>474</v>
+      </c>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M97" s="7"/>
+      <c r="N97" s="7"/>
+      <c r="O97" s="7"/>
+      <c r="P97" s="7"/>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B98" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="7"/>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B99" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
+      <c r="O99" s="7"/>
+      <c r="P99" s="7"/>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B100" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M100" s="7"/>
+      <c r="N100" s="7"/>
+      <c r="O100" s="7"/>
+      <c r="P100" s="7"/>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B101" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="H101" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+      <c r="P101" s="7"/>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B102" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M102" s="7"/>
+      <c r="N102" s="7"/>
+      <c r="O102" s="7"/>
+      <c r="P102" s="7"/>
+    </row>
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B103" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M103" s="7"/>
+      <c r="N103" s="7"/>
+      <c r="O103" s="7"/>
+      <c r="P103" s="7"/>
+    </row>
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B104" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M104" s="7"/>
+      <c r="N104" s="7"/>
+      <c r="O104" s="7"/>
+      <c r="P104" s="7"/>
+    </row>
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B105" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="N105" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="O105" s="7"/>
+      <c r="P105" s="7"/>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B106" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M106" s="7"/>
+      <c r="N106" s="7"/>
+      <c r="O106" s="7"/>
+      <c r="P106" s="7"/>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B107" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="F107" s="16"/>
+      <c r="G107" s="16"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M107" s="7"/>
+      <c r="N107" s="7"/>
+      <c r="O107" s="7"/>
+      <c r="P107" s="7"/>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B108" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I108" s="7"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M108" s="7"/>
+      <c r="N108" s="7"/>
+      <c r="O108" s="7"/>
+      <c r="P108" s="7"/>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B109" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H109" t="s">
+        <v>220</v>
+      </c>
+      <c r="I109" s="7"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M109" s="7"/>
+      <c r="N109" s="7"/>
+      <c r="O109" s="7"/>
+      <c r="P109" s="7"/>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B110" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F110" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="H110" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I110" s="7"/>
+      <c r="J110" s="7"/>
+      <c r="K110" s="7"/>
+      <c r="L110" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M110" s="7"/>
+      <c r="N110" s="7"/>
+      <c r="O110" s="7"/>
+      <c r="P110" s="7"/>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B111" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="7"/>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B112" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F112" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="H112" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M112" s="7"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="7"/>
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B113" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="P113" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -5012,7 +6355,7 @@
         <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M3" t="s">
         <v>82</v>
@@ -5032,7 +6375,7 @@
         <v>254</v>
       </c>
       <c r="H4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M4" t="s">
         <v>254</v>
@@ -5052,7 +6395,7 @@
         <v>213</v>
       </c>
       <c r="H5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M5" t="s">
         <v>213</v>
@@ -5072,7 +6415,7 @@
         <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M6" t="s">
         <v>76</v>
@@ -5089,10 +6432,10 @@
         <v>217</v>
       </c>
       <c r="G7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H7" t="s">
         <v>288</v>
-      </c>
-      <c r="H7" t="s">
-        <v>289</v>
       </c>
       <c r="M7" t="s">
         <v>258</v>
@@ -5112,7 +6455,7 @@
         <v>258</v>
       </c>
       <c r="H8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M8" t="s">
         <v>80</v>
@@ -5132,7 +6475,7 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M9" t="s">
         <v>261</v>
@@ -5152,7 +6495,7 @@
         <v>261</v>
       </c>
       <c r="H10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M10" t="s">
         <v>263</v>
@@ -5172,7 +6515,7 @@
         <v>263</v>
       </c>
       <c r="H11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M11" t="s">
         <v>265</v>
@@ -5192,7 +6535,7 @@
         <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M12" t="s">
         <v>182</v>
@@ -5212,7 +6555,7 @@
         <v>220</v>
       </c>
       <c r="H13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M13" t="s">
         <v>220</v>
@@ -5232,7 +6575,7 @@
         <v>222</v>
       </c>
       <c r="H14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M14" t="s">
         <v>222</v>
@@ -5252,7 +6595,7 @@
         <v>271</v>
       </c>
       <c r="H15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M15" t="s">
         <v>224</v>
@@ -5272,7 +6615,7 @@
         <v>227</v>
       </c>
       <c r="H16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M16" t="s">
         <v>271</v>
@@ -5292,7 +6635,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M17" t="s">
         <v>272</v>
@@ -5312,7 +6655,7 @@
         <v>183</v>
       </c>
       <c r="H18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M18" t="s">
         <v>274</v>
@@ -5332,7 +6675,7 @@
         <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M19" t="s">
         <v>78</v>
@@ -5521,7 +6864,7 @@
         <v>186</v>
       </c>
       <c r="M31" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P31" t="s">
         <v>147</v>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B88485-E0F2-48AB-A2C1-463FAB38E153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F613F-6152-4B8A-A5D4-6447C0B0071E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="557">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1222,10 +1222,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>0.2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>wait1 face_wait lip_surp</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1357,15 +1353,9 @@
     <t>surp1</t>
   </si>
   <si>
-    <t>그러니까 싫은 거야. 그렇게 보는 눈이 많은 곳에서 넘어지기라도 해 봐.</t>
-  </si>
-  <si>
     <t>s001011</t>
   </si>
   <si>
-    <t>애초에 후유, 달리기 그렇게 잘 하는 편이 아니니까…</t>
-  </si>
-  <si>
     <t>s001012</t>
   </si>
   <si>
@@ -1375,9 +1365,6 @@
     <t>s001013</t>
   </si>
   <si>
-    <t>그렇구나… 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
-  </si>
-  <si>
     <t>s001014</t>
   </si>
   <si>
@@ -1692,14 +1679,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>AUIDO</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_100</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>후유코쨩, 정말 괜찮아?</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1782,10 +1761,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait4 lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>메이가 이야기했듯이, 이어달리기는 운동회의 꽃이니까.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1821,10 +1796,6 @@
     <t>s001066</t>
   </si>
   <si>
-    <t>anger2 face_cry lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>TEXT</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1912,10 +1883,6 @@
     <t>s001075</t>
   </si>
   <si>
-    <t>think1 lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>몰라도 돼, 너는.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1973,10 +1940,6 @@
     <t>s001083</t>
   </si>
   <si>
-    <t>너가 그만큼 열심히 달리면 되잖아!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>s001084</t>
   </si>
   <si>
@@ -1988,6 +1951,128 @@
   </si>
   <si>
     <t>wipe_left</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_jito lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러니까 싫은 거야. 보는 눈이 너무 많으니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_close3 lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>애초에 후유, 달리기 그렇게 잘 하는 편도 아니고…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그렇구나… </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001086</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile3 face_serious lip_serious_s</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>저번에 나간 대운동회에서는 이상한 얼굴 캡쳐당해서 한동안 돌아다녔고…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001087</t>
+  </si>
+  <si>
+    <t>wait4 face_serious lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런 거, 두번 다시 사양이야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s001088</t>
+  </si>
+  <si>
+    <t>좋아! 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger2 face_smile2 lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>smile1 face_cry lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>하기 싫어도 해야 하는 일…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S001089</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1 face_serious lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug face_close</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>나가주는 것 만으로도 감사하게 생각하란 말이야!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S001090</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 1등이 하고 싶으면, 네가 후유의 몫까지 달리면 되잖아</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>경쾌한 일상</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_101</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_77</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2252,12 +2337,12 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -2324,28 +2409,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P113" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P113" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P121" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P121" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="13">
+    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="11">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="11" dataCellStyle="표준 2">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="10" dataCellStyle="표준 2">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@CG" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Position" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Animation" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect" dataDxfId="7">
@@ -2855,7 +2940,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -3139,7 +3224,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
-  <dimension ref="B2:P113"/>
+  <dimension ref="B2:P121"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -3208,7 +3293,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3218,15 +3303,15 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7" t="s">
-        <v>39</v>
+        <v>526</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>300</v>
+        <v>554</v>
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -3249,12 +3334,12 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3267,7 +3352,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -3281,19 +3366,19 @@
         <v>241</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3311,22 +3396,22 @@
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>316</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3347,19 +3432,19 @@
         <v>241</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>319</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -3377,22 +3462,22 @@
         <v>88</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -3413,19 +3498,19 @@
         <v>241</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>325</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
@@ -3446,10 +3531,10 @@
         <v>241</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>327</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -3467,7 +3552,7 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -3476,7 +3561,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -3497,10 +3582,10 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -3508,12 +3593,12 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -3526,10 +3611,10 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
@@ -3539,22 +3624,22 @@
         <v>88</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>335</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -3575,19 +3660,19 @@
         <v>241</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>337</v>
-      </c>
       <c r="F16" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -3605,22 +3690,22 @@
         <v>88</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>67</v>
+        <v>527</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -3641,19 +3726,19 @@
         <v>241</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>342</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -3671,22 +3756,22 @@
         <v>88</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>343</v>
+        <v>528</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>67</v>
+        <v>529</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -3704,17 +3789,23 @@
         <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>345</v>
+        <v>530</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+        <v>343</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>531</v>
+      </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -3731,13 +3822,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3755,32 +3846,30 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>88</v>
+        <v>482</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>241</v>
+        <v>64</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>349</v>
+        <v>532</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>350</v>
+        <v>533</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>325</v>
+      <c r="H22" t="s">
+        <v>534</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -3788,32 +3877,30 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>88</v>
+        <v>482</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>351</v>
+        <v>535</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>352</v>
+        <v>536</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>353</v>
+        <v>537</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L23" s="7"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -3821,32 +3908,24 @@
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>88</v>
+        <v>482</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>354</v>
+        <v>538</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>356</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -3857,22 +3936,22 @@
         <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>357</v>
+        <v>540</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>197</v>
+        <v>310</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>138</v>
+        <v>541</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -3893,19 +3972,19 @@
         <v>241</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="H26" s="7" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -3923,22 +4002,22 @@
         <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
@@ -3953,20 +4032,32 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
-        <v>329</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
+      <c r="L28" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
@@ -3974,78 +4065,86 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>309</v>
+      </c>
       <c r="G29" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="H29" s="7"/>
+        <v>310</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>357</v>
+      </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
+      <c r="L29" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="7" t="s">
-        <v>305</v>
-      </c>
+      <c r="P29" s="7"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="7"/>
+      <c r="L30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7" t="s">
-        <v>366</v>
-      </c>
+      <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I31" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
@@ -4053,30 +4152,30 @@
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="G32" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
-        <v>369</v>
-      </c>
+      <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
-      <c r="O32" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="P32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4085,13 +4184,13 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="K33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="L33" s="7"/>
       <c r="M33" s="7" t="s">
-        <v>39</v>
+        <v>362</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -4099,128 +4198,122 @@
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>341</v>
+      </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
+      <c r="L34" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
-      <c r="P34" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P34" s="7"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>88</v>
+        <v>327</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="I35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7" t="s">
+        <v>365</v>
+      </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="O35" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>376</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+      <c r="J36" s="7" t="s">
+        <v>302</v>
+      </c>
       <c r="K36" s="7"/>
-      <c r="L36" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>554</v>
+      </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>379</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="7" t="s">
-        <v>377</v>
-      </c>
+      <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
       <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
+      <c r="P37" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>381</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
+      <c r="I38" s="7" t="s">
+        <v>542</v>
+      </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
-      <c r="L38" s="7" t="s">
-        <v>377</v>
-      </c>
+      <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
@@ -4230,23 +4323,23 @@
       <c r="B39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>369</v>
+      </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7" t="s">
-        <v>377</v>
+        <v>543</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -4258,28 +4351,22 @@
         <v>88</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G40" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>386</v>
-      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -4291,13 +4378,13 @@
         <v>88</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -4306,7 +4393,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -4318,13 +4405,13 @@
         <v>88</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -4333,7 +4420,7 @@
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
@@ -4345,28 +4432,22 @@
         <v>88</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>393</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
@@ -4378,22 +4459,28 @@
         <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+        <v>381</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>382</v>
+      </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4405,13 +4492,13 @@
         <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4420,7 +4507,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4432,28 +4519,22 @@
         <v>88</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>400</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -4465,22 +4546,28 @@
         <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
+        <v>388</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>389</v>
+      </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4492,28 +4579,22 @@
         <v>88</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>405</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4525,13 +4606,13 @@
         <v>88</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -4540,7 +4621,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4555,19 +4636,19 @@
         <v>240</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
@@ -4585,13 +4666,13 @@
         <v>88</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -4600,7 +4681,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4612,22 +4693,28 @@
         <v>88</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+        <v>400</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4636,20 +4723,26 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="7" t="s">
-        <v>329</v>
-      </c>
+      <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
+      <c r="L53" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
@@ -4657,60 +4750,86 @@
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>382</v>
+      </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
+      <c r="L54" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P54" s="7"/>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7" t="s">
-        <v>414</v>
-      </c>
+      <c r="L55" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M55" s="7"/>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>409</v>
+      </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
+      <c r="L56" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -4718,32 +4837,20 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="I57" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
-      <c r="L57" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
@@ -4751,98 +4858,62 @@
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>319</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
-      <c r="L58" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
+      <c r="P58" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>423</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
-      <c r="L59" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7" t="s">
+        <v>410</v>
+      </c>
       <c r="N59" s="7"/>
       <c r="O59" s="7"/>
       <c r="P59" s="7"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="I60" s="7"/>
+        <v>411</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7" t="s">
+        <v>542</v>
+      </c>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
-      <c r="L60" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L60" s="7"/>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
       <c r="O60" s="7"/>
@@ -4853,22 +4924,28 @@
         <v>88</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>427</v>
+        <v>312</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
+        <v>413</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7" t="s">
-        <v>430</v>
+        <v>89</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -4880,22 +4957,28 @@
         <v>88</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>427</v>
+        <v>241</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
+        <v>416</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7" t="s">
-        <v>430</v>
+        <v>89</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
@@ -4907,22 +4990,28 @@
         <v>88</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
+        <v>418</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
@@ -4934,22 +5023,28 @@
         <v>88</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
+        <v>421</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>422</v>
+      </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
@@ -4961,13 +5056,13 @@
         <v>88</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>374</v>
+        <v>423</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -4976,7 +5071,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
@@ -4988,13 +5083,13 @@
         <v>88</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>439</v>
-      </c>
       <c r="E66" s="7" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -5003,7 +5098,7 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
@@ -5015,28 +5110,22 @@
         <v>88</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
@@ -5048,28 +5137,22 @@
         <v>88</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>418</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
@@ -5081,28 +5164,22 @@
         <v>88</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>342</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
@@ -5114,13 +5191,13 @@
         <v>88</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
@@ -5129,7 +5206,7 @@
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
@@ -5141,22 +5218,28 @@
         <v>88</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>374</v>
+        <v>241</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
+        <v>438</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
@@ -5168,22 +5251,22 @@
         <v>88</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
@@ -5198,39 +5281,59 @@
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>341</v>
+      </c>
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7" t="s">
-        <v>453</v>
-      </c>
+      <c r="L73" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M73" s="7"/>
       <c r="N73" s="7"/>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>444</v>
+      </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
+      <c r="L74" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
@@ -5238,55 +5341,67 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>446</v>
+      </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
-      <c r="I75" s="7" t="s">
-        <v>369</v>
-      </c>
+      <c r="I75" s="7"/>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
+      <c r="L75" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="7" t="s">
-        <v>370</v>
-      </c>
+      <c r="O75" s="7"/>
       <c r="P75" s="7"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="I76" s="7"/>
-      <c r="J76" s="7" t="s">
-        <v>303</v>
-      </c>
+      <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="N76" s="7" t="s">
-        <v>300</v>
-      </c>
+      <c r="L76" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -5298,41 +5413,27 @@
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c r="M77" s="7" t="s">
+        <v>449</v>
+      </c>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
-      <c r="P77" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P77" s="7"/>
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H78" t="s">
-        <v>139</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
-      <c r="L78" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L78" s="7"/>
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
@@ -5340,116 +5441,89 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="I79" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7" t="s">
+        <v>365</v>
+      </c>
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
-      <c r="L79" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L79" s="7"/>
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
+      <c r="O79" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="P79" s="7"/>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D80" t="s">
-        <v>463</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>464</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
       <c r="F80" s="7"/>
-      <c r="L80" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>467</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
+      <c r="P81" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I82" s="7"/>
+        <v>411</v>
+      </c>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7" t="s">
+        <v>542</v>
+      </c>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
-      <c r="L82" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L82" s="7"/>
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
       <c r="O82" s="7"/>
@@ -5460,22 +5534,28 @@
         <v>88</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>427</v>
+        <v>241</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
+        <v>451</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="H83" t="s">
+        <v>139</v>
+      </c>
       <c r="I83" s="7"/>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7" t="s">
-        <v>430</v>
+        <v>89</v>
       </c>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
@@ -5484,145 +5564,172 @@
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>415</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>472</v>
+        <v>312</v>
+      </c>
+      <c r="D85" t="s">
+        <v>457</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="F85" t="s">
-        <v>474</v>
-      </c>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
+        <v>458</v>
+      </c>
+      <c r="F85" s="7"/>
       <c r="L85" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="7"/>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D86" t="s">
-        <v>475</v>
+        <v>240</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>477</v>
+        <v>368</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="I86" s="7"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M86" s="7"/>
+      <c r="N86" s="7"/>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D87" t="s">
-        <v>479</v>
+        <v>312</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M87" s="7"/>
+      <c r="N87" s="7"/>
+      <c r="O87" s="7"/>
+      <c r="P87" s="7"/>
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D88" t="s">
-        <v>481</v>
+        <v>423</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>464</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="M88" s="7"/>
+      <c r="N88" s="7"/>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
+        <v>411</v>
+      </c>
+      <c r="K89">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
+        <v>467</v>
+      </c>
+      <c r="F90" t="s">
+        <v>468</v>
+      </c>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
@@ -5639,115 +5746,82 @@
         <v>88</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>487</v>
+        <v>312</v>
+      </c>
+      <c r="D91" t="s">
+        <v>469</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
+        <v>544</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>490</v>
+        <v>88</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>491</v>
+        <v>312</v>
+      </c>
+      <c r="D92" t="s">
+        <v>472</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H92" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
+        <v>473</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>494</v>
+        <v>312</v>
+      </c>
+      <c r="D93" t="s">
+        <v>474</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="F93" t="s">
-        <v>474</v>
-      </c>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
+        <v>475</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="G94" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>498</v>
+        <v>477</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>352</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
@@ -5765,17 +5839,17 @@
         <v>88</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="17"/>
+        <v>479</v>
+      </c>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
@@ -5789,46 +5863,58 @@
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>315</v>
+      </c>
       <c r="G96" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>503</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
       <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
+      <c r="L96" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
       <c r="O96" s="7"/>
-      <c r="P96" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P96" s="7"/>
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>88</v>
+        <v>482</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="F97" t="s">
-        <v>474</v>
+        <v>484</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>485</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="7"/>
@@ -5846,22 +5932,16 @@
         <v>88</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>148</v>
+        <v>487</v>
+      </c>
+      <c r="F98" t="s">
+        <v>468</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
@@ -5879,17 +5959,23 @@
         <v>88</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
+        <v>489</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>490</v>
+      </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
       <c r="K99" s="7"/>
@@ -5906,17 +5992,17 @@
         <v>88</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
+        <v>492</v>
+      </c>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="17"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
@@ -5930,58 +6016,46 @@
     </row>
     <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="F101" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="G101" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="H101" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="K101" s="7"/>
-      <c r="L101" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L101" s="7"/>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
       <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
+      <c r="P101" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>150</v>
+        <v>497</v>
+      </c>
+      <c r="F102" t="s">
+        <v>468</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
@@ -5996,47 +6070,34 @@
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
-      <c r="L103" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M103" s="7"/>
-      <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="7"/>
+        <v>411</v>
+      </c>
+      <c r="K103">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
+        <v>499</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>148</v>
+      </c>
       <c r="I104" s="7"/>
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
@@ -6050,24 +6111,28 @@
     </row>
     <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>501</v>
+      </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="N105" s="7" t="s">
-        <v>333</v>
-      </c>
+      <c r="L105" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M105" s="7"/>
+      <c r="N105" s="7"/>
       <c r="O105" s="7"/>
       <c r="P105" s="7"/>
     </row>
@@ -6076,23 +6141,17 @@
         <v>88</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F106" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="G106" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="H106" s="15" t="s">
-        <v>498</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -6112,14 +6171,20 @@
         <v>240</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="F107" s="16"/>
-      <c r="G107" s="16"/>
-      <c r="H107" s="15"/>
+        <v>547</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="H107" s="17" t="s">
+        <v>548</v>
+      </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
@@ -6136,23 +6201,17 @@
         <v>88</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>82</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="17"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
@@ -6169,22 +6228,22 @@
         <v>88</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>241</v>
+        <v>312</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="H109" t="s">
-        <v>220</v>
+        <v>452</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>549</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
@@ -6202,23 +6261,17 @@
         <v>88</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="F110" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="G110" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="H110" s="17" t="s">
-        <v>82</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
@@ -6235,23 +6288,17 @@
         <v>88</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>211</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
@@ -6271,19 +6318,19 @@
         <v>240</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="H112" s="17" t="s">
-        <v>82</v>
+        <v>455</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>490</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
@@ -6298,7 +6345,7 @@
     </row>
     <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -6306,18 +6353,260 @@
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
-      <c r="I113" s="7" t="s">
-        <v>535</v>
-      </c>
+      <c r="I113" s="7"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="7" t="s">
-        <v>370</v>
-      </c>
+      <c r="M113" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="N113" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="O113" s="7"/>
       <c r="P113" s="7"/>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B114" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M114" s="7"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+    </row>
+    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B115" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I115" s="7"/>
+      <c r="J115" s="7"/>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M115" s="7"/>
+      <c r="N115" s="7"/>
+      <c r="O115" s="7"/>
+      <c r="P115" s="7"/>
+    </row>
+    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B116" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="7"/>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M116" s="7"/>
+      <c r="N116" s="7"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="7"/>
+    </row>
+    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B117" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="H117" t="s">
+        <v>220</v>
+      </c>
+      <c r="I117" s="7"/>
+      <c r="J117" s="7"/>
+      <c r="K117" s="7"/>
+      <c r="L117" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M117" s="7"/>
+      <c r="N117" s="7"/>
+      <c r="O117" s="7"/>
+      <c r="P117" s="7"/>
+    </row>
+    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B118" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F118" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="H118" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I118" s="7"/>
+      <c r="J118" s="7"/>
+      <c r="K118" s="7"/>
+      <c r="L118" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M118" s="7"/>
+      <c r="N118" s="7"/>
+      <c r="O118" s="7"/>
+      <c r="P118" s="7"/>
+    </row>
+    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B119" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+    </row>
+    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B120" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="F120" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G120" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="H120" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I120" s="7"/>
+      <c r="J120" s="7"/>
+      <c r="K120" s="7"/>
+      <c r="L120" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M120" s="7"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="7"/>
+      <c r="P120" s="7"/>
+    </row>
+    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B121" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="J121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7"/>
+      <c r="M121" s="7"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="P121" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -6864,7 +7153,7 @@
         <v>186</v>
       </c>
       <c r="M31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P31" t="s">
         <v>147</v>
@@ -7139,7 +7428,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAFF6E4-78A0-4059-AA76-1F2F07C1CB1A}">
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:F19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
@@ -7282,6 +7571,14 @@
         <v>101</v>
       </c>
     </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F613F-6152-4B8A-A5D4-6447C0B0071E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2762FDBF-85A5-4108-B10E-2982731A1CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="559">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2073,6 +2073,14 @@
   </si>
   <si>
     <t>BGM_77</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 메이 무표정으로 말할 때에는 lip_surp 쓰세요</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 사히 무표정으로 말할 때에는 lip_surp 쓰세요</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2080,7 +2088,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -2179,6 +2187,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="넥슨Lv2고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2243,7 +2258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2296,6 +2311,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7002,11 +7020,8 @@
       <c r="E22" t="s">
         <v>69</v>
       </c>
-      <c r="G22" t="s">
-        <v>65</v>
-      </c>
-      <c r="J22" t="s">
-        <v>72</v>
+      <c r="G22" s="18" t="s">
+        <v>557</v>
       </c>
       <c r="M22" t="s">
         <v>183</v>
@@ -7022,12 +7037,6 @@
       <c r="E23" t="s">
         <v>70</v>
       </c>
-      <c r="G23" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" t="s">
-        <v>73</v>
-      </c>
       <c r="M23" t="s">
         <v>281</v>
       </c>
@@ -7042,12 +7051,6 @@
       <c r="E24" t="s">
         <v>84</v>
       </c>
-      <c r="G24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
@@ -7057,16 +7060,13 @@
         <v>144</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="J25" t="s">
-        <v>140</v>
-      </c>
-      <c r="M25" t="s">
-        <v>90</v>
-      </c>
-      <c r="P25" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
@@ -7077,16 +7077,16 @@
         <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="P26" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
@@ -7096,11 +7096,17 @@
       <c r="E27" t="s">
         <v>151</v>
       </c>
+      <c r="G27" t="s">
+        <v>86</v>
+      </c>
+      <c r="J27" t="s">
+        <v>87</v>
+      </c>
       <c r="M27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
@@ -7110,11 +7116,17 @@
       <c r="E28" t="s">
         <v>179</v>
       </c>
+      <c r="G28" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" t="s">
+        <v>140</v>
+      </c>
       <c r="M28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
@@ -7124,11 +7136,17 @@
       <c r="E29" t="s">
         <v>181</v>
       </c>
+      <c r="G29" t="s">
+        <v>145</v>
+      </c>
+      <c r="J29" t="s">
+        <v>146</v>
+      </c>
       <c r="M29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
@@ -7139,10 +7157,10 @@
         <v>185</v>
       </c>
       <c r="M30" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
@@ -7153,10 +7171,10 @@
         <v>186</v>
       </c>
       <c r="M31" t="s">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="P31" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
@@ -7165,6 +7183,12 @@
       </c>
       <c r="E32" t="s">
         <v>187</v>
+      </c>
+      <c r="M32" t="s">
+        <v>300</v>
+      </c>
+      <c r="P32" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2762FDBF-85A5-4108-B10E-2982731A1CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7D31FD-91B2-4F4B-B070-35FF9B0D337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="468">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -885,10 +885,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>오른팔 올려서 가드</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>shrug2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -909,10 +905,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>오른팔 넓게 가드</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>smile3</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -937,14 +929,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>뒤로 놀라기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞으로 놀라기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>think</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -969,18 +953,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>들썩 후 모으기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 절레절레</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>들썩 후 끄덕</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>BG</t>
   </si>
   <si>
@@ -1238,857 +1210,649 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>bg_rouka</t>
-  </si>
-  <si>
     <t>SE</t>
   </si>
   <si>
-    <t>se_jihannki</t>
-  </si>
-  <si>
-    <t>아 후유코쨩, 그거 들었어?</t>
-  </si>
-  <si>
-    <t>s001001</t>
-  </si>
-  <si>
-    <t>mei_idol_3</t>
+    <t>후유코</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>iris</t>
+  </si>
+  <si>
+    <t>se_trans_out|se_trans_in</t>
+  </si>
+  <si>
+    <t>se_door_ake</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAK</t>
+  </si>
+  <si>
+    <t>프로듀서</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>se_door_sime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>left</t>
-  </si>
-  <si>
-    <t>wait1</t>
-  </si>
-  <si>
-    <t>후유코</t>
-  </si>
-  <si>
-    <t>그거?</t>
-  </si>
-  <si>
-    <t>s001002</t>
-  </si>
-  <si>
-    <t>fuyuko_idol_3</t>
-  </si>
-  <si>
-    <t>다음 달에 있는 운동회 이야기!</t>
-  </si>
-  <si>
-    <t>s001003</t>
-  </si>
-  <si>
-    <t>wait2</t>
-  </si>
-  <si>
-    <t>아 그러고보니…</t>
-  </si>
-  <si>
-    <t>s001004</t>
-  </si>
-  <si>
-    <t>think</t>
-  </si>
-  <si>
-    <t>이번에는 유닛 별로 종목을 고를 수 있대~</t>
-  </si>
-  <si>
-    <t>s001005</t>
-  </si>
-  <si>
-    <t>smile2</t>
-  </si>
-  <si>
-    <t>후유코쨩은 뭐 나가고 싶어?</t>
-  </si>
-  <si>
-    <t>s001006</t>
-  </si>
-  <si>
-    <t>TRANSITION</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>center</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>zoom</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>경쾌한 일상</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 메이 무표정으로 말할 때에는 lip_surp 쓰세요</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 사히 무표정으로 말할 때에는 lip_surp 쓰세요</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>센치한 과거 회상</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_phone</t>
+  </si>
+  <si>
+    <t>se_phone_long</t>
+  </si>
+  <si>
+    <t>flashback</t>
+  </si>
+  <si>
+    <t>fuyuko_sports_2</t>
+  </si>
+  <si>
+    <t>smile1 face_serious</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait4 face_close3 lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hasisita_sunset</t>
+  </si>
+  <si>
+    <t>그럼, 내가 후유코쨩이 진심으로 달리지 않아도 될 만큼\n엄~청 빠르게 달리면 된다는 거잖아?</t>
+  </si>
+  <si>
+    <t>S002077</t>
+  </si>
+  <si>
+    <t>S002078</t>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Close1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>웃으면서 눈감기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>close2/3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>야레야레</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>close4/5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>화내면서 눈감기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>fase_jito 1 &gt; 2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>화내는 정도</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>normal</t>
-  </si>
-  <si>
-    <t>zoom</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>se_tansan</t>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>음… 그러네…</t>
-  </si>
-  <si>
-    <t>s001007</t>
-  </si>
-  <si>
-    <t>계주라던가, 어때?</t>
-  </si>
-  <si>
-    <t>s001008</t>
-  </si>
-  <si>
-    <t>아… 최악이야. 계주같은 건, 죽어도 사양이야</t>
-  </si>
-  <si>
-    <t>s001009</t>
-  </si>
-  <si>
-    <t>에, 정말? 계주는 운동회의 꽃이잖아?</t>
-  </si>
-  <si>
-    <t>s001010</t>
-  </si>
-  <si>
-    <t>surp1</t>
-  </si>
-  <si>
-    <t>s001011</t>
-  </si>
-  <si>
-    <t>s001012</t>
-  </si>
-  <si>
-    <t>팬들에게 완벽하지 않은 모습은 보여주고 싶지 않아.</t>
-  </si>
-  <si>
-    <t>s001013</t>
-  </si>
-  <si>
-    <t>s001014</t>
-  </si>
-  <si>
-    <t>아, 근데 아사히쨩은 분명 이어달리기 나가고 싶어할 텐데…</t>
-  </si>
-  <si>
-    <t>s001015</t>
-  </si>
-  <si>
-    <t>skill2 face_sad</t>
-  </si>
-  <si>
-    <t>그 녀석 성격 상, 무조건 그렇겠지…</t>
-  </si>
-  <si>
-    <t>s001016</t>
-  </si>
-  <si>
-    <t>wait2 face_serious lip_sad</t>
-  </si>
-  <si>
-    <t>잠깐만, 메이.</t>
-  </si>
-  <si>
-    <t>s001017</t>
-  </si>
-  <si>
-    <t>후유코쨩?</t>
-  </si>
-  <si>
-    <t>s001018</t>
-  </si>
-  <si>
-    <t>wait1 face_surp</t>
-  </si>
-  <si>
-    <t>왠지 불길한 기분이 들어… 빨리 돌아가자.</t>
-  </si>
-  <si>
-    <t>s001019</t>
-  </si>
-  <si>
-    <t>wait4 face_jito lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait3 face_surp lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 의문</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈감고 절레절레</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>끄덕하면서 웃기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유모드 놀라기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐텐 놀람 (경악)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>깜짝 놀람</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른팔 올리기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_hikaesitu2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭠까?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>asahi_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_sports_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_sad</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_runninTrack_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashback</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait5 face_jito lip_anger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸네.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003092</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가버렸슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S003093</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM_131</t>
+  </si>
+  <si>
+    <t>anger2 face_serious lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아사히쨩.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004001</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004002</t>
+  </si>
+  <si>
+    <t>분해?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004003</t>
+  </si>
+  <si>
+    <t>bg_ceiling</t>
+  </si>
+  <si>
+    <t>se_sofa_sitdown</t>
+  </si>
+  <si>
+    <t>달리기 시작하면 바로 따라잡을 줄 알았슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004004</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>작년에 그랬던 것처럼.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004005</t>
+  </si>
+  <si>
+    <t>분명, 결승선 직전에 아슬아슬하게 추월했다고 했지.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004006</t>
+  </si>
+  <si>
+    <t>se_sofa_wait</t>
+  </si>
+  <si>
+    <t>저는 후유코쨩이나 메이쨩처럼 연습 같은 거 안 했슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004007</t>
+  </si>
+  <si>
+    <t>해야겠다는 생각도 안 했슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004008</t>
+  </si>
+  <si>
+    <t>만약 졌다고 하더라도,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004009</t>
+  </si>
+  <si>
+    <t>그건 아사히쨩의 책임이 아니야.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004010</t>
+  </si>
+  <si>
+    <t>책임…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004011</t>
+  </si>
+  <si>
+    <t>se_sofa_wakeup</t>
+  </si>
+  <si>
+    <t>잠깐 뛰고 오겠슴다.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004012</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>shy1 face_wait lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004013</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 face_serious lip_shy</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>현장 정리 중이니까 안 된다고 해야 되는데…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad2 lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>mei_sports_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 한 팀이니까!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아하하…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004015</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>sad1 lip_smile1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이렇게 큰 소리 쳐놓고 진 사람도 있는데 말이야…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004016</t>
+  </si>
+  <si>
+    <t>그 때, 후유코쨩의 표정…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004017</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 두 사람한테…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004018</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무런 도움도…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004019</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 역시 나도 뛰고 올래.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004020</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger1 face_serious lip_anger2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러니까, 그런 게…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>어라?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>se_rouka_run</t>
-  </si>
-  <si>
-    <t>자, 잠깐만 후유코쨩!</t>
-  </si>
-  <si>
-    <t>s001020</t>
-  </si>
-  <si>
-    <t>iris</t>
-  </si>
-  <si>
-    <t>se_trans_out|se_trans_in</t>
-  </si>
-  <si>
-    <t>asahi_idol_3</t>
-  </si>
-  <si>
-    <t>center</t>
-  </si>
-  <si>
-    <t>wait1 face_smile</t>
-  </si>
-  <si>
-    <t>방송 PD</t>
-  </si>
-  <si>
-    <t>와하하! 좋네, 그거!</t>
-  </si>
-  <si>
-    <t>s001021</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>아사히쨩이 달리는 거, 분명 그림이 될 테니까!</t>
-  </si>
-  <si>
-    <t>s001022</t>
-  </si>
-  <si>
-    <t>작년 방송이 꽤 화제가 돼서 말이야.</t>
-  </si>
-  <si>
-    <t>s001023</t>
-  </si>
-  <si>
-    <t>이번에는 이어달리기용 원샷 카메라도 준비해뒀다고!</t>
-  </si>
-  <si>
-    <t>s001024</t>
-  </si>
-  <si>
-    <t>그거, 본 적 있슴다!</t>
-  </si>
-  <si>
-    <t>s001025</t>
-  </si>
-  <si>
-    <t>smile3 lip_wait</t>
-  </si>
-  <si>
-    <t>카메라 감독님이 카메라를 들고 선수보다 빨리 뛰는 거!</t>
-  </si>
-  <si>
-    <t>s001026</t>
-  </si>
-  <si>
-    <t>아니, 아무리 그래도 직접 들고 뛰진 않지~</t>
-  </si>
-  <si>
-    <t>s001027</t>
-  </si>
-  <si>
-    <t>뭐야, 직접 뛰는 건 줄 알았슴다…</t>
-  </si>
-  <si>
-    <t>s001028</t>
-  </si>
-  <si>
-    <t>sad2 lip_anger</t>
-  </si>
-  <si>
-    <t>뭐, 옛날에는 직접 들고 뛰었을지도 모르겠지만</t>
-  </si>
-  <si>
-    <t>s001029</t>
-  </si>
-  <si>
-    <t>지금은 보통 트랙 러너 카메라라는 녀석으로 찍거든</t>
-  </si>
-  <si>
-    <t>s001030</t>
-  </si>
-  <si>
-    <t>그 트랙 러너 카메라라는 거, 빠른 검까?</t>
-  </si>
-  <si>
-    <t>s001031</t>
-  </si>
-  <si>
-    <t>think1</t>
-  </si>
-  <si>
-    <t>그야 달리는 선수들을 찍어야 하니까 당연히…</t>
-  </si>
-  <si>
-    <t>s001032</t>
-  </si>
-  <si>
-    <t>그럼, 그 녀석을 이기면 제가 1등인 거네요?</t>
-  </si>
-  <si>
-    <t>s001033</t>
-  </si>
-  <si>
-    <t>skill1</t>
-  </si>
-  <si>
-    <t>아하하! 그렇네, 아사히쨩이 이길 수 있다면 말이지!</t>
-  </si>
-  <si>
-    <t>s001034</t>
-  </si>
-  <si>
-    <t>그 트랙… 무슨 카메라는 지금 어디있슴까?</t>
-  </si>
-  <si>
-    <t>s001035</t>
-  </si>
-  <si>
-    <t>빨리 승부하고 싶슴다!</t>
-  </si>
-  <si>
-    <t>s001036</t>
-  </si>
-  <si>
-    <t>아쉽게도 다음 달 대여 예정이라서</t>
-  </si>
-  <si>
-    <t>s001037</t>
-  </si>
-  <si>
-    <t>se_door_ake</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BREAK</t>
-  </si>
-  <si>
-    <t>수고하십니다~</t>
-  </si>
-  <si>
-    <t>s001038</t>
-  </si>
-  <si>
-    <t>smile1</t>
-  </si>
-  <si>
-    <t>수고하십니다.</t>
-  </si>
-  <si>
-    <t>s001039</t>
-  </si>
-  <si>
-    <t>다음 달까지는 못 기다림다~</t>
-  </si>
-  <si>
-    <t>s001040</t>
-  </si>
-  <si>
-    <t>anger1</t>
-  </si>
-  <si>
-    <t>저기, 프로듀서 님… 이건…?</t>
-  </si>
-  <si>
-    <t>s001041</t>
-  </si>
-  <si>
-    <t>wait1 face_smile lip_bitter_smile</t>
-  </si>
-  <si>
-    <t>프로듀서</t>
-  </si>
-  <si>
-    <t>아 후유코, 메이. 어서 와.</t>
-  </si>
-  <si>
-    <t>s001042</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PD님이랑 아사히가 다음 달에 나갈 운동회 이야기를 하고 있던 중이었는데…</t>
-  </si>
-  <si>
-    <t>s001043</t>
-  </si>
-  <si>
-    <t>어, 마침 잘 왔네!</t>
-  </si>
-  <si>
-    <t>s001044</t>
-  </si>
-  <si>
-    <t>스트레이라이트한테는 꼭 이어달리기에 나가줬으면 해서!</t>
-  </si>
-  <si>
-    <t>s001045</t>
-  </si>
-  <si>
-    <t>두 사람도 괜찮지? 운동 잘 하잖아?</t>
-  </si>
-  <si>
-    <t>s001046</t>
-  </si>
-  <si>
-    <t>P, PD님, 잠시…</t>
-  </si>
-  <si>
-    <t>s001047</t>
-  </si>
-  <si>
-    <t>아, 그건…</t>
-  </si>
-  <si>
-    <t>s001048</t>
-  </si>
-  <si>
-    <t>네. 저희한테 맡겨주세요.</t>
-  </si>
-  <si>
-    <t>s001049</t>
-  </si>
-  <si>
-    <t>후, 후유코쨩…?</t>
-  </si>
-  <si>
-    <t>s001050</t>
-  </si>
-  <si>
-    <t>후유코…?</t>
-  </si>
-  <si>
-    <t>s001051</t>
-  </si>
-  <si>
-    <t>아하하, 좋네! 그럼 다음 달에 잘 부탁해!</t>
-  </si>
-  <si>
-    <t>s001052</t>
-  </si>
-  <si>
-    <t>네, 잘 부탁드립니다~</t>
-  </si>
-  <si>
-    <t>s001053</t>
-  </si>
-  <si>
-    <t>se_door_sime</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩, 정말 괜찮아?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001054</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>left</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>괜찮을 리가 없잖아.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001055</t>
-  </si>
-  <si>
-    <t>right</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug2 lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>왜 후유가 이 녀석 때문에 이어달리기에 나가야 되는 건데</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001056</t>
-  </si>
-  <si>
-    <t>그치만 나가겠다고 한 건 후유코쨩임다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001057</t>
-  </si>
-  <si>
-    <t>wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 분위기에서 나가기 싫다고 할 수 있겠냐고!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001058</t>
-  </si>
-  <si>
-    <t>나가는 종목에 대해서는 조금 더 생각해보겠다고 지금이라도 이야기하면…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001059</t>
-  </si>
-  <si>
-    <t>아니.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001060</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>none</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유가 좋고 싫고 이전에, 이건 확실히 좋은 기회야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001061</t>
-  </si>
-  <si>
-    <t>center</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>메이가 이야기했듯이, 이어달리기는 운동회의 꽃이니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001062</t>
-  </si>
-  <si>
-    <t>거기에 이번에는 원샷 카메라까지 받을 수 있다며?</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001063</t>
-  </si>
-  <si>
-    <t>PD님이 이야기한 것처럼, 이 녀석이 주목 받을 건 거의 확실하니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001064</t>
-  </si>
-  <si>
-    <t>스트레이라이트의 인지도를 올릴 좋은 기회야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001065</t>
-  </si>
-  <si>
-    <t>괜히 나중에 말을 바꿔서 나쁜 인상을 주고 싶지도 않고.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001066</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그치만 후유코쨩이…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001067</t>
-  </si>
-  <si>
-    <t>wait3 face_sad lip_anger2</t>
-  </si>
-  <si>
-    <t>후유코쨩.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001068</t>
-  </si>
-  <si>
-    <t>하기 싫은데 억지로 나가는 건, 이상함다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001069</t>
-  </si>
-  <si>
-    <t>wait1 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그런 거, 전혀 재미있지 않슴다…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001070</t>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>zoom</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>후유코쨩이 하기 싫은 거라면…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001071</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>바보네.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001072</t>
-  </si>
-  <si>
-    <t>어른에게는 하기 싫어도 해야 하는 일이라는 게 있거든.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001073</t>
-  </si>
-  <si>
-    <t>죽을만큼 하기 싫어도, 해야 하는 일이라면 후유는 할 거야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001074</t>
-  </si>
-  <si>
-    <t>… 잘 모르겠슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001075</t>
-  </si>
-  <si>
-    <t>몰라도 돼, 너는.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001076</t>
-  </si>
-  <si>
-    <t>재밌게 달리기만 하면 되니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001077</t>
-  </si>
-  <si>
-    <t>자, 이거.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001078</t>
-  </si>
-  <si>
-    <t>감사함다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001079</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그치만, 후유코쨩 느리니까 1등은 못할 것 같슴다.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001080</t>
-  </si>
-  <si>
-    <t>시끄러! 알고 있거든!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001081</t>
-  </si>
-  <si>
-    <t>아하하, 후유코쨩… 진정 진정~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001082</t>
-  </si>
-  <si>
-    <t>에~ 1등 아니면 재미 없슴다~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001083</t>
-  </si>
-  <si>
-    <t>s001084</t>
-  </si>
-  <si>
-    <t>무리임다, 그런 거~</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001085</t>
-  </si>
-  <si>
-    <t>wipe_left</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_jito lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러니까 싫은 거야. 보는 눈이 너무 많으니까.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger3 face_close3 lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>애초에 후유, 달리기 그렇게 잘 하는 편도 아니고…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그렇구나… </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001086</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile3 face_serious lip_serious_s</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>저번에 나간 대운동회에서는 이상한 얼굴 캡쳐당해서 한동안 돌아다녔고…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001087</t>
-  </si>
-  <si>
-    <t>wait4 face_serious lip_anger</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그런 거, 두번 다시 사양이야.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>s001088</t>
-  </si>
-  <si>
-    <t>좋아! 후유코쨩이 그렇다면 이어달리기는 안 나가는 걸로!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger2 face_smile2 lip_smile1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>clean</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger1 face_serious lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>smile1 face_cry lip_sad</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>하기 싫어도 해야 하는 일…</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S001089</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>think1 face_serious lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug face_close</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나가주는 것 만으로도 감사하게 생각하란 말이야!</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>S001090</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇게 1등이 하고 싶으면, 네가 후유의 몫까지 달리면 되잖아</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>경쾌한 일상</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_101</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM_77</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 메이 무표정으로 말할 때에는 lip_surp 쓰세요</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 사히 무표정으로 말할 때에는 lip_surp 쓰세요</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>너, 어디 간다는 말 들었어?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004023</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 별다른 연락은…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유코, 이거.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004026</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔데?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004027</t>
+  </si>
+  <si>
+    <t>두 사람, 지금 트랙에서 달리기 중이라나 봐.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004028</t>
+  </si>
+  <si>
+    <t>메이, 이런 건 네가 말리란 말이야…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004029</t>
+  </si>
+  <si>
+    <t>anger1 face_close3 lip_bitter_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>후유한테는 큰 소리 쳤으면서,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004030</t>
+  </si>
+  <si>
+    <t>진짜 바보들이라니까.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004031</t>
+  </si>
+  <si>
+    <t>후유코.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004032</t>
+  </si>
+  <si>
+    <t>알고 있어.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004033</t>
+  </si>
+  <si>
+    <t>너는 가게나 예약해 놔.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004034</t>
+  </si>
+  <si>
+    <t>anger3 face_serious lip_smile</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약…?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004035</t>
+  </si>
+  <si>
+    <t>담당 아이돌이 열심히 노력해서 1등을 했는데, 회식 정도는 해야 하지 않겠어?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004036</t>
+  </si>
+  <si>
+    <t>그, 그렇네…</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004037</t>
+  </si>
+  <si>
+    <t>물론, 프로듀서 님이 쏘시는 거죠?</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004038</t>
+  </si>
+  <si>
+    <t>후유는 소고기가 먹고싶은데~</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004039</t>
+  </si>
+  <si>
+    <t>무, 물론이지.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004041</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 나한테 맡겨줘.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>S004040</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -2182,13 +1946,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="넥슨Lv2고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="넥슨Lv2고딕"/>
       <family val="3"/>
@@ -2215,31 +1972,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2258,7 +1995,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2301,21 +2038,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="HeadLine" xfId="1" xr:uid="{E4A97682-4FCD-4053-8CB5-ED3783212F4A}"/>
@@ -2355,12 +2077,12 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <sz val="12"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -2427,28 +2149,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P121" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
-  <autoFilter ref="B2:P121" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8E21CA5-A208-41B6-B5C8-13A3526EE99A}" name="표1" displayName="표1" ref="B2:P118" tableType="xml" totalsRowShown="0" headerRowDxfId="15" headerRowCellStyle="HeadLine" connectionId="1">
+  <autoFilter ref="B2:P118" xr:uid="{160FF696-8FC2-44DF-96A2-501D4731471F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{5FA6574F-1E38-4DF3-B00C-4E51D9874E7C}" uniqueName="Type" name="Type" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Type" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{00C89300-2FD4-4DE1-97BB-669E278B6E51}" uniqueName="Name" name="Name" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{80B42F9F-04FB-43FD-8594-5F56CF126A38}" uniqueName="Text" name="Text" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Text" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="10" dataCellStyle="표준 2">
+    <tableColumn id="4" xr3:uid="{451AAED8-3C4C-42DD-8491-E2D914AFC3C3}" uniqueName="Voice" name="Voice" dataDxfId="11" dataCellStyle="표준 2">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Voice" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{2250E71F-6FFB-46F9-8032-38AFCEA5F92A}" uniqueName="CG" name="CG" dataDxfId="10">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@CG" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{857FC71F-8320-469F-93BE-FCBDE0F4C52F}" uniqueName="Position" name="Position" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Position" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{46E305BE-48DF-4BEC-A79A-2AE3776D3AC7}" uniqueName="Animation" name="Animation" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/Scene/Line/@Animation" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87FED91B-F993-4E51-A50E-383C17A47EAA}" uniqueName="Effect" name="Effect" dataDxfId="7">
@@ -2958,7 +2680,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -3242,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB9BAC8-CA22-4954-AC71-01A81D37B05A}">
-  <dimension ref="B2:P121"/>
+  <dimension ref="B2:P118"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -3311,7 +3033,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3320,23 +3042,19 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="7" t="s">
-        <v>302</v>
-      </c>
+      <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>554</v>
-      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3345,19 +3063,23 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>295</v>
+      </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="M4" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="O4" s="7"/>
-      <c r="P4" s="7" t="s">
-        <v>304</v>
-      </c>
+      <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3365,13 +3087,13 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="7" t="s">
-        <v>306</v>
-      </c>
+      <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -3381,22 +3103,22 @@
         <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>310</v>
-      </c>
       <c r="H6" s="7" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3414,22 +3136,22 @@
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>314</v>
+        <v>368</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3444,32 +3166,20 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="I8" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -3477,65 +3187,49 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>315</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+        <v>371</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>372</v>
+      </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
+      <c r="P9" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K10" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -3546,13 +3240,13 @@
         <v>88</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -3570,20 +3264,26 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>375</v>
+      </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
-        <v>328</v>
-      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="L12" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -3591,35 +3291,41 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>330</v>
-      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="L13" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="7" t="s">
-        <v>304</v>
-      </c>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -3627,44 +3333,28 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>332</v>
-      </c>
+      <c r="L14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>321</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -3672,32 +3362,20 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="I16" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -3705,98 +3383,62 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>527</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>341</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="I19" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L19" s="7"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -3807,23 +3449,17 @@
         <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>530</v>
+        <v>380</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>531</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -3840,13 +3476,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3864,30 +3500,26 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>482</v>
+        <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>64</v>
+        <v>234</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>532</v>
+        <v>384</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H22" t="s">
-        <v>534</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -3895,47 +3527,38 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>537</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="M23" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>482</v>
+        <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>538</v>
+        <v>387</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>539</v>
+        <v>388</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -3943,7 +3566,9 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="L24" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -3954,23 +3579,17 @@
         <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>540</v>
+        <v>389</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>541</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -3987,23 +3606,14 @@
         <v>88</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>349</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -4020,23 +3630,17 @@
         <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>352</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -4053,23 +3657,17 @@
         <v>88</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>138</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
@@ -4086,23 +3684,17 @@
         <v>88</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>357</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -4116,32 +3708,20 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="I30" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
@@ -4149,7 +3729,7 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -4157,43 +3737,43 @@
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
-        <v>328</v>
-      </c>
+      <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
+      <c r="P31" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>239</v>
+        <v>359</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7" t="s">
-        <v>361</v>
-      </c>
+      <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
+      <c r="M32" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="O32" s="7"/>
-      <c r="P32" s="7" t="s">
-        <v>304</v>
-      </c>
+      <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4201,15 +3781,13 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
+      <c r="I33" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J33" s="7"/>
-      <c r="K33" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K33" s="7"/>
       <c r="L33" s="7"/>
-      <c r="M33" s="7" t="s">
-        <v>362</v>
-      </c>
+      <c r="M33" s="7"/>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
@@ -4219,22 +3797,22 @@
         <v>88</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -4249,30 +3827,40 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7" t="s">
-        <v>365</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
+      <c r="L35" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="7" t="s">
-        <v>366</v>
-      </c>
+      <c r="O35" s="7"/>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -4281,44 +3869,44 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
-      <c r="J36" s="7" t="s">
-        <v>302</v>
-      </c>
+      <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
-        <v>555</v>
+        <v>307</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>554</v>
+        <v>319</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="F37" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
+      <c r="L37" s="7" t="s">
+        <v>317</v>
+      </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
       <c r="O37" s="7"/>
-      <c r="P37" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P37" s="7"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -4327,10 +3915,12 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>542</v>
+        <v>316</v>
       </c>
       <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
+      <c r="K38" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -4341,23 +3931,29 @@
       <c r="B39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="C39" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>405</v>
+      </c>
       <c r="F39" s="7" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>368</v>
+        <v>309</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7" t="s">
-        <v>543</v>
+        <v>89</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -4369,14 +3965,12 @@
         <v>88</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>370</v>
+        <v>234</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>372</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -4384,7 +3978,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7" t="s">
-        <v>373</v>
+        <v>89</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -4393,26 +3987,20 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>375</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
+      <c r="I41" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
@@ -4420,53 +4008,45 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>377</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
+      <c r="I42" s="7" t="s">
+        <v>325</v>
+      </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
-      <c r="L42" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
+      <c r="P42" s="7" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>379</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
+      <c r="I43" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="K43" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
@@ -4477,22 +4057,22 @@
         <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>367</v>
+        <v>407</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>382</v>
+        <v>182</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
@@ -4510,13 +4090,13 @@
         <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4534,26 +4114,20 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>386</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
+      <c r="I46" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -4561,59 +4135,43 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>389</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
+      <c r="P47" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>391</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
+      <c r="I48" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="K48" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
@@ -4624,22 +4182,28 @@
         <v>88</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>370</v>
+        <v>234</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
+        <v>410</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
-        <v>373</v>
+        <v>89</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4651,23 +4215,17 @@
         <v>88</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>396</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
@@ -4681,26 +4239,20 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>398</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
+      <c r="I51" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="7"/>
@@ -4708,92 +4260,64 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>401</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
-      <c r="L52" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
+      <c r="P52" s="7" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>403</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="I54" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
@@ -4804,13 +4328,13 @@
         <v>88</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -4828,26 +4352,20 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>409</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
+      <c r="I56" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -4855,7 +4373,7 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -4864,7 +4382,7 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7" t="s">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
@@ -4872,11 +4390,13 @@
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
-      <c r="P57" s="7"/>
+      <c r="P57" s="7" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>239</v>
+        <v>353</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -4884,41 +4404,51 @@
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
+      <c r="I58" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
-      <c r="P58" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P58" s="7"/>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
+      <c r="F59" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H59" t="s">
+        <v>225</v>
+      </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7" t="s">
-        <v>410</v>
-      </c>
+      <c r="L59" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M59" s="7"/>
       <c r="N59" s="7"/>
       <c r="O59" s="7"/>
       <c r="P59" s="7"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -4926,11 +4456,11 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
-      <c r="I60" s="7" t="s">
-        <v>542</v>
-      </c>
+      <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
+      <c r="K60" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -4939,32 +4469,20 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="I61" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
-      <c r="L61" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L61" s="7"/>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
@@ -4972,65 +4490,43 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>318</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
-      <c r="L62" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L62" s="7"/>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
+      <c r="P62" s="7" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I63" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K63" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L63" s="7"/>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -5041,23 +4537,17 @@
         <v>88</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>422</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
@@ -5074,13 +4564,13 @@
         <v>88</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>423</v>
+        <v>234</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -5089,7 +4579,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7" t="s">
-        <v>426</v>
+        <v>89</v>
       </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
@@ -5098,26 +4588,20 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>428</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7" t="s">
-        <v>426</v>
-      </c>
+      <c r="K66" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -5125,26 +4609,20 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>430</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
+      <c r="I67" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
-      <c r="L67" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L67" s="7"/>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
@@ -5152,80 +4630,64 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>432</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
-      <c r="L68" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L68" s="7"/>
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
+      <c r="P68" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>434</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>436</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
+      <c r="I70" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
-      <c r="L70" s="7" t="s">
-        <v>426</v>
-      </c>
+      <c r="L70" s="7"/>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
@@ -5236,22 +4698,22 @@
         <v>88</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>86</v>
+        <v>422</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
@@ -5266,31 +4728,21 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C72" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>440</v>
-      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G72" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="H72" s="7" t="s">
-        <v>414</v>
-      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7" t="s">
-        <v>89</v>
+        <v>317</v>
       </c>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
@@ -5299,59 +4751,45 @@
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>341</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
-      <c r="L73" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>444</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
+      <c r="I74" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7" t="s">
-        <v>426</v>
-      </c>
+      <c r="K74" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L74" s="7"/>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
@@ -5359,67 +4797,51 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>446</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
+      <c r="I75" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
-      <c r="L75" s="7" t="s">
-        <v>373</v>
-      </c>
+      <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
+      <c r="O75" s="7" t="s">
+        <v>302</v>
+      </c>
       <c r="P75" s="7"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>414</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
+      <c r="P76" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -5427,31 +4849,45 @@
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
+      <c r="I77" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
-      <c r="M77" s="7" t="s">
-        <v>449</v>
-      </c>
+      <c r="M77" s="7"/>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H78" t="s">
+        <v>364</v>
+      </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
+      <c r="L78" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
@@ -5459,7 +4895,7 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -5467,22 +4903,22 @@
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
-        <v>365</v>
-      </c>
+      <c r="I79" s="7"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7" t="s">
-        <v>366</v>
-      </c>
+      <c r="M79" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="O79" s="7"/>
       <c r="P79" s="7"/>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -5491,44 +4927,46 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
-      <c r="J80" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="K80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="L80" s="7"/>
-      <c r="M80" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="N80" s="7" t="s">
-        <v>554</v>
-      </c>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
+      <c r="L81" s="7" t="s">
+        <v>306</v>
+      </c>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
-      <c r="P81" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P81" s="7"/>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>411</v>
+        <v>299</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -5537,7 +4975,7 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>542</v>
+        <v>342</v>
       </c>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
@@ -5549,65 +4987,49 @@
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>309</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
       <c r="G83" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H83" t="s">
-        <v>139</v>
-      </c>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
+        <v>427</v>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>315</v>
+      </c>
       <c r="K83" s="7"/>
-      <c r="L83" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
+      <c r="P83" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="I84" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K84" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L84" s="7"/>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
       <c r="O84" s="7"/>
@@ -5615,76 +5037,67 @@
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D85" t="s">
-        <v>457</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>458</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
       <c r="F85" s="7"/>
-      <c r="L85" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
+      <c r="P85" s="7"/>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>461</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
-      <c r="L86" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L86" s="7"/>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
       <c r="O86" s="7"/>
-      <c r="P86" s="7"/>
+      <c r="P86" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>211</v>
+        <v>311</v>
+      </c>
+      <c r="H87" t="s">
+        <v>357</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
@@ -5702,13 +5115,13 @@
         <v>88</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>423</v>
+        <v>305</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -5717,7 +5130,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7" t="s">
-        <v>426</v>
+        <v>306</v>
       </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -5726,126 +5139,140 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="K89">
-        <v>0.3</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="M89" s="7"/>
+      <c r="N89" s="7"/>
+      <c r="O89" s="7"/>
+      <c r="P89" s="7"/>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F90" t="s">
-        <v>468</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7" t="s">
+      <c r="K90" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
+      <c r="L90" s="7"/>
+      <c r="M90" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D91" t="s">
-        <v>469</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="L91">
-        <v>1</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="7"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D92" t="s">
-        <v>472</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="L92">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="7"/>
+      <c r="N92" s="7"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D93" t="s">
-        <v>474</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="L93">
-        <v>1</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>476</v>
+        <v>434</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>352</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
@@ -5857,17 +5284,16 @@
         <v>88</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
@@ -5884,28 +5310,22 @@
         <v>88</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>545</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
@@ -5914,32 +5334,19 @@
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="I97" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
-      <c r="L97" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
@@ -5947,52 +5354,42 @@
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="F98" t="s">
-        <v>468</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
-      <c r="L98" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L98" s="7"/>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
+      <c r="P98" s="7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="F99" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="G99" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="H99" s="15" t="s">
-        <v>490</v>
+        <v>333</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H99" t="s">
+        <v>225</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
@@ -6007,26 +5404,17 @@
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F100" s="16"/>
-      <c r="G100" s="16"/>
-      <c r="H100" s="17"/>
+        <v>304</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
-      <c r="L100" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L100" s="7"/>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
       <c r="O100" s="7"/>
@@ -6034,47 +5422,52 @@
     </row>
     <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="G101" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>495</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="H101" t="s">
+        <v>442</v>
+      </c>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
       <c r="K101" s="7"/>
-      <c r="L101" s="7"/>
+      <c r="L101" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
       <c r="O101" s="7"/>
-      <c r="P101" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="P101" s="7"/>
     </row>
     <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>496</v>
+        <v>443</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="F102" t="s">
-        <v>468</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
@@ -6088,40 +5481,50 @@
     </row>
     <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="K103">
-        <v>0.5</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H103" t="s">
+        <v>328</v>
+      </c>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M103" s="7"/>
+      <c r="N103" s="7"/>
+      <c r="O103" s="7"/>
+      <c r="P103" s="7"/>
     </row>
     <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>148</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
-      <c r="L104" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="L104" s="7"/>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
       <c r="O104" s="7"/>
@@ -6132,13 +5535,13 @@
         <v>88</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>500</v>
+        <v>447</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>501</v>
+        <v>448</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
@@ -6147,7 +5550,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -6159,17 +5562,23 @@
         <v>88</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>502</v>
+        <v>449</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
+        <v>450</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H106" t="s">
+        <v>327</v>
+      </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -6183,59 +5592,41 @@
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="F107" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="G107" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="H107" s="17" t="s">
-        <v>548</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
-      <c r="L107" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
+      <c r="L107" s="7"/>
+      <c r="M107" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="N107" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="O107" s="7"/>
       <c r="P107" s="7"/>
     </row>
     <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="F108" s="16"/>
-      <c r="G108" s="16"/>
-      <c r="H108" s="17"/>
+        <v>304</v>
+      </c>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K108" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L108" s="7"/>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
       <c r="O108" s="7"/>
@@ -6246,22 +5637,18 @@
         <v>88</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>506</v>
+        <v>451</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G109" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="H109" s="7" t="s">
-        <v>549</v>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" t="s">
+        <v>453</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
@@ -6279,13 +5666,13 @@
         <v>88</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>509</v>
+        <v>455</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -6294,7 +5681,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -6306,17 +5693,23 @@
         <v>88</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>510</v>
+        <v>456</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
+        <v>457</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H111" t="s">
+        <v>237</v>
+      </c>
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
@@ -6333,28 +5726,22 @@
         <v>88</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="F112" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="G112" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="H112" s="15" t="s">
-        <v>490</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -6363,24 +5750,34 @@
     </row>
     <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H113" t="s">
+        <v>222</v>
+      </c>
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="N113" s="7" t="s">
-        <v>332</v>
-      </c>
+      <c r="L113" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
       <c r="O113" s="7"/>
       <c r="P113" s="7"/>
     </row>
@@ -6389,17 +5786,16 @@
         <v>88</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>514</v>
+        <v>462</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="F114" s="16"/>
-      <c r="G114" s="16"/>
-      <c r="H114" s="15"/>
+        <v>463</v>
+      </c>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
@@ -6416,28 +5812,24 @@
         <v>88</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>516</v>
+        <v>464</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>517</v>
+        <v>465</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>82</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
@@ -6449,13 +5841,13 @@
         <v>88</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>550</v>
+        <v>466</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>551</v>
+        <v>467</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -6464,7 +5856,7 @@
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7" t="s">
-        <v>89</v>
+        <v>306</v>
       </c>
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
@@ -6473,158 +5865,48 @@
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="H117" t="s">
-        <v>220</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
-      <c r="L117" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
+      <c r="L117" s="7"/>
+      <c r="M117" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="N117" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="O117" s="7"/>
       <c r="P117" s="7"/>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="F118" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="G118" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="H118" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I118" s="7"/>
+        <v>304</v>
+      </c>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K118" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="L118" s="7"/>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
       <c r="O118" s="7"/>
       <c r="P118" s="7"/>
-    </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B119" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I119" s="7"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-    </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B120" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="F120" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="G120" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="H120" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-    </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B121" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="P121" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -6637,7 +5919,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0AC287-6B30-491F-A320-ECD650B57881}">
-  <dimension ref="B2:P36"/>
+  <dimension ref="B2:P43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
@@ -6662,13 +5944,13 @@
         <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M3" t="s">
         <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
@@ -6679,16 +5961,16 @@
         <v>212</v>
       </c>
       <c r="G4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N4" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
@@ -6702,93 +5984,93 @@
         <v>213</v>
       </c>
       <c r="H5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M5" t="s">
         <v>213</v>
       </c>
       <c r="N5" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G6" t="s">
         <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="M6" t="s">
         <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
         <v>217</v>
       </c>
       <c r="G7" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="H7" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N7" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
         <v>218</v>
       </c>
       <c r="G8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="M8" t="s">
         <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>350</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="M9" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="N9" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
@@ -6799,16 +6081,16 @@
         <v>221</v>
       </c>
       <c r="G10" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H10" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M10" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N10" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -6819,96 +6101,96 @@
         <v>223</v>
       </c>
       <c r="G11" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M11" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="N11" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>347</v>
       </c>
       <c r="G12" t="s">
         <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M12" t="s">
         <v>182</v>
       </c>
       <c r="N12" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>348</v>
       </c>
       <c r="G13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H13" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="M13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="G14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H14" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="M14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N14" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H15" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N15" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -6916,39 +6198,39 @@
         <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="M16" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N16" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G17" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H17" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="M17" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N17" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -6956,19 +6238,19 @@
         <v>183</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="G18" t="s">
         <v>183</v>
       </c>
       <c r="H18" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="M18" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="N18" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
@@ -6976,88 +6258,82 @@
         <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="G19" t="s">
         <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M19" t="s">
         <v>78</v>
       </c>
       <c r="N19" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="M20" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N20" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>557</v>
+      <c r="G22" s="13" t="s">
+        <v>320</v>
       </c>
       <c r="M22" t="s">
         <v>183</v>
       </c>
       <c r="N22" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>248</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N23" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s">
         <v>65</v>
@@ -7065,16 +6341,16 @@
       <c r="J25" t="s">
         <v>72</v>
       </c>
-      <c r="M25" s="18" t="s">
-        <v>558</v>
+      <c r="M25" s="13" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
         <v>66</v>
@@ -7091,10 +6367,10 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G27" t="s">
         <v>86</v>
@@ -7111,10 +6387,10 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="G28" t="s">
         <v>139</v>
@@ -7131,10 +6407,10 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s">
         <v>145</v>
@@ -7151,10 +6427,10 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M30" t="s">
         <v>82</v>
@@ -7165,10 +6441,10 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>250</v>
+        <v>183</v>
       </c>
       <c r="E31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M31" t="s">
         <v>141</v>
@@ -7179,13 +6455,13 @@
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M32" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="P32" t="s">
         <v>147</v>
@@ -7193,34 +6469,74 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E34" t="s">
-        <v>243</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E35" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E36" t="s">
-        <v>247</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>334</v>
+      </c>
+      <c r="E39" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>336</v>
+      </c>
+      <c r="E40" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>338</v>
+      </c>
+      <c r="E41" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>340</v>
+      </c>
+      <c r="E43" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -7595,12 +6911,20 @@
         <v>101</v>
       </c>
     </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>318</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>553</v>
+        <v>322</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/resource/Script/ScriptManual.xlsx
+++ b/resource/Script/ScriptManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usosctheater\resource\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7D31FD-91B2-4F4B-B070-35FF9B0D337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F37E61-7398-4158-BCAF-93B10B83125C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{F190326C-52FC-4B9A-869B-607708A8B8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptManual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="470">
   <si>
     <t>* 본 문서는 가짜샤니마스극장의 스크립트에 사용할 스크립트 전용 제작 시트입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -586,10 +586,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>키티탄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>No7</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -628,10 +624,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>진지한 표정으로 이야기</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>wait4</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1194,10 +1186,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>wait1 face_wait lip_surp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>AUDIO</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1846,6 +1834,26 @@
   </si>
   <si>
     <t>S004040</t>
+  </si>
+  <si>
+    <t>키리땅</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>즌코</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>들썩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait1 lip_surp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>무표정으로 이야기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2680,12 +2688,12 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -2835,10 +2843,10 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>23</v>
@@ -2852,16 +2860,16 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -2869,36 +2877,36 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="F43" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="F44" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -2906,54 +2914,54 @@
         <v>19</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="2:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3033,7 +3041,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3049,12 +3057,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3064,22 +3072,22 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3088,7 +3096,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3103,22 +3111,22 @@
         <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3136,22 +3144,22 @@
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3166,7 +3174,7 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3175,7 +3183,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -3187,21 +3195,21 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -3209,12 +3217,12 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3223,11 +3231,11 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -3240,13 +3248,13 @@
         <v>88</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -3267,13 +3275,13 @@
         <v>88</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -3294,13 +3302,13 @@
         <v>88</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -3321,10 +3329,10 @@
         <v>88</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3343,7 +3351,7 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -3362,7 +3370,7 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -3371,7 +3379,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -3383,7 +3391,7 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -3399,12 +3407,12 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -3417,7 +3425,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -3425,7 +3433,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -3434,7 +3442,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -3449,13 +3457,13 @@
         <v>88</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -3476,13 +3484,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -3503,13 +3511,13 @@
         <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -3527,7 +3535,7 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -3539,10 +3547,10 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -3552,13 +3560,13 @@
         <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -3579,13 +3587,13 @@
         <v>88</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -3606,10 +3614,10 @@
         <v>88</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -3630,13 +3638,13 @@
         <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -3657,13 +3665,13 @@
         <v>88</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -3684,13 +3692,13 @@
         <v>88</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -3708,7 +3716,7 @@
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3717,7 +3725,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -3729,7 +3737,7 @@
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -3745,12 +3753,12 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -3763,17 +3771,17 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -3782,7 +3790,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -3797,22 +3805,22 @@
         <v>88</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -3830,22 +3838,22 @@
         <v>88</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
@@ -3860,7 +3868,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -3873,23 +3881,23 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -3897,7 +3905,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -3906,7 +3914,7 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -3915,11 +3923,11 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -3932,22 +3940,22 @@
         <v>88</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
@@ -3965,10 +3973,10 @@
         <v>88</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -3987,7 +3995,7 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -3996,7 +4004,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
@@ -4008,7 +4016,7 @@
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -4017,7 +4025,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
@@ -4026,12 +4034,12 @@
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
       <c r="P42" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -4040,11 +4048,11 @@
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J43" s="7"/>
       <c r="K43" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
@@ -4057,22 +4065,22 @@
         <v>88</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
@@ -4090,13 +4098,13 @@
         <v>88</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -4114,7 +4122,7 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -4123,7 +4131,7 @@
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
       <c r="I46" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
@@ -4135,7 +4143,7 @@
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -4151,12 +4159,12 @@
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
       <c r="P47" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -4165,11 +4173,11 @@
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
       <c r="I48" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J48" s="7"/>
       <c r="K48" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
@@ -4182,22 +4190,22 @@
         <v>88</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
@@ -4215,13 +4223,13 @@
         <v>88</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -4239,7 +4247,7 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -4248,7 +4256,7 @@
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
       <c r="I51" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
@@ -4260,7 +4268,7 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -4276,12 +4284,12 @@
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
       <c r="P52" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4294,17 +4302,17 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -4313,7 +4321,7 @@
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
@@ -4328,13 +4336,13 @@
         <v>88</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -4352,7 +4360,7 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -4361,7 +4369,7 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
@@ -4373,7 +4381,7 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -4382,7 +4390,7 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
@@ -4391,12 +4399,12 @@
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
       <c r="P57" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -4405,7 +4413,7 @@
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
@@ -4420,20 +4428,20 @@
         <v>88</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H59" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
@@ -4448,7 +4456,7 @@
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -4459,7 +4467,7 @@
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
@@ -4469,7 +4477,7 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -4478,7 +4486,7 @@
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
@@ -4490,7 +4498,7 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -4506,12 +4514,12 @@
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
       <c r="P62" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -4520,11 +4528,11 @@
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J63" s="7"/>
       <c r="K63" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
@@ -4537,13 +4545,13 @@
         <v>88</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -4564,13 +4572,13 @@
         <v>88</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -4588,7 +4596,7 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -4599,7 +4607,7 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
@@ -4609,7 +4617,7 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -4618,7 +4626,7 @@
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
@@ -4630,7 +4638,7 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -4646,12 +4654,12 @@
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
       <c r="P68" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -4664,17 +4672,17 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N69" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -4683,7 +4691,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
@@ -4698,22 +4706,22 @@
         <v>88</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
@@ -4728,13 +4736,13 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -4742,7 +4750,7 @@
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
@@ -4751,7 +4759,7 @@
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -4764,17 +4772,17 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -4783,11 +4791,11 @@
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J74" s="7"/>
       <c r="K74" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
@@ -4797,7 +4805,7 @@
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -4806,7 +4814,7 @@
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
@@ -4814,13 +4822,13 @@
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P75" s="7"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -4836,12 +4844,12 @@
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
       <c r="P76" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -4850,7 +4858,7 @@
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
@@ -4865,22 +4873,22 @@
         <v>88</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H78" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
@@ -4895,7 +4903,7 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -4908,17 +4916,17 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O79" s="7"/>
       <c r="P79" s="7"/>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -4929,7 +4937,7 @@
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
       <c r="K80" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
@@ -4942,13 +4950,13 @@
         <v>88</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
@@ -4957,7 +4965,7 @@
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
@@ -4966,7 +4974,7 @@
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -4975,7 +4983,7 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
@@ -4987,21 +4995,21 @@
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
       <c r="G83" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -5009,12 +5017,12 @@
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
       <c r="P83" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -5023,11 +5031,11 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J84" s="7"/>
       <c r="K84" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
@@ -5037,7 +5045,7 @@
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -5046,7 +5054,7 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5058,7 +5066,7 @@
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -5074,7 +5082,7 @@
       <c r="N86" s="7"/>
       <c r="O86" s="7"/>
       <c r="P86" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
@@ -5082,22 +5090,22 @@
         <v>88</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H87" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
@@ -5115,13 +5123,13 @@
         <v>88</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -5130,7 +5138,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -5142,13 +5150,13 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -5157,7 +5165,7 @@
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
       <c r="L89" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
@@ -5166,7 +5174,7 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -5181,7 +5189,7 @@
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N90" s="7" t="s">
         <v>89</v>
@@ -5191,7 +5199,7 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -5200,7 +5208,7 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
@@ -5212,7 +5220,7 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -5228,12 +5236,12 @@
       <c r="N92" s="7"/>
       <c r="O92" s="7"/>
       <c r="P92" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -5242,7 +5250,7 @@
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
@@ -5257,13 +5265,13 @@
         <v>88</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -5272,7 +5280,7 @@
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
@@ -5284,13 +5292,13 @@
         <v>88</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -5310,13 +5318,13 @@
         <v>88</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -5325,7 +5333,7 @@
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
@@ -5334,7 +5342,7 @@
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -5342,7 +5350,7 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -5354,7 +5362,7 @@
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -5369,7 +5377,7 @@
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
       <c r="P98" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
@@ -5377,19 +5385,19 @@
         <v>88</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H99" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
@@ -5404,7 +5412,7 @@
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -5425,22 +5433,22 @@
         <v>88</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H101" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
@@ -5458,13 +5466,13 @@
         <v>88</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -5484,22 +5492,22 @@
         <v>88</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H103" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -5514,7 +5522,7 @@
     </row>
     <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -5535,13 +5543,13 @@
         <v>88</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
@@ -5550,7 +5558,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -5562,22 +5570,22 @@
         <v>88</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H106" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
@@ -5592,7 +5600,7 @@
     </row>
     <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -5604,17 +5612,17 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N107" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O107" s="7"/>
       <c r="P107" s="7"/>
     </row>
     <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -5624,7 +5632,7 @@
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
@@ -5637,18 +5645,18 @@
         <v>88</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
       <c r="H109" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
@@ -5666,13 +5674,13 @@
         <v>88</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -5681,7 +5689,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -5693,22 +5701,22 @@
         <v>88</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H111" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
@@ -5726,13 +5734,13 @@
         <v>88</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -5741,7 +5749,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -5753,22 +5761,22 @@
         <v>88</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H113" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
@@ -5786,13 +5794,13 @@
         <v>88</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -5812,16 +5820,16 @@
         <v>88</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
@@ -5829,7 +5837,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
@@ -5841,13 +5849,13 @@
         <v>88</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -5856,7 +5864,7 @@
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
@@ -5865,7 +5873,7 @@
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -5878,17 +5886,17 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N117" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O117" s="7"/>
       <c r="P117" s="7"/>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -5896,11 +5904,11 @@
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J118" s="7"/>
       <c r="K118" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
@@ -5938,79 +5946,79 @@
         <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G3" t="s">
         <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M3" t="s">
         <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G6" t="s">
         <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M6" t="s">
         <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
@@ -6018,292 +6026,292 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M8" t="s">
         <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G10" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" t="s">
+        <v>282</v>
+      </c>
+      <c r="M10" t="s">
         <v>254</v>
       </c>
-      <c r="H10" t="s">
-        <v>284</v>
-      </c>
-      <c r="M10" t="s">
-        <v>256</v>
-      </c>
       <c r="N10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G11" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" t="s">
+        <v>279</v>
+      </c>
+      <c r="M11" t="s">
         <v>256</v>
       </c>
-      <c r="H11" t="s">
-        <v>281</v>
-      </c>
-      <c r="M11" t="s">
-        <v>258</v>
-      </c>
       <c r="N11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C14" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H14" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H15" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M19" t="s">
         <v>78</v>
       </c>
       <c r="N19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="M20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="G22" s="13" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M22" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
@@ -6314,23 +6322,29 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="N23" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E24" t="s">
         <v>70</v>
       </c>
+      <c r="M24" t="s">
+        <v>272</v>
+      </c>
+      <c r="N24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E25" t="s">
         <v>84</v>
@@ -6341,16 +6355,13 @@
       <c r="J25" t="s">
         <v>72</v>
       </c>
-      <c r="M25" s="13" t="s">
-        <v>321</v>
-      </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
         <v>66</v>
@@ -6358,19 +6369,16 @@
       <c r="J26" t="s">
         <v>73</v>
       </c>
-      <c r="M26" t="s">
-        <v>90</v>
-      </c>
-      <c r="P26" t="s">
-        <v>91</v>
+      <c r="M26" s="13" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
         <v>86</v>
@@ -6379,164 +6387,170 @@
         <v>87</v>
       </c>
       <c r="M27" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" t="s">
         <v>139</v>
       </c>
-      <c r="J28" t="s">
-        <v>140</v>
-      </c>
       <c r="M28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G29" t="s">
+        <v>144</v>
+      </c>
+      <c r="J29" t="s">
         <v>145</v>
       </c>
-      <c r="J29" t="s">
-        <v>146</v>
-      </c>
       <c r="M29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" t="s">
         <v>183</v>
       </c>
-      <c r="E31" t="s">
-        <v>185</v>
-      </c>
       <c r="M31" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="P31" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="M32" t="s">
+        <v>140</v>
+      </c>
+      <c r="P32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" t="s">
+        <v>185</v>
+      </c>
+      <c r="M33" t="s">
+        <v>468</v>
+      </c>
+      <c r="P33" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>243</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E34" t="s">
         <v>186</v>
       </c>
-      <c r="M32" t="s">
-        <v>293</v>
-      </c>
-      <c r="P32" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>244</v>
-      </c>
-      <c r="E33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>235</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>237</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E37" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>239</v>
-      </c>
-      <c r="E37" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
+        <v>331</v>
+      </c>
+      <c r="E39" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>333</v>
+      </c>
+      <c r="E40" t="s">
         <v>334</v>
       </c>
-      <c r="E39" t="s">
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
+      <c r="E41" t="s">
         <v>336</v>
       </c>
-      <c r="E40" t="s">
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+      <c r="E43" t="s">
         <v>338</v>
-      </c>
-      <c r="E41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>340</v>
-      </c>
-      <c r="E43" t="s">
-        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6608,6 +6622,9 @@
       <c r="C12" t="s">
         <v>104</v>
       </c>
+      <c r="D12" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
@@ -6675,7 +6692,7 @@
         <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
@@ -6699,7 +6716,7 @@
         <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
@@ -6773,74 +6790,74 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F10">
         <v>71</v>
@@ -6848,10 +6865,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F11">
         <v>73</v>
@@ -6859,7 +6876,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -6867,7 +6884,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F13">
         <v>77</v>
@@ -6875,10 +6892,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F14">
         <v>88</v>
@@ -6886,10 +6903,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -6897,7 +6914,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -6905,7 +6922,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F17">
         <v>101</v>
@@ -6913,7 +6930,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -6921,7 +6938,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F19">
         <v>102</v>
